--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A62E2C-B67D-3F4E-9B38-466B9B70D95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AC7F90-D72B-FB44-BAD0-C18F42BEE336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23600" yWindow="3900" windowWidth="22500" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4240" yWindow="4100" windowWidth="22500" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>First name</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>Holman</t>
+  </si>
+  <si>
+    <t>Exam 1</t>
+  </si>
+  <si>
+    <t>total</t>
   </si>
 </sst>
 </file>
@@ -634,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:M30"/>
+  <dimension ref="A3:M52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
@@ -1010,6 +1016,155 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>4</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>5</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>6</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>7</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>8</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>12</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>13</v>
+      </c>
+      <c r="B46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>14</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>15</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52">
+        <f>SUM(B34:B51)</f>
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AC7F90-D72B-FB44-BAD0-C18F42BEE336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252D6949-A9FA-5F4B-9A4B-1CF5F8B05361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4240" yWindow="4100" windowWidth="22500" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -640,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:M52"/>
+  <dimension ref="A3:M53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
@@ -694,13 +694,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -708,13 +708,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -722,13 +722,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -736,13 +736,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -750,13 +750,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -764,13 +764,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -778,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -792,13 +792,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -806,13 +806,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -820,13 +820,13 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -834,13 +834,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -848,13 +848,13 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -862,200 +862,192 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>20</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>21</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F29" s="1" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B30">
-        <f>COUNT(B5:B23,B26:B27)</f>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <f>COUNT(B5:B17,B27:B28)</f>
         <v>0</v>
       </c>
-      <c r="C30">
-        <f>COUNT(C5:C23,C26:C27)</f>
+      <c r="C31">
+        <f>COUNT(C5:C17,C27:C28)</f>
         <v>0</v>
       </c>
-      <c r="D30">
-        <f>COUNT(D5:D23,D26:D27)</f>
+      <c r="D31">
+        <f>COUNT(D5:D17,D27:D28)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B33" s="1" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34">
-        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38">
         <v>6</v>
@@ -1063,31 +1055,31 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
+        <v>5</v>
+      </c>
+      <c r="B39">
         <v>6</v>
-      </c>
-      <c r="B39">
-        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41">
         <v>8</v>
-      </c>
-      <c r="B41">
-        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -1095,23 +1087,23 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -1119,49 +1111,57 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B52">
-        <f>SUM(B34:B51)</f>
+      <c r="B53">
+        <f>SUM(B35:B52)</f>
         <v>100</v>
       </c>
     </row>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252D6949-A9FA-5F4B-9A4B-1CF5F8B05361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F451E5D-B505-6B4F-9CA7-CD10B19FF4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="4100" windowWidth="22500" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4240" yWindow="4100" windowWidth="28680" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>First name</t>
   </si>
@@ -264,6 +264,78 @@
   </si>
   <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>Z Bevans</t>
+  </si>
+  <si>
+    <t>W. Cho</t>
+  </si>
+  <si>
+    <t>J. Falcoz-Vigne</t>
+  </si>
+  <si>
+    <t>Fahim Foraejee</t>
+  </si>
+  <si>
+    <t>S. Hood</t>
+  </si>
+  <si>
+    <t>A. Masi</t>
+  </si>
+  <si>
+    <t>A. Mathias</t>
+  </si>
+  <si>
+    <t>J. Pack</t>
+  </si>
+  <si>
+    <t>F. Smith</t>
+  </si>
+  <si>
+    <t>C. van Heugten</t>
+  </si>
+  <si>
+    <t>M. Velasco</t>
+  </si>
+  <si>
+    <t>B. Wilson</t>
+  </si>
+  <si>
+    <t>E. Wilson</t>
+  </si>
+  <si>
+    <t>E. Arnold</t>
+  </si>
+  <si>
+    <t>C. Bowers</t>
+  </si>
+  <si>
+    <t>I. Caraballo-Lopez</t>
+  </si>
+  <si>
+    <t>I. Davis</t>
+  </si>
+  <si>
+    <t>P. Decker-Fish</t>
+  </si>
+  <si>
+    <t>Z. Sweeney</t>
+  </si>
+  <si>
+    <t>C. Myers</t>
+  </si>
+  <si>
+    <t>T. Holman</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Avg + curve</t>
+  </si>
+  <si>
+    <t>Stdev</t>
   </si>
 </sst>
 </file>
@@ -640,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:M53"/>
+  <dimension ref="A3:W55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
@@ -702,6 +774,9 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
+      <c r="F5">
+        <v>93</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -716,6 +791,9 @@
       <c r="D6" t="s">
         <v>18</v>
       </c>
+      <c r="F6">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -730,6 +808,9 @@
       <c r="D7" t="s">
         <v>27</v>
       </c>
+      <c r="F7">
+        <v>97</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -744,6 +825,9 @@
       <c r="D8" t="s">
         <v>30</v>
       </c>
+      <c r="F8">
+        <v>98</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -758,6 +842,9 @@
       <c r="D9" t="s">
         <v>33</v>
       </c>
+      <c r="F9">
+        <v>76</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -771,6 +858,9 @@
       </c>
       <c r="D10" t="s">
         <v>36</v>
+      </c>
+      <c r="F10">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -786,6 +876,9 @@
       <c r="D11" t="s">
         <v>39</v>
       </c>
+      <c r="F11">
+        <v>94</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -800,6 +893,9 @@
       <c r="D12" t="s">
         <v>45</v>
       </c>
+      <c r="F12">
+        <v>85</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -814,6 +910,9 @@
       <c r="D13" t="s">
         <v>48</v>
       </c>
+      <c r="F13">
+        <v>92</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -828,6 +927,9 @@
       <c r="D14" t="s">
         <v>53</v>
       </c>
+      <c r="F14">
+        <v>93</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -842,6 +944,9 @@
       <c r="D15" t="s">
         <v>56</v>
       </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -856,6 +961,9 @@
       <c r="D16" t="s">
         <v>59</v>
       </c>
+      <c r="F16">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
@@ -870,6 +978,9 @@
       <c r="D17" t="s">
         <v>60</v>
       </c>
+      <c r="F17">
+        <v>78</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
@@ -884,6 +995,9 @@
       <c r="D19" t="s">
         <v>6</v>
       </c>
+      <c r="F19">
+        <v>100</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
@@ -898,6 +1012,9 @@
       <c r="D20" t="s">
         <v>12</v>
       </c>
+      <c r="F20">
+        <v>94</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
@@ -940,6 +1057,9 @@
       <c r="D23" t="s">
         <v>24</v>
       </c>
+      <c r="F23">
+        <v>86</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
@@ -954,6 +1074,9 @@
       <c r="D24" t="s">
         <v>50</v>
       </c>
+      <c r="F24">
+        <v>78</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
@@ -973,6 +1096,9 @@
       <c r="D27" t="s">
         <v>42</v>
       </c>
+      <c r="F27">
+        <v>72</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28">
@@ -987,182 +1113,1202 @@
       <c r="D28" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="F28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F30" s="1" t="s">
+      <c r="E30" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30">
+        <f>AVERAGE(F5:F28)</f>
+        <v>83.263157894736835</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <f>STDEV(F5:F28)</f>
+        <v>19.53868557293783</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E32" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <f>COUNT(B5:B17,B27:B28)</f>
+      <c r="F32" s="1">
+        <v>7</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="E33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33">
+        <f>F30+F32</f>
+        <v>90.263157894736835</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>11</v>
+      </c>
+      <c r="H37">
+        <v>12</v>
+      </c>
+      <c r="I37">
+        <v>12</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37">
+        <v>12</v>
+      </c>
+      <c r="L37">
+        <v>11</v>
+      </c>
+      <c r="M37">
+        <v>12</v>
+      </c>
+      <c r="N37">
+        <v>11</v>
+      </c>
+      <c r="O37">
+        <v>7</v>
+      </c>
+      <c r="P37">
+        <v>12</v>
+      </c>
+      <c r="Q37">
+        <v>11</v>
+      </c>
+      <c r="T37">
+        <v>6</v>
+      </c>
+      <c r="U37">
+        <v>11</v>
+      </c>
+      <c r="V37">
+        <v>9</v>
+      </c>
+      <c r="W37">
         <v>0</v>
       </c>
-      <c r="C31">
-        <f>COUNT(C5:C17,C27:C28)</f>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <v>18</v>
+      </c>
+      <c r="C38">
+        <v>18</v>
+      </c>
+      <c r="D38">
+        <v>18</v>
+      </c>
+      <c r="E38">
+        <v>18</v>
+      </c>
+      <c r="F38">
+        <v>18</v>
+      </c>
+      <c r="G38">
+        <v>14</v>
+      </c>
+      <c r="H38">
+        <v>16</v>
+      </c>
+      <c r="I38">
+        <v>16</v>
+      </c>
+      <c r="J38">
+        <v>18</v>
+      </c>
+      <c r="K38">
+        <v>18</v>
+      </c>
+      <c r="L38">
+        <v>16</v>
+      </c>
+      <c r="M38">
+        <v>18</v>
+      </c>
+      <c r="N38">
+        <v>17</v>
+      </c>
+      <c r="O38">
+        <v>18</v>
+      </c>
+      <c r="P38">
+        <v>18</v>
+      </c>
+      <c r="Q38">
+        <v>16</v>
+      </c>
+      <c r="T38">
+        <v>14</v>
+      </c>
+      <c r="U38">
+        <v>10</v>
+      </c>
+      <c r="V38">
+        <v>6</v>
+      </c>
+      <c r="W38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="H39">
+        <v>7</v>
+      </c>
+      <c r="I39">
+        <v>6</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39">
+        <v>7</v>
+      </c>
+      <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="M39">
+        <v>8</v>
+      </c>
+      <c r="N39">
+        <v>8</v>
+      </c>
+      <c r="O39">
+        <v>6</v>
+      </c>
+      <c r="P39">
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <v>7</v>
+      </c>
+      <c r="T39">
+        <v>5</v>
+      </c>
+      <c r="U39">
+        <v>7</v>
+      </c>
+      <c r="V39">
+        <v>8</v>
+      </c>
+      <c r="W39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>4</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>6</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="H40">
+        <v>6</v>
+      </c>
+      <c r="I40">
+        <v>6</v>
+      </c>
+      <c r="J40">
+        <v>6</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>6</v>
+      </c>
+      <c r="M40">
+        <v>6</v>
+      </c>
+      <c r="N40">
+        <v>4</v>
+      </c>
+      <c r="O40">
+        <v>6</v>
+      </c>
+      <c r="P40">
+        <v>6</v>
+      </c>
+      <c r="Q40">
+        <v>4</v>
+      </c>
+      <c r="T40">
+        <v>5</v>
+      </c>
+      <c r="U40">
+        <v>6</v>
+      </c>
+      <c r="V40">
+        <v>6</v>
+      </c>
+      <c r="W40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>5</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>6</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
+        <v>6</v>
+      </c>
+      <c r="F41">
+        <v>6</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>5</v>
+      </c>
+      <c r="I41">
+        <v>6</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41">
+        <v>6</v>
+      </c>
+      <c r="L41">
+        <v>5</v>
+      </c>
+      <c r="M41">
+        <v>6</v>
+      </c>
+      <c r="N41">
         <v>0</v>
       </c>
-      <c r="D31">
-        <f>COUNT(D5:D17,D27:D28)</f>
+      <c r="O41">
+        <v>5</v>
+      </c>
+      <c r="P41">
+        <v>6</v>
+      </c>
+      <c r="Q41">
+        <v>6</v>
+      </c>
+      <c r="T41">
+        <v>6</v>
+      </c>
+      <c r="U41">
+        <v>6</v>
+      </c>
+      <c r="V41">
+        <v>6</v>
+      </c>
+      <c r="W41">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>6</v>
+      </c>
+      <c r="B42">
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>5</v>
+      </c>
+      <c r="H42">
+        <v>5</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42">
+        <v>4</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>4</v>
+      </c>
+      <c r="O42">
+        <v>4</v>
+      </c>
+      <c r="P42">
+        <v>5</v>
+      </c>
+      <c r="Q42">
+        <v>5</v>
+      </c>
+      <c r="T42">
+        <v>5</v>
+      </c>
+      <c r="U42">
+        <v>5</v>
+      </c>
+      <c r="V42">
+        <v>3</v>
+      </c>
+      <c r="W42">
         <v>1</v>
       </c>
-      <c r="B35">
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>7</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43">
+        <v>8</v>
+      </c>
+      <c r="H43">
+        <v>8</v>
+      </c>
+      <c r="I43">
+        <v>8</v>
+      </c>
+      <c r="J43">
+        <v>8</v>
+      </c>
+      <c r="K43">
+        <v>7</v>
+      </c>
+      <c r="L43">
+        <v>8</v>
+      </c>
+      <c r="M43">
+        <v>8</v>
+      </c>
+      <c r="N43">
+        <v>4</v>
+      </c>
+      <c r="O43">
+        <v>5</v>
+      </c>
+      <c r="P43">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>8</v>
+      </c>
+      <c r="T43">
+        <v>8</v>
+      </c>
+      <c r="U43">
+        <v>6</v>
+      </c>
+      <c r="V43">
+        <v>8</v>
+      </c>
+      <c r="W43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>8</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>4</v>
+      </c>
+      <c r="I44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44">
+        <v>4</v>
+      </c>
+      <c r="L44">
+        <v>4</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="N44">
+        <v>3</v>
+      </c>
+      <c r="O44">
+        <v>2</v>
+      </c>
+      <c r="P44">
+        <v>4</v>
+      </c>
+      <c r="Q44">
+        <v>4</v>
+      </c>
+      <c r="T44">
+        <v>4</v>
+      </c>
+      <c r="U44">
+        <v>2</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>9</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>3</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>4</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
+      <c r="P45">
+        <v>4</v>
+      </c>
+      <c r="Q45">
+        <v>4</v>
+      </c>
+      <c r="T45">
+        <v>4</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45">
+        <v>2</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>10</v>
+      </c>
+      <c r="B46">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46">
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>6</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46">
+        <v>6</v>
+      </c>
+      <c r="L46">
+        <v>6</v>
+      </c>
+      <c r="M46">
+        <v>6</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>5</v>
+      </c>
+      <c r="P46">
+        <v>6</v>
+      </c>
+      <c r="Q46">
+        <v>6</v>
+      </c>
+      <c r="T46">
+        <v>6</v>
+      </c>
+      <c r="U46">
+        <v>4</v>
+      </c>
+      <c r="V46">
+        <v>6</v>
+      </c>
+      <c r="W46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>11</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <v>4</v>
+      </c>
+      <c r="I47">
+        <v>4</v>
+      </c>
+      <c r="J47">
+        <v>4</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="L47">
+        <v>4</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>4</v>
+      </c>
+      <c r="P47">
+        <v>4</v>
+      </c>
+      <c r="Q47">
+        <v>4</v>
+      </c>
+      <c r="T47">
+        <v>4</v>
+      </c>
+      <c r="U47">
+        <v>4</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36">
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>4</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
+      </c>
+      <c r="J48">
+        <v>4</v>
+      </c>
+      <c r="K48">
+        <v>4</v>
+      </c>
+      <c r="L48">
+        <v>4</v>
+      </c>
+      <c r="M48">
+        <v>4</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
         <v>2</v>
       </c>
-      <c r="B36">
+      <c r="P48">
+        <v>4</v>
+      </c>
+      <c r="Q48">
+        <v>4</v>
+      </c>
+      <c r="T48">
+        <v>4</v>
+      </c>
+      <c r="U48">
+        <v>4</v>
+      </c>
+      <c r="V48">
+        <v>3</v>
+      </c>
+      <c r="W48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>13</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49">
+        <v>6</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <v>6</v>
+      </c>
+      <c r="I49">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>5</v>
+      </c>
+      <c r="K49">
+        <v>6</v>
+      </c>
+      <c r="L49">
+        <v>6</v>
+      </c>
+      <c r="M49">
+        <v>6</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>5</v>
+      </c>
+      <c r="P49">
+        <v>6</v>
+      </c>
+      <c r="Q49">
+        <v>6</v>
+      </c>
+      <c r="T49">
+        <v>6</v>
+      </c>
+      <c r="U49">
+        <v>6</v>
+      </c>
+      <c r="V49">
+        <v>6</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>14</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>5</v>
+      </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
+      <c r="K50">
+        <v>5</v>
+      </c>
+      <c r="L50">
+        <v>5</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>4</v>
+      </c>
+      <c r="P50">
+        <v>5</v>
+      </c>
+      <c r="Q50">
+        <v>5</v>
+      </c>
+      <c r="T50">
+        <v>5</v>
+      </c>
+      <c r="U50">
+        <v>3</v>
+      </c>
+      <c r="V50">
+        <v>5</v>
+      </c>
+      <c r="W50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>15</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51">
+        <v>4</v>
+      </c>
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51">
+        <v>4</v>
+      </c>
+      <c r="L51">
+        <v>4</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51">
+        <v>4</v>
+      </c>
+      <c r="Q51">
+        <v>4</v>
+      </c>
+      <c r="T51">
+        <v>4</v>
+      </c>
+      <c r="U51">
+        <v>3</v>
+      </c>
+      <c r="V51">
+        <v>4</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>3</v>
-      </c>
-      <c r="B37">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>4</v>
-      </c>
-      <c r="B38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>5</v>
-      </c>
-      <c r="B39">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>6</v>
-      </c>
-      <c r="B40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>7</v>
-      </c>
-      <c r="B41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>8</v>
-      </c>
-      <c r="B42">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>9</v>
-      </c>
-      <c r="B43">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>10</v>
-      </c>
-      <c r="B44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>11</v>
-      </c>
-      <c r="B45">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>12</v>
-      </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>13</v>
-      </c>
-      <c r="B47">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>14</v>
-      </c>
-      <c r="B48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>15</v>
-      </c>
-      <c r="B49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B53">
-        <f>SUM(B35:B52)</f>
+      <c r="B55">
+        <f>SUM(B37:B54)</f>
         <v>100</v>
+      </c>
+      <c r="C55">
+        <f t="shared" ref="C55:W55" si="0">SUM(C37:C54)</f>
+        <v>93</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="0"/>
+        <v>97</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L55">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="V55">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F451E5D-B505-6B4F-9CA7-CD10B19FF4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEAD0E3-055B-5C4A-92E4-F1596FD5665D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="4100" windowWidth="28680" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23360" yWindow="4740" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">(Sheet1!$F$5:$F$17,Sheet1!$F$19:$F$24,Sheet1!$F$27:$F$28)</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$R$5:$R$10</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$R$8</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$R$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>First name</t>
   </si>
@@ -336,6 +342,9 @@
   </si>
   <si>
     <t>Stdev</t>
+  </si>
+  <si>
+    <t>Grade</t>
   </si>
 </sst>
 </file>
@@ -712,13 +721,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:W55"/>
+  <dimension ref="A2:W69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>0.16</v>
+      </c>
+      <c r="G2">
+        <v>0.16</v>
+      </c>
+      <c r="H2">
+        <v>0.16</v>
+      </c>
+      <c r="I2">
+        <v>0.16</v>
+      </c>
+      <c r="J2">
+        <v>0.16</v>
+      </c>
+      <c r="K2">
+        <v>0.05</v>
+      </c>
+      <c r="L2">
+        <v>0.05</v>
+      </c>
+      <c r="M2">
+        <v>0.1</v>
+      </c>
+      <c r="N2">
+        <f>SUM(F2:M2)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>71</v>
       </c>
@@ -747,7 +789,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -761,7 +803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -777,8 +819,12 @@
       <c r="F5">
         <v>93</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O5">
+        <f>(F5+F$32)*F$2/(100*$F$2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -794,8 +840,12 @@
       <c r="F6">
         <v>81</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O6">
+        <f t="shared" ref="O6:O24" si="0">(F6+F$32)*F$2/(100*$F$2)</f>
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -811,8 +861,12 @@
       <c r="F7">
         <v>97</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -828,8 +882,12 @@
       <c r="F8">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -845,8 +903,12 @@
       <c r="F9">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>0.83000000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -862,8 +924,12 @@
       <c r="F10">
         <v>94</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
@@ -879,8 +945,12 @@
       <c r="F11">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
@@ -896,8 +966,12 @@
       <c r="F12">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O12">
+        <f t="shared" si="0"/>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
@@ -913,8 +987,12 @@
       <c r="F13">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O13">
+        <f t="shared" si="0"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -930,8 +1008,12 @@
       <c r="F14">
         <v>93</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -947,8 +1029,12 @@
       <c r="F15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -964,8 +1050,12 @@
       <c r="F16">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -981,8 +1071,12 @@
       <c r="F17">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>14</v>
       </c>
@@ -998,8 +1092,12 @@
       <c r="F19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O19">
+        <f t="shared" si="0"/>
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1015,8 +1113,12 @@
       <c r="F20">
         <v>94</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O20">
+        <f t="shared" si="0"/>
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1029,8 +1131,15 @@
       <c r="D21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <v>70</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="0"/>
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1043,8 +1152,15 @@
       <c r="D22" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F22">
+        <v>90</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="0"/>
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1060,8 +1176,12 @@
       <c r="F23">
         <v>86</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O23">
+        <f t="shared" si="0"/>
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1077,13 +1197,42 @@
       <c r="F24">
         <v>78</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O24">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B26" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>0.2</v>
+      </c>
+      <c r="G26">
+        <v>0.2</v>
+      </c>
+      <c r="H26">
+        <v>0.2</v>
+      </c>
+      <c r="I26">
+        <v>0.2</v>
+      </c>
+      <c r="K26">
+        <v>0.05</v>
+      </c>
+      <c r="L26">
+        <v>0.05</v>
+      </c>
+      <c r="M26">
+        <v>0.1</v>
+      </c>
+      <c r="N26">
+        <f>SUM(F26:M26)</f>
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>20</v>
       </c>
@@ -1099,8 +1248,12 @@
       <c r="F27">
         <v>72</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O27">
+        <f>(F27+F$32)*F$26/(100*$F$26)</f>
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>21</v>
       </c>
@@ -1116,31 +1269,99 @@
       <c r="F28">
         <v>20</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="O28">
+        <f>(F28+F$32)*F$26/(100*$F$26)</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E30" s="1" t="s">
         <v>98</v>
       </c>
       <c r="F30">
-        <f>AVERAGE(F5:F28)</f>
-        <v>83.263157894736835</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+        <f>AVERAGE(F5:F24,F27:F28)</f>
+        <v>82.952380952380949</v>
+      </c>
+      <c r="G30" t="e">
+        <f t="shared" ref="G30:I30" si="1">AVERAGE(G5:G24,G27:G28)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H30" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I30" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J30" t="e">
+        <f t="shared" ref="J30:N30" si="2">AVERAGE(J5:J24,J27:J28)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E31" s="1" t="s">
         <v>100</v>
       </c>
       <c r="F31">
-        <f>STDEV(F5:F28)</f>
-        <v>19.53868557293783</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <f>STDEV(F5:F24,F27:F28)</f>
+        <v>18.829434910469786</v>
+      </c>
+      <c r="G31" t="e">
+        <f t="shared" ref="G31:I31" si="3">STDEV(G5:G24,G27:G28)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J31" t="e">
+        <f t="shared" ref="J31:N31" si="4">STDEV(J5:J24,J27:J28)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
         <v>69</v>
       </c>
@@ -1150,6 +1371,11 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E33" s="1" t="s">
@@ -1157,7 +1383,39 @@
       </c>
       <c r="F33">
         <f>F30+F32</f>
-        <v>90.263157894736835</v>
+        <v>89.952380952380949</v>
+      </c>
+      <c r="G33" t="e">
+        <f t="shared" ref="G33:I33" si="5">G30+G32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H33" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I33" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J33" t="e">
+        <f t="shared" ref="J33" si="6">J30+J32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K33" t="e">
+        <f t="shared" ref="K33" si="7">K30+K32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L33" t="e">
+        <f t="shared" ref="L33" si="8">L30+L32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M33" t="e">
+        <f t="shared" ref="M33" si="9">M30+M32</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" t="e">
+        <f t="shared" ref="N33" si="10">N30+N32</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.2">
@@ -1280,6 +1538,12 @@
       <c r="Q37">
         <v>11</v>
       </c>
+      <c r="R37">
+        <v>6</v>
+      </c>
+      <c r="S37">
+        <v>12</v>
+      </c>
       <c r="T37">
         <v>6</v>
       </c>
@@ -1345,6 +1609,12 @@
       <c r="Q38">
         <v>16</v>
       </c>
+      <c r="R38">
+        <v>14</v>
+      </c>
+      <c r="S38">
+        <v>18</v>
+      </c>
       <c r="T38">
         <v>14</v>
       </c>
@@ -1410,6 +1680,12 @@
       <c r="Q39">
         <v>7</v>
       </c>
+      <c r="R39">
+        <v>7</v>
+      </c>
+      <c r="S39">
+        <v>7</v>
+      </c>
       <c r="T39">
         <v>5</v>
       </c>
@@ -1475,6 +1751,12 @@
       <c r="Q40">
         <v>4</v>
       </c>
+      <c r="R40">
+        <v>4</v>
+      </c>
+      <c r="S40">
+        <v>6</v>
+      </c>
       <c r="T40">
         <v>5</v>
       </c>
@@ -1540,6 +1822,12 @@
       <c r="Q41">
         <v>6</v>
       </c>
+      <c r="R41">
+        <v>6</v>
+      </c>
+      <c r="S41">
+        <v>5</v>
+      </c>
       <c r="T41">
         <v>6</v>
       </c>
@@ -1603,6 +1891,12 @@
         <v>5</v>
       </c>
       <c r="Q42">
+        <v>5</v>
+      </c>
+      <c r="R42">
+        <v>3</v>
+      </c>
+      <c r="S42">
         <v>5</v>
       </c>
       <c r="T42">
@@ -1670,6 +1964,12 @@
       <c r="Q43">
         <v>8</v>
       </c>
+      <c r="R43">
+        <v>5</v>
+      </c>
+      <c r="S43">
+        <v>7</v>
+      </c>
       <c r="T43">
         <v>8</v>
       </c>
@@ -1735,6 +2035,12 @@
       <c r="Q44">
         <v>4</v>
       </c>
+      <c r="R44">
+        <v>3</v>
+      </c>
+      <c r="S44">
+        <v>3</v>
+      </c>
       <c r="T44">
         <v>4</v>
       </c>
@@ -1800,6 +2106,12 @@
       <c r="Q45">
         <v>4</v>
       </c>
+      <c r="R45">
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <v>4</v>
+      </c>
       <c r="T45">
         <v>4</v>
       </c>
@@ -1865,6 +2177,12 @@
       <c r="Q46">
         <v>6</v>
       </c>
+      <c r="R46">
+        <v>6</v>
+      </c>
+      <c r="S46">
+        <v>6</v>
+      </c>
       <c r="T46">
         <v>6</v>
       </c>
@@ -1930,6 +2248,12 @@
       <c r="Q47">
         <v>4</v>
       </c>
+      <c r="R47">
+        <v>3</v>
+      </c>
+      <c r="S47">
+        <v>3</v>
+      </c>
       <c r="T47">
         <v>4</v>
       </c>
@@ -1995,6 +2319,12 @@
       <c r="Q48">
         <v>4</v>
       </c>
+      <c r="R48">
+        <v>2</v>
+      </c>
+      <c r="S48">
+        <v>1</v>
+      </c>
       <c r="T48">
         <v>4</v>
       </c>
@@ -2060,6 +2390,12 @@
       <c r="Q49">
         <v>6</v>
       </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <v>5</v>
+      </c>
       <c r="T49">
         <v>6</v>
       </c>
@@ -2125,6 +2461,12 @@
       <c r="Q50">
         <v>5</v>
       </c>
+      <c r="R50">
+        <v>5</v>
+      </c>
+      <c r="S50">
+        <v>4</v>
+      </c>
       <c r="T50">
         <v>5</v>
       </c>
@@ -2190,6 +2532,12 @@
       <c r="Q51">
         <v>4</v>
       </c>
+      <c r="R51">
+        <v>4</v>
+      </c>
+      <c r="S51">
+        <v>4</v>
+      </c>
       <c r="T51">
         <v>4</v>
       </c>
@@ -2204,111 +2552,369 @@
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A52">
+      <c r="A52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52">
+        <f>SUM(B37:B51)</f>
+        <v>100</v>
+      </c>
+      <c r="C52">
+        <f>SUM(C37:C51)</f>
+        <v>93</v>
+      </c>
+      <c r="D52">
+        <f>SUM(D37:D51)</f>
+        <v>81</v>
+      </c>
+      <c r="E52">
+        <f>SUM(E37:E51)</f>
+        <v>97</v>
+      </c>
+      <c r="F52">
+        <f>SUM(F37:F51)</f>
+        <v>98</v>
+      </c>
+      <c r="G52">
+        <f>SUM(G37:G51)</f>
+        <v>76</v>
+      </c>
+      <c r="H52">
+        <f>SUM(H37:H51)</f>
+        <v>94</v>
+      </c>
+      <c r="I52">
+        <f>SUM(I37:I51)</f>
+        <v>94</v>
+      </c>
+      <c r="J52">
+        <f>SUM(J37:J51)</f>
+        <v>85</v>
+      </c>
+      <c r="K52">
+        <f>SUM(K37:K51)</f>
+        <v>92</v>
+      </c>
+      <c r="L52">
+        <f>SUM(L37:L51)</f>
+        <v>93</v>
+      </c>
+      <c r="M52">
+        <f>SUM(M37:M51)</f>
+        <v>100</v>
+      </c>
+      <c r="N52">
+        <f>SUM(N37:N51)</f>
+        <v>51</v>
+      </c>
+      <c r="O52">
+        <f>SUM(O37:O51)</f>
+        <v>78</v>
+      </c>
+      <c r="P52">
+        <f>SUM(P37:P51)</f>
+        <v>100</v>
+      </c>
+      <c r="Q52">
+        <f>SUM(Q37:Q51)</f>
+        <v>94</v>
+      </c>
+      <c r="R52">
+        <f>SUM(R37:R51)</f>
+        <v>70</v>
+      </c>
+      <c r="S52">
+        <f>SUM(S37:S51)</f>
+        <v>90</v>
+      </c>
+      <c r="T52">
+        <f>SUM(T37:T51)</f>
+        <v>86</v>
+      </c>
+      <c r="U52">
+        <f>SUM(U37:U51)</f>
+        <v>78</v>
+      </c>
+      <c r="V52">
+        <f>SUM(V37:V51)</f>
+        <v>72</v>
+      </c>
+      <c r="W52">
+        <f>SUM(W37:W51)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>2</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57">
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="B59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>6</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>7</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>8</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>9</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>10</v>
+      </c>
+      <c r="B64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>11</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>12</v>
+      </c>
+      <c r="B66">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>13</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>14</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B55">
-        <f>SUM(B37:B54)</f>
+      <c r="B69">
+        <f>SUM(B55:B68)</f>
         <v>100</v>
       </c>
-      <c r="C55">
-        <f t="shared" ref="C55:W55" si="0">SUM(C37:C54)</f>
-        <v>93</v>
-      </c>
-      <c r="D55">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="E55">
-        <f t="shared" si="0"/>
-        <v>97</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="H55">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="I55">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="J55">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="K55">
-        <f t="shared" si="0"/>
-        <v>92</v>
-      </c>
-      <c r="L55">
-        <f t="shared" si="0"/>
-        <v>93</v>
-      </c>
-      <c r="M55">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="O55">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="P55">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="Q55">
-        <f t="shared" si="0"/>
-        <v>94</v>
-      </c>
-      <c r="R55">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <f t="shared" si="0"/>
-        <v>86</v>
-      </c>
-      <c r="U55">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="V55">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="W55">
-        <f t="shared" si="0"/>
-        <v>20</v>
+      <c r="C69">
+        <f>SUM(C55:C68)</f>
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <f>SUM(D55:D68)</f>
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <f>SUM(E55:E68)</f>
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <f>SUM(F55:F68)</f>
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <f>SUM(G55:G68)</f>
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <f>SUM(H55:H68)</f>
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <f>SUM(I55:I68)</f>
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <f>SUM(J55:J68)</f>
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <f>SUM(K55:K68)</f>
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <f>SUM(L55:L68)</f>
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <f>SUM(M55:M68)</f>
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <f>SUM(N55:N68)</f>
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <f>SUM(O55:O68)</f>
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <f>SUM(P55:P68)</f>
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <f>SUM(Q55:Q68)</f>
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <f>SUM(R55:R68)</f>
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <f>SUM(S55:S68)</f>
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <f>SUM(T55:T68)</f>
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <f>SUM(U55:U68)</f>
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <f>SUM(V55:V68)</f>
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <f>SUM(W55:W68)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -5,22 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEAD0E3-055B-5C4A-92E4-F1596FD5665D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE67D28-BD46-A341-9A89-E654951FFF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23360" yWindow="4740" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="760" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">(Sheet1!$F$5:$F$17,Sheet1!$F$19:$F$24,Sheet1!$F$27:$F$28)</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$R$5:$R$10</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$R$8</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$R$8</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2556,91 +2550,91 @@
         <v>76</v>
       </c>
       <c r="B52">
-        <f>SUM(B37:B51)</f>
+        <f t="shared" ref="B52:W52" si="11">SUM(B37:B51)</f>
         <v>100</v>
       </c>
       <c r="C52">
-        <f>SUM(C37:C51)</f>
+        <f t="shared" si="11"/>
         <v>93</v>
       </c>
       <c r="D52">
-        <f>SUM(D37:D51)</f>
+        <f t="shared" si="11"/>
         <v>81</v>
       </c>
       <c r="E52">
-        <f>SUM(E37:E51)</f>
+        <f t="shared" si="11"/>
         <v>97</v>
       </c>
       <c r="F52">
-        <f>SUM(F37:F51)</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="G52">
-        <f>SUM(G37:G51)</f>
+        <f t="shared" si="11"/>
         <v>76</v>
       </c>
       <c r="H52">
-        <f>SUM(H37:H51)</f>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="I52">
-        <f>SUM(I37:I51)</f>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="J52">
-        <f>SUM(J37:J51)</f>
+        <f t="shared" si="11"/>
         <v>85</v>
       </c>
       <c r="K52">
-        <f>SUM(K37:K51)</f>
+        <f t="shared" si="11"/>
         <v>92</v>
       </c>
       <c r="L52">
-        <f>SUM(L37:L51)</f>
+        <f t="shared" si="11"/>
         <v>93</v>
       </c>
       <c r="M52">
-        <f>SUM(M37:M51)</f>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
       <c r="N52">
-        <f>SUM(N37:N51)</f>
+        <f t="shared" si="11"/>
         <v>51</v>
       </c>
       <c r="O52">
-        <f>SUM(O37:O51)</f>
+        <f t="shared" si="11"/>
         <v>78</v>
       </c>
       <c r="P52">
-        <f>SUM(P37:P51)</f>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
       <c r="Q52">
-        <f>SUM(Q37:Q51)</f>
+        <f t="shared" si="11"/>
         <v>94</v>
       </c>
       <c r="R52">
-        <f>SUM(R37:R51)</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="S52">
-        <f>SUM(S37:S51)</f>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
       <c r="T52">
-        <f>SUM(T37:T51)</f>
+        <f t="shared" si="11"/>
         <v>86</v>
       </c>
       <c r="U52">
-        <f>SUM(U37:U51)</f>
+        <f t="shared" si="11"/>
         <v>78</v>
       </c>
       <c r="V52">
-        <f>SUM(V37:V51)</f>
+        <f t="shared" si="11"/>
         <v>72</v>
       </c>
       <c r="W52">
-        <f>SUM(W37:W51)</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
     </row>
@@ -2725,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="B56">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.2">
@@ -2741,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="B58">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.2">
@@ -2749,7 +2743,7 @@
         <v>5</v>
       </c>
       <c r="B59">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.2">
@@ -2757,7 +2751,7 @@
         <v>6</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.2">
@@ -2781,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.2">
@@ -2789,7 +2783,7 @@
         <v>10</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.2">
@@ -2805,7 +2799,7 @@
         <v>12</v>
       </c>
       <c r="B66">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.2">
@@ -2813,7 +2807,7 @@
         <v>13</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.2">
@@ -2821,7 +2815,7 @@
         <v>14</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.2">
@@ -2829,91 +2823,91 @@
         <v>76</v>
       </c>
       <c r="B69">
-        <f>SUM(B55:B68)</f>
+        <f t="shared" ref="B69:W69" si="12">SUM(B55:B68)</f>
         <v>100</v>
       </c>
       <c r="C69">
-        <f>SUM(C55:C68)</f>
+        <f t="shared" ref="C69" si="13">SUM(C55:C68)</f>
         <v>0</v>
       </c>
       <c r="D69">
-        <f>SUM(D55:D68)</f>
+        <f t="shared" ref="D69" si="14">SUM(D55:D68)</f>
         <v>0</v>
       </c>
       <c r="E69">
-        <f>SUM(E55:E68)</f>
+        <f t="shared" ref="E69" si="15">SUM(E55:E68)</f>
         <v>0</v>
       </c>
       <c r="F69">
-        <f>SUM(F55:F68)</f>
+        <f t="shared" ref="F69" si="16">SUM(F55:F68)</f>
         <v>0</v>
       </c>
       <c r="G69">
-        <f>SUM(G55:G68)</f>
+        <f t="shared" ref="G69" si="17">SUM(G55:G68)</f>
         <v>0</v>
       </c>
       <c r="H69">
-        <f>SUM(H55:H68)</f>
+        <f t="shared" ref="H69" si="18">SUM(H55:H68)</f>
         <v>0</v>
       </c>
       <c r="I69">
-        <f>SUM(I55:I68)</f>
+        <f t="shared" ref="I69" si="19">SUM(I55:I68)</f>
         <v>0</v>
       </c>
       <c r="J69">
-        <f>SUM(J55:J68)</f>
+        <f t="shared" ref="J69" si="20">SUM(J55:J68)</f>
         <v>0</v>
       </c>
       <c r="K69">
-        <f>SUM(K55:K68)</f>
+        <f t="shared" ref="K69" si="21">SUM(K55:K68)</f>
         <v>0</v>
       </c>
       <c r="L69">
-        <f>SUM(L55:L68)</f>
+        <f t="shared" ref="L69" si="22">SUM(L55:L68)</f>
         <v>0</v>
       </c>
       <c r="M69">
-        <f>SUM(M55:M68)</f>
+        <f t="shared" ref="M69" si="23">SUM(M55:M68)</f>
         <v>0</v>
       </c>
       <c r="N69">
-        <f>SUM(N55:N68)</f>
+        <f t="shared" ref="N69" si="24">SUM(N55:N68)</f>
         <v>0</v>
       </c>
       <c r="O69">
-        <f>SUM(O55:O68)</f>
+        <f t="shared" ref="O69" si="25">SUM(O55:O68)</f>
         <v>0</v>
       </c>
       <c r="P69">
-        <f>SUM(P55:P68)</f>
+        <f t="shared" ref="P69" si="26">SUM(P55:P68)</f>
         <v>0</v>
       </c>
       <c r="Q69">
-        <f>SUM(Q55:Q68)</f>
+        <f t="shared" ref="Q69" si="27">SUM(Q55:Q68)</f>
         <v>0</v>
       </c>
       <c r="R69">
-        <f>SUM(R55:R68)</f>
+        <f t="shared" ref="R69" si="28">SUM(R55:R68)</f>
         <v>0</v>
       </c>
       <c r="S69">
-        <f>SUM(S55:S68)</f>
+        <f t="shared" ref="S69" si="29">SUM(S55:S68)</f>
         <v>0</v>
       </c>
       <c r="T69">
-        <f>SUM(T55:T68)</f>
+        <f t="shared" ref="T69" si="30">SUM(T55:T68)</f>
         <v>0</v>
       </c>
       <c r="U69">
-        <f>SUM(U55:U68)</f>
+        <f t="shared" ref="U69" si="31">SUM(U55:U68)</f>
         <v>0</v>
       </c>
       <c r="V69">
-        <f>SUM(V55:V68)</f>
+        <f t="shared" ref="V69" si="32">SUM(V55:V68)</f>
         <v>0</v>
       </c>
       <c r="W69">
-        <f>SUM(W55:W68)</f>
+        <f t="shared" ref="W69" si="33">SUM(W55:W68)</f>
         <v>0</v>
       </c>
     </row>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE67D28-BD46-A341-9A89-E654951FFF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB762813-E62C-B843-BDE2-5B0026104145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="760" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20700" yWindow="4580" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -345,6 +345,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -378,9 +381,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,46 +719,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W69"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="H1">
+        <v>0.16</v>
+      </c>
+      <c r="I1">
+        <v>0.16</v>
+      </c>
+      <c r="J1">
+        <v>0.16</v>
+      </c>
+      <c r="K1">
+        <v>0.05</v>
+      </c>
+      <c r="L1">
+        <v>0.05</v>
+      </c>
+      <c r="M1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F2">
         <v>0.16</v>
       </c>
       <c r="G2">
         <v>0.16</v>
       </c>
-      <c r="H2">
-        <v>0.16</v>
-      </c>
-      <c r="I2">
-        <v>0.16</v>
-      </c>
-      <c r="J2">
-        <v>0.16</v>
-      </c>
       <c r="K2">
         <v>0.05</v>
       </c>
-      <c r="L2">
-        <v>0.05</v>
-      </c>
-      <c r="M2">
-        <v>0.1</v>
-      </c>
       <c r="N2">
         <f>SUM(F2:M2)</f>
-        <v>1.0000000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>71</v>
       </c>
@@ -783,7 +792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -797,7 +806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -813,12 +822,19 @@
       <c r="F5">
         <v>93</v>
       </c>
+      <c r="G5">
+        <v>93</v>
+      </c>
       <c r="O5">
-        <f>(F5+F$32)*F$2/(100*$F$2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+        <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
+        <v>31.68</v>
+      </c>
+      <c r="P5" s="2">
+        <f>O5/$N$2</f>
+        <v>85.621621621621628</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -834,12 +850,22 @@
       <c r="F6">
         <v>81</v>
       </c>
+      <c r="G6">
+        <v>87</v>
+      </c>
+      <c r="K6">
+        <v>88</v>
+      </c>
       <c r="O6">
-        <f t="shared" ref="O6:O24" si="0">(F6+F$32)*F$2/(100*$F$2)</f>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="O6:O17" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
+        <v>33.200000000000003</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" ref="P6:P24" si="1">O6/$N$2</f>
+        <v>89.72972972972974</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -855,12 +881,19 @@
       <c r="F7">
         <v>97</v>
       </c>
+      <c r="G7">
+        <v>98</v>
+      </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+        <v>33.120000000000005</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="1"/>
+        <v>89.51351351351353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -876,12 +909,19 @@
       <c r="F8">
         <v>98</v>
       </c>
+      <c r="G8">
+        <v>99</v>
+      </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+        <v>33.44</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="1"/>
+        <v>90.378378378378372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -897,12 +937,19 @@
       <c r="F9">
         <v>76</v>
       </c>
+      <c r="G9">
+        <v>86</v>
+      </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>0.83000000000000007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+        <v>27.840000000000003</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="1"/>
+        <v>75.243243243243256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -918,12 +965,22 @@
       <c r="F10">
         <v>94</v>
       </c>
+      <c r="G10">
+        <v>90</v>
+      </c>
+      <c r="K10">
+        <v>98</v>
+      </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+        <v>36.26</v>
+      </c>
+      <c r="P10" s="2">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>7</v>
       </c>
@@ -939,12 +996,22 @@
       <c r="F11">
         <v>94</v>
       </c>
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>91</v>
+      </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+        <v>37.51</v>
+      </c>
+      <c r="P11" s="2">
+        <f t="shared" si="1"/>
+        <v>101.37837837837837</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
@@ -960,12 +1027,19 @@
       <c r="F12">
         <v>85</v>
       </c>
+      <c r="G12">
+        <v>85</v>
+      </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+        <v>29.12</v>
+      </c>
+      <c r="P12" s="2">
+        <f t="shared" si="1"/>
+        <v>78.702702702702709</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9</v>
       </c>
@@ -981,12 +1055,19 @@
       <c r="F13">
         <v>92</v>
       </c>
+      <c r="G13">
+        <v>95</v>
+      </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+        <v>31.84</v>
+      </c>
+      <c r="P13" s="2">
+        <f t="shared" si="1"/>
+        <v>86.054054054054049</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1002,12 +1083,22 @@
       <c r="F14">
         <v>93</v>
       </c>
+      <c r="G14">
+        <v>94</v>
+      </c>
+      <c r="K14">
+        <v>98</v>
+      </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+        <v>36.74</v>
+      </c>
+      <c r="P14" s="2">
+        <f t="shared" si="1"/>
+        <v>99.297297297297305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -1023,12 +1114,19 @@
       <c r="F15">
         <v>100</v>
       </c>
+      <c r="G15">
+        <v>90</v>
+      </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+        <v>32.32</v>
+      </c>
+      <c r="P15" s="2">
+        <f t="shared" si="1"/>
+        <v>87.351351351351354</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -1044,12 +1142,22 @@
       <c r="F16">
         <v>51</v>
       </c>
+      <c r="G16">
+        <v>72</v>
+      </c>
+      <c r="K16">
+        <v>85</v>
+      </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>25.85</v>
+      </c>
+      <c r="P16" s="2">
+        <f t="shared" si="1"/>
+        <v>69.86486486486487</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1065,12 +1173,22 @@
       <c r="F17">
         <v>78</v>
       </c>
+      <c r="G17">
+        <v>88</v>
+      </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+        <v>28.48</v>
+      </c>
+      <c r="P17" s="2">
+        <f t="shared" si="1"/>
+        <v>76.972972972972968</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1086,12 +1204,22 @@
       <c r="F19">
         <v>100</v>
       </c>
+      <c r="G19">
+        <v>96</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
       <c r="O19">
-        <f t="shared" si="0"/>
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="O19" si="2">(F19+F$33)*F$2+G$2*(G19+G$33)+H$2*(H19+H$33)+I$2*(I19+I$33)+J$2*(J19+J$33)+K$2*(K19+K$33)+L$2*(L19+L$33)+M$2*(M19+M$33)</f>
+        <v>38.28</v>
+      </c>
+      <c r="P19" s="2">
+        <f t="shared" si="1"/>
+        <v>103.45945945945947</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1107,12 +1235,19 @@
       <c r="F20">
         <v>94</v>
       </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
       <c r="O20">
-        <f t="shared" si="0"/>
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <f t="shared" ref="O20:O24" si="3">(F20+F$33)*F$2+G$2*(G20+G$33)+H$2*(H20+H$33)+I$2*(I20+I$33)+J$2*(J20+J$33)+K$2*(K20+K$33)+L$2*(L20+L$33)+M$2*(M20+M$33)</f>
+        <v>32.96</v>
+      </c>
+      <c r="P20" s="2">
+        <f t="shared" si="1"/>
+        <v>89.081081081081081</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1128,12 +1263,19 @@
       <c r="F21">
         <v>70</v>
       </c>
+      <c r="G21">
+        <v>65</v>
+      </c>
       <c r="O21">
-        <f t="shared" si="0"/>
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>23.520000000000003</v>
+      </c>
+      <c r="P21" s="2">
+        <f t="shared" si="1"/>
+        <v>63.567567567567579</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1149,12 +1291,19 @@
       <c r="F22">
         <v>90</v>
       </c>
+      <c r="G22">
+        <v>81</v>
+      </c>
       <c r="O22">
-        <f t="shared" si="0"/>
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>29.28</v>
+      </c>
+      <c r="P22" s="2">
+        <f t="shared" si="1"/>
+        <v>79.135135135135144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1170,12 +1319,22 @@
       <c r="F23">
         <v>86</v>
       </c>
+      <c r="G23">
+        <v>93</v>
+      </c>
+      <c r="K23">
+        <v>94</v>
+      </c>
       <c r="O23">
-        <f t="shared" si="0"/>
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>35.260000000000005</v>
+      </c>
+      <c r="P23" s="2">
+        <f t="shared" si="1"/>
+        <v>95.297297297297305</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1191,21 +1350,22 @@
       <c r="F24">
         <v>78</v>
       </c>
+      <c r="G24">
+        <v>81</v>
+      </c>
       <c r="O24">
-        <f t="shared" si="0"/>
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26">
-        <v>0.2</v>
-      </c>
-      <c r="G26">
-        <v>0.2</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>27.36</v>
+      </c>
+      <c r="P24" s="2">
+        <f t="shared" si="1"/>
+        <v>73.945945945945951</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="H26">
         <v>0.2</v>
       </c>
@@ -1221,552 +1381,516 @@
       <c r="M26">
         <v>0.1</v>
       </c>
-      <c r="N26">
-        <f>SUM(F26:M26)</f>
-        <v>1.0000000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27">
+        <v>0.2</v>
+      </c>
+      <c r="G27">
+        <v>0.2</v>
+      </c>
+      <c r="K27">
+        <v>0.05</v>
+      </c>
+      <c r="N27">
+        <f>SUM(F27:M27)</f>
+        <v>0.45</v>
+      </c>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>20</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>41</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>42</v>
       </c>
-      <c r="F27">
+      <c r="F28">
         <v>72</v>
       </c>
-      <c r="O27">
-        <f>(F27+F$32)*F$26/(100*$F$26)</f>
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="G28">
+        <v>86</v>
+      </c>
+      <c r="K28">
+        <v>75</v>
+      </c>
+      <c r="O28">
+        <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
+        <v>37.75</v>
+      </c>
+      <c r="P28" s="2">
+        <f>O28/$N$27</f>
+        <v>83.888888888888886</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>21</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F28">
+      <c r="F29">
         <v>20</v>
       </c>
-      <c r="O28">
-        <f>(F28+F$32)*F$26/(100*$F$26)</f>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="E30" s="1" t="s">
+      <c r="G29">
+        <v>17</v>
+      </c>
+      <c r="O29">
+        <f>(F29+F$33)*F$27+G$27*(G29+G$33)+H$27*(H29+H$33)+I$27*(I29+I$33)+J$27*(J29+J$33)+K$27*(K29+K$33)+L$27*(L29+L$33)+M$27*(M29+M$33)</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="P29" s="2">
+        <f>O29/$N$27</f>
+        <v>21.777777777777779</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="E31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F30">
-        <f>AVERAGE(F5:F24,F27:F28)</f>
+      <c r="F31">
+        <f>AVERAGE(F5:F24,F28:F29)</f>
         <v>82.952380952380949</v>
       </c>
-      <c r="G30" t="e">
-        <f t="shared" ref="G30:I30" si="1">AVERAGE(G5:G24,G27:G28)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H30" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I30" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J30" t="e">
-        <f t="shared" ref="J30:N30" si="2">AVERAGE(J5:J24,J27:J28)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L30" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="E31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F31">
-        <f>STDEV(F5:F24,F27:F28)</f>
-        <v>18.829434910469786</v>
-      </c>
-      <c r="G31" t="e">
-        <f t="shared" ref="G31:I31" si="3">STDEV(G5:G24,G27:G28)</f>
-        <v>#DIV/0!</v>
+      <c r="G31">
+        <f t="shared" ref="G31:I31" si="4">AVERAGE(G5:G24,G28:G29)</f>
+        <v>85.523809523809518</v>
       </c>
       <c r="H31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J31" t="e">
-        <f t="shared" ref="J31:N31" si="4">STDEV(J5:J24,J27:J28)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L31" t="e">
+      <c r="I31" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="J31" t="e">
+        <f t="shared" ref="J31:N31" si="5">AVERAGE(J5:J24,J28:J29)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="5"/>
+        <v>91.125</v>
+      </c>
+      <c r="L31" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="M31" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N31" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="1">
-        <v>7</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="F32">
+        <f>STDEV(F5:F24,F28:F29)</f>
+        <v>18.829434910469786</v>
+      </c>
+      <c r="G32">
+        <f t="shared" ref="G32:I32" si="6">STDEV(G5:G24,G28:G29)</f>
+        <v>18.06825682687473</v>
+      </c>
+      <c r="H32" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I32" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J32" t="e">
+        <f t="shared" ref="J32:N32" si="7">STDEV(J5:J24,J28:J29)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="7"/>
+        <v>8.3569902305965211</v>
+      </c>
+      <c r="L32" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M32" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N32" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="1">
+        <v>7</v>
+      </c>
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="E34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F33">
-        <f>F30+F32</f>
+      <c r="F34">
+        <f>F31+F33</f>
         <v>89.952380952380949</v>
       </c>
-      <c r="G33" t="e">
-        <f t="shared" ref="G33:I33" si="5">G30+G32</f>
+      <c r="G34">
+        <f t="shared" ref="G34:I34" si="8">G31+G33</f>
+        <v>90.523809523809518</v>
+      </c>
+      <c r="H34" t="e">
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H33" t="e">
-        <f t="shared" si="5"/>
+      <c r="I34" t="e">
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I33" t="e">
-        <f t="shared" si="5"/>
+      <c r="J34" t="e">
+        <f t="shared" ref="J34" si="9">J31+J33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J33" t="e">
-        <f t="shared" ref="J33" si="6">J30+J32</f>
+      <c r="K34">
+        <f t="shared" ref="K34" si="10">K31+K33</f>
+        <v>91.125</v>
+      </c>
+      <c r="L34" t="e">
+        <f t="shared" ref="L34" si="11">L31+L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K33" t="e">
-        <f t="shared" ref="K33" si="7">K30+K32</f>
+      <c r="M34" t="e">
+        <f t="shared" ref="M34" si="12">M31+M33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L33" t="e">
-        <f t="shared" ref="L33" si="8">L30+L32</f>
+      <c r="N34" t="e">
+        <f t="shared" ref="N34" si="13">N31+N33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M33" t="e">
-        <f t="shared" ref="M33" si="9">M30+M32</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N33" t="e">
-        <f t="shared" ref="N33" si="10">N30+N32</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="M37" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="N37" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="O37" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="P37" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q36" s="1" t="s">
+      <c r="Q37" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R36" s="1" t="s">
+      <c r="R37" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S36" s="1" t="s">
+      <c r="S37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T36" s="1" t="s">
+      <c r="T37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U36" s="1" t="s">
+      <c r="U37" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="V36" s="1" t="s">
+      <c r="V37" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W36" s="1" t="s">
+      <c r="W37" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37">
-        <v>12</v>
-      </c>
-      <c r="C37">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>9</v>
-      </c>
-      <c r="E37">
-        <v>10</v>
-      </c>
-      <c r="F37">
-        <v>11</v>
-      </c>
-      <c r="G37">
-        <v>11</v>
-      </c>
-      <c r="H37">
-        <v>12</v>
-      </c>
-      <c r="I37">
-        <v>12</v>
-      </c>
-      <c r="J37">
-        <v>10</v>
-      </c>
-      <c r="K37">
-        <v>12</v>
-      </c>
-      <c r="L37">
-        <v>11</v>
-      </c>
-      <c r="M37">
-        <v>12</v>
-      </c>
-      <c r="N37">
-        <v>11</v>
-      </c>
-      <c r="O37">
-        <v>7</v>
-      </c>
-      <c r="P37">
-        <v>12</v>
-      </c>
-      <c r="Q37">
-        <v>11</v>
-      </c>
-      <c r="R37">
-        <v>6</v>
-      </c>
-      <c r="S37">
-        <v>12</v>
-      </c>
-      <c r="T37">
-        <v>6</v>
-      </c>
-      <c r="U37">
-        <v>11</v>
-      </c>
-      <c r="V37">
-        <v>9</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C38">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F38">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I38">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J38">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L38">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M38">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N38">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="O38">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="P38">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q38">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R38">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="S38">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T38">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E39">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F39">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H39">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K39">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M39">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N39">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O39">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q39">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R39">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S39">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T39">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C40">
         <v>6</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40">
         <v>6</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O40">
         <v>6</v>
       </c>
       <c r="P40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>5</v>
       </c>
       <c r="U40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B41">
         <v>6</v>
@@ -1775,7 +1899,7 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -1784,194 +1908,194 @@
         <v>6</v>
       </c>
       <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>6</v>
+      </c>
+      <c r="I41">
+        <v>6</v>
+      </c>
+      <c r="J41">
+        <v>6</v>
+      </c>
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="L41">
+        <v>6</v>
+      </c>
+      <c r="M41">
+        <v>6</v>
+      </c>
+      <c r="N41">
+        <v>4</v>
+      </c>
+      <c r="O41">
+        <v>6</v>
+      </c>
+      <c r="P41">
+        <v>6</v>
+      </c>
+      <c r="Q41">
+        <v>4</v>
+      </c>
+      <c r="R41">
+        <v>4</v>
+      </c>
+      <c r="S41">
+        <v>6</v>
+      </c>
+      <c r="T41">
+        <v>5</v>
+      </c>
+      <c r="U41">
+        <v>6</v>
+      </c>
+      <c r="V41">
+        <v>6</v>
+      </c>
+      <c r="W41">
         <v>1</v>
-      </c>
-      <c r="H41">
-        <v>5</v>
-      </c>
-      <c r="I41">
-        <v>6</v>
-      </c>
-      <c r="J41">
-        <v>5</v>
-      </c>
-      <c r="K41">
-        <v>6</v>
-      </c>
-      <c r="L41">
-        <v>5</v>
-      </c>
-      <c r="M41">
-        <v>6</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>5</v>
-      </c>
-      <c r="P41">
-        <v>6</v>
-      </c>
-      <c r="Q41">
-        <v>6</v>
-      </c>
-      <c r="R41">
-        <v>6</v>
-      </c>
-      <c r="S41">
-        <v>5</v>
-      </c>
-      <c r="T41">
-        <v>6</v>
-      </c>
-      <c r="U41">
-        <v>6</v>
-      </c>
-      <c r="V41">
-        <v>6</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H42">
         <v>5</v>
       </c>
       <c r="I42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>5</v>
       </c>
       <c r="M42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S42">
         <v>5</v>
       </c>
       <c r="T42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J43">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N43">
         <v>4</v>
       </c>
       <c r="O43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="W43">
         <v>1</v>
@@ -1979,78 +2103,78 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G44">
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>8</v>
+      </c>
+      <c r="I44">
+        <v>8</v>
+      </c>
+      <c r="J44">
+        <v>8</v>
+      </c>
+      <c r="K44">
+        <v>7</v>
+      </c>
+      <c r="L44">
+        <v>8</v>
+      </c>
+      <c r="M44">
+        <v>8</v>
+      </c>
+      <c r="N44">
+        <v>4</v>
+      </c>
+      <c r="O44">
+        <v>5</v>
+      </c>
+      <c r="P44">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>8</v>
+      </c>
+      <c r="R44">
+        <v>5</v>
+      </c>
+      <c r="S44">
+        <v>7</v>
+      </c>
+      <c r="T44">
+        <v>8</v>
+      </c>
+      <c r="U44">
+        <v>6</v>
+      </c>
+      <c r="V44">
+        <v>8</v>
+      </c>
+      <c r="W44">
         <v>1</v>
-      </c>
-      <c r="H44">
-        <v>4</v>
-      </c>
-      <c r="I44">
-        <v>3</v>
-      </c>
-      <c r="J44">
-        <v>3</v>
-      </c>
-      <c r="K44">
-        <v>4</v>
-      </c>
-      <c r="L44">
-        <v>4</v>
-      </c>
-      <c r="M44">
-        <v>4</v>
-      </c>
-      <c r="N44">
-        <v>3</v>
-      </c>
-      <c r="O44">
-        <v>2</v>
-      </c>
-      <c r="P44">
-        <v>4</v>
-      </c>
-      <c r="Q44">
-        <v>4</v>
-      </c>
-      <c r="R44">
-        <v>3</v>
-      </c>
-      <c r="S44">
-        <v>3</v>
-      </c>
-      <c r="T44">
-        <v>4</v>
-      </c>
-      <c r="U44">
-        <v>2</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -2059,61 +2183,61 @@
         <v>4</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45">
         <v>3</v>
       </c>
       <c r="K45">
+        <v>4</v>
+      </c>
+      <c r="L45">
+        <v>4</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+      <c r="N45">
+        <v>3</v>
+      </c>
+      <c r="O45">
         <v>2</v>
       </c>
-      <c r="L45">
-        <v>4</v>
-      </c>
-      <c r="M45">
-        <v>4</v>
-      </c>
-      <c r="N45">
+      <c r="P45">
+        <v>4</v>
+      </c>
+      <c r="Q45">
+        <v>4</v>
+      </c>
+      <c r="R45">
+        <v>3</v>
+      </c>
+      <c r="S45">
+        <v>3</v>
+      </c>
+      <c r="T45">
+        <v>4</v>
+      </c>
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="V45">
         <v>0</v>
-      </c>
-      <c r="O45">
-        <v>4</v>
-      </c>
-      <c r="P45">
-        <v>4</v>
-      </c>
-      <c r="Q45">
-        <v>4</v>
-      </c>
-      <c r="R45">
-        <v>1</v>
-      </c>
-      <c r="S45">
-        <v>4</v>
-      </c>
-      <c r="T45">
-        <v>4</v>
-      </c>
-      <c r="U45">
-        <v>1</v>
-      </c>
-      <c r="V45">
-        <v>2</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -2121,155 +2245,155 @@
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N46">
         <v>0</v>
       </c>
       <c r="O46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R46">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G47">
         <v>4</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U47">
         <v>4</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W47">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -2281,7 +2405,7 @@
         <v>4</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48">
         <v>4</v>
@@ -2305,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="O48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P48">
         <v>4</v>
@@ -2314,10 +2438,10 @@
         <v>4</v>
       </c>
       <c r="R48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T48">
         <v>4</v>
@@ -2326,589 +2450,1562 @@
         <v>4</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N49">
         <v>0</v>
       </c>
       <c r="O49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R49">
+        <v>2</v>
+      </c>
+      <c r="S49">
         <v>1</v>
       </c>
-      <c r="S49">
-        <v>5</v>
-      </c>
       <c r="T49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U50">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H51">
         <v>4</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51">
         <v>0</v>
       </c>
       <c r="O51">
+        <v>4</v>
+      </c>
+      <c r="P51">
+        <v>5</v>
+      </c>
+      <c r="Q51">
+        <v>5</v>
+      </c>
+      <c r="R51">
+        <v>5</v>
+      </c>
+      <c r="S51">
+        <v>4</v>
+      </c>
+      <c r="T51">
+        <v>5</v>
+      </c>
+      <c r="U51">
+        <v>3</v>
+      </c>
+      <c r="V51">
+        <v>5</v>
+      </c>
+      <c r="W51">
         <v>1</v>
       </c>
-      <c r="P51">
-        <v>4</v>
-      </c>
-      <c r="Q51">
-        <v>4</v>
-      </c>
-      <c r="R51">
-        <v>4</v>
-      </c>
-      <c r="S51">
-        <v>4</v>
-      </c>
-      <c r="T51">
-        <v>4</v>
-      </c>
-      <c r="U51">
-        <v>3</v>
-      </c>
-      <c r="V51">
-        <v>4</v>
-      </c>
-      <c r="W51">
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>15</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+      <c r="F52">
+        <v>4</v>
+      </c>
+      <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
+        <v>4</v>
+      </c>
+      <c r="I52">
+        <v>4</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>4</v>
+      </c>
+      <c r="L52">
+        <v>4</v>
+      </c>
+      <c r="M52">
+        <v>4</v>
+      </c>
+      <c r="N52">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52">
+        <v>4</v>
+      </c>
+      <c r="Q52">
+        <v>4</v>
+      </c>
+      <c r="R52">
+        <v>4</v>
+      </c>
+      <c r="S52">
+        <v>4</v>
+      </c>
+      <c r="T52">
+        <v>4</v>
+      </c>
+      <c r="U52">
+        <v>3</v>
+      </c>
+      <c r="V52">
+        <v>4</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B52">
-        <f t="shared" ref="B52:W52" si="11">SUM(B37:B51)</f>
+      <c r="B53">
+        <f t="shared" ref="B53:W53" si="14">SUM(B38:B52)</f>
         <v>100</v>
       </c>
-      <c r="C52">
-        <f t="shared" si="11"/>
+      <c r="C53">
+        <f t="shared" si="14"/>
         <v>93</v>
       </c>
-      <c r="D52">
-        <f t="shared" si="11"/>
+      <c r="D53">
+        <f t="shared" si="14"/>
         <v>81</v>
       </c>
-      <c r="E52">
-        <f t="shared" si="11"/>
+      <c r="E53">
+        <f t="shared" si="14"/>
         <v>97</v>
       </c>
-      <c r="F52">
-        <f t="shared" si="11"/>
+      <c r="F53">
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
-      <c r="G52">
-        <f t="shared" si="11"/>
+      <c r="G53">
+        <f t="shared" si="14"/>
         <v>76</v>
       </c>
-      <c r="H52">
-        <f t="shared" si="11"/>
+      <c r="H53">
+        <f t="shared" si="14"/>
         <v>94</v>
       </c>
-      <c r="I52">
-        <f t="shared" si="11"/>
+      <c r="I53">
+        <f t="shared" si="14"/>
         <v>94</v>
       </c>
-      <c r="J52">
-        <f t="shared" si="11"/>
+      <c r="J53">
+        <f t="shared" si="14"/>
         <v>85</v>
       </c>
-      <c r="K52">
-        <f t="shared" si="11"/>
+      <c r="K53">
+        <f t="shared" si="14"/>
         <v>92</v>
       </c>
-      <c r="L52">
-        <f t="shared" si="11"/>
+      <c r="L53">
+        <f t="shared" si="14"/>
         <v>93</v>
       </c>
-      <c r="M52">
-        <f t="shared" si="11"/>
+      <c r="M53">
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="N52">
-        <f t="shared" si="11"/>
+      <c r="N53">
+        <f t="shared" si="14"/>
         <v>51</v>
       </c>
-      <c r="O52">
-        <f t="shared" si="11"/>
+      <c r="O53">
+        <f t="shared" si="14"/>
         <v>78</v>
       </c>
-      <c r="P52">
-        <f t="shared" si="11"/>
+      <c r="P53">
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="Q52">
-        <f t="shared" si="11"/>
+      <c r="Q53">
+        <f t="shared" si="14"/>
         <v>94</v>
       </c>
-      <c r="R52">
-        <f t="shared" si="11"/>
+      <c r="R53">
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
-      <c r="S52">
-        <f t="shared" si="11"/>
+      <c r="S53">
+        <f t="shared" si="14"/>
         <v>90</v>
       </c>
-      <c r="T52">
-        <f t="shared" si="11"/>
+      <c r="T53">
+        <f t="shared" si="14"/>
         <v>86</v>
       </c>
-      <c r="U52">
-        <f t="shared" si="11"/>
+      <c r="U53">
+        <f t="shared" si="14"/>
         <v>78</v>
       </c>
-      <c r="V52">
-        <f t="shared" si="11"/>
+      <c r="V53">
+        <f t="shared" si="14"/>
         <v>72</v>
       </c>
-      <c r="W52">
-        <f t="shared" si="11"/>
+      <c r="W53">
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B54" s="1" t="s">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B55" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="L55" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M55" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N54" s="1" t="s">
+      <c r="N55" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O54" s="1" t="s">
+      <c r="O55" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P54" s="1" t="s">
+      <c r="P55" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q54" s="1" t="s">
+      <c r="Q55" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R54" s="1" t="s">
+      <c r="R55" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S54" s="1" t="s">
+      <c r="S55" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T54" s="1" t="s">
+      <c r="T55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U54" s="1" t="s">
+      <c r="U55" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="V54" s="1" t="s">
+      <c r="V55" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W54" s="1" t="s">
+      <c r="W55" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>1</v>
-      </c>
-      <c r="B55">
-        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="C56">
+        <v>10</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>6</v>
+      </c>
+      <c r="H56">
+        <v>9</v>
+      </c>
+      <c r="I56">
+        <v>10</v>
+      </c>
+      <c r="J56">
+        <v>9</v>
+      </c>
+      <c r="K56">
+        <v>10</v>
+      </c>
+      <c r="L56">
+        <v>9</v>
+      </c>
+      <c r="M56">
+        <v>10</v>
+      </c>
+      <c r="N56">
+        <v>7</v>
+      </c>
+      <c r="O56">
+        <v>10</v>
+      </c>
+      <c r="P56">
+        <v>10</v>
+      </c>
+      <c r="Q56">
+        <v>10</v>
+      </c>
+      <c r="R56">
+        <v>4</v>
+      </c>
+      <c r="S56">
+        <v>10</v>
+      </c>
+      <c r="T56">
+        <v>10</v>
+      </c>
+      <c r="U56">
+        <v>6</v>
+      </c>
+      <c r="V56">
+        <v>7</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57">
+        <v>7</v>
+      </c>
+      <c r="F57">
+        <v>8</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="H57">
+        <v>6</v>
+      </c>
+      <c r="I57">
+        <v>8</v>
+      </c>
+      <c r="J57">
+        <v>8</v>
+      </c>
+      <c r="K57">
+        <v>8</v>
+      </c>
+      <c r="L57">
+        <v>6</v>
+      </c>
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57">
+        <v>6</v>
+      </c>
+      <c r="O57">
+        <v>8</v>
+      </c>
+      <c r="P57">
+        <v>6</v>
+      </c>
+      <c r="Q57">
+        <v>8</v>
+      </c>
+      <c r="R57">
+        <v>6</v>
+      </c>
+      <c r="S57">
+        <v>8</v>
+      </c>
+      <c r="T57">
+        <v>8</v>
+      </c>
+      <c r="U57">
+        <v>8</v>
+      </c>
+      <c r="V57">
+        <v>8</v>
+      </c>
+      <c r="W57">
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="C58">
+        <v>16</v>
+      </c>
+      <c r="D58">
+        <v>15</v>
+      </c>
+      <c r="E58">
+        <v>16</v>
+      </c>
+      <c r="F58">
+        <v>16</v>
+      </c>
+      <c r="G58">
+        <v>16</v>
+      </c>
+      <c r="H58">
+        <v>16</v>
+      </c>
+      <c r="I58">
+        <v>16</v>
+      </c>
+      <c r="J58">
+        <v>15</v>
+      </c>
+      <c r="K58">
+        <v>16</v>
+      </c>
+      <c r="L58">
+        <v>16</v>
+      </c>
+      <c r="M58">
+        <v>16</v>
+      </c>
+      <c r="N58">
+        <v>15</v>
+      </c>
+      <c r="O58">
+        <v>16</v>
+      </c>
+      <c r="P58">
+        <v>16</v>
+      </c>
+      <c r="Q58">
+        <v>16</v>
+      </c>
+      <c r="R58">
+        <v>12</v>
+      </c>
+      <c r="S58">
+        <v>15</v>
+      </c>
+      <c r="T58">
+        <v>16</v>
+      </c>
+      <c r="U58">
+        <v>13</v>
+      </c>
+      <c r="V58">
+        <v>16</v>
+      </c>
+      <c r="W58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>6</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59">
+        <v>6</v>
+      </c>
+      <c r="I59">
+        <v>6</v>
+      </c>
+      <c r="J59">
+        <v>4</v>
+      </c>
+      <c r="K59">
+        <v>6</v>
+      </c>
+      <c r="L59">
+        <v>6</v>
+      </c>
+      <c r="M59">
+        <v>6</v>
+      </c>
+      <c r="N59">
+        <v>6</v>
+      </c>
+      <c r="O59">
+        <v>6</v>
+      </c>
+      <c r="P59">
+        <v>6</v>
+      </c>
+      <c r="Q59">
+        <v>6</v>
+      </c>
+      <c r="R59">
+        <v>4</v>
+      </c>
+      <c r="S59">
+        <v>6</v>
+      </c>
+      <c r="T59">
+        <v>6</v>
+      </c>
+      <c r="U59">
+        <v>5</v>
+      </c>
+      <c r="V59">
+        <v>6</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+      <c r="F60">
+        <v>8</v>
+      </c>
+      <c r="G60">
+        <v>7</v>
+      </c>
+      <c r="H60">
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>8</v>
+      </c>
+      <c r="J60">
+        <v>8</v>
+      </c>
+      <c r="K60">
+        <v>8</v>
+      </c>
+      <c r="L60">
+        <v>8</v>
+      </c>
+      <c r="M60">
+        <v>8</v>
+      </c>
+      <c r="N60">
+        <v>7</v>
+      </c>
+      <c r="O60">
+        <v>8</v>
+      </c>
+      <c r="P60">
+        <v>7</v>
+      </c>
+      <c r="Q60">
+        <v>8</v>
+      </c>
+      <c r="R60">
+        <v>6</v>
+      </c>
+      <c r="S60">
+        <v>8</v>
+      </c>
+      <c r="T60">
+        <v>7</v>
+      </c>
+      <c r="U60">
+        <v>8</v>
+      </c>
+      <c r="V60">
+        <v>8</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B61">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
+        <v>4</v>
+      </c>
+      <c r="F61">
+        <v>4</v>
+      </c>
+      <c r="G61">
+        <v>4</v>
+      </c>
+      <c r="H61">
+        <v>4</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61">
+        <v>3</v>
+      </c>
+      <c r="K61">
+        <v>4</v>
+      </c>
+      <c r="L61">
+        <v>4</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61">
+        <v>4</v>
+      </c>
+      <c r="O61">
+        <v>4</v>
+      </c>
+      <c r="P61">
+        <v>4</v>
+      </c>
+      <c r="Q61">
+        <v>4</v>
+      </c>
+      <c r="R61">
+        <v>4</v>
+      </c>
+      <c r="S61">
+        <v>4</v>
+      </c>
+      <c r="T61">
+        <v>2</v>
+      </c>
+      <c r="U61">
+        <v>4</v>
+      </c>
+      <c r="V61">
+        <v>4</v>
+      </c>
+      <c r="W61">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>7</v>
+      </c>
+      <c r="D62">
+        <v>6</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+      <c r="G62">
+        <v>6</v>
+      </c>
+      <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62">
+        <v>8</v>
+      </c>
+      <c r="J62">
+        <v>6</v>
+      </c>
+      <c r="K62">
+        <v>8</v>
+      </c>
+      <c r="L62">
+        <v>8</v>
+      </c>
+      <c r="M62">
+        <v>7</v>
+      </c>
+      <c r="N62">
+        <v>4</v>
+      </c>
+      <c r="O62">
+        <v>5</v>
+      </c>
+      <c r="P62">
+        <v>8</v>
+      </c>
+      <c r="Q62">
+        <v>8</v>
+      </c>
+      <c r="R62">
+        <v>5</v>
+      </c>
+      <c r="S62">
+        <v>4</v>
+      </c>
+      <c r="T62">
+        <v>6</v>
+      </c>
+      <c r="U62">
+        <v>3</v>
+      </c>
+      <c r="V62">
+        <v>6</v>
+      </c>
+      <c r="W62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63">
+        <v>3</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="H63">
+        <v>3</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63">
+        <v>3</v>
+      </c>
+      <c r="L63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="P63">
+        <v>3</v>
+      </c>
+      <c r="Q63">
+        <v>3</v>
+      </c>
+      <c r="R63">
+        <v>3</v>
+      </c>
+      <c r="S63">
+        <v>2</v>
+      </c>
+      <c r="T63">
+        <v>2</v>
+      </c>
+      <c r="U63">
+        <v>3</v>
+      </c>
+      <c r="V63">
+        <v>3</v>
+      </c>
+      <c r="W63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64">
+        <v>5</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64">
+        <v>5</v>
+      </c>
+      <c r="L64">
+        <v>5</v>
+      </c>
+      <c r="M64">
+        <v>3</v>
+      </c>
+      <c r="N64">
+        <v>5</v>
+      </c>
+      <c r="O64">
+        <v>4</v>
+      </c>
+      <c r="P64">
+        <v>5</v>
+      </c>
+      <c r="Q64">
+        <v>5</v>
+      </c>
+      <c r="R64">
+        <v>3</v>
+      </c>
+      <c r="S64">
+        <v>4</v>
+      </c>
+      <c r="T64">
+        <v>5</v>
+      </c>
+      <c r="U64">
+        <v>4</v>
+      </c>
+      <c r="V64">
+        <v>2</v>
+      </c>
+      <c r="W64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65">
         <v>8</v>
+      </c>
+      <c r="C65">
+        <v>8</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+      <c r="E65">
+        <v>8</v>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+      <c r="G65">
+        <v>6</v>
+      </c>
+      <c r="H65">
+        <v>6</v>
+      </c>
+      <c r="I65">
+        <v>8</v>
+      </c>
+      <c r="J65">
+        <v>7</v>
+      </c>
+      <c r="K65">
+        <v>7</v>
+      </c>
+      <c r="L65">
+        <v>8</v>
+      </c>
+      <c r="M65">
+        <v>7</v>
+      </c>
+      <c r="N65">
+        <v>6</v>
+      </c>
+      <c r="O65">
+        <v>5</v>
+      </c>
+      <c r="P65">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>8</v>
+      </c>
+      <c r="R65">
+        <v>4</v>
+      </c>
+      <c r="S65">
+        <v>3</v>
+      </c>
+      <c r="T65">
+        <v>8</v>
+      </c>
+      <c r="U65">
+        <v>6</v>
+      </c>
+      <c r="V65">
+        <v>3</v>
+      </c>
+      <c r="W65">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>7</v>
+      </c>
+      <c r="E66">
+        <v>8</v>
+      </c>
+      <c r="F66">
+        <v>8</v>
+      </c>
+      <c r="G66">
+        <v>8</v>
+      </c>
+      <c r="H66">
+        <v>8</v>
+      </c>
+      <c r="I66">
+        <v>8</v>
+      </c>
+      <c r="J66">
+        <v>8</v>
+      </c>
+      <c r="K66">
+        <v>6</v>
+      </c>
+      <c r="L66">
+        <v>8</v>
+      </c>
+      <c r="M66">
+        <v>8</v>
+      </c>
+      <c r="N66">
+        <v>4</v>
+      </c>
+      <c r="O66">
+        <v>8</v>
+      </c>
+      <c r="P66">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>8</v>
+      </c>
+      <c r="R66">
+        <v>5</v>
+      </c>
+      <c r="S66">
+        <v>5</v>
+      </c>
+      <c r="T66">
+        <v>8</v>
+      </c>
+      <c r="U66">
+        <v>7</v>
+      </c>
+      <c r="V66">
+        <v>8</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B67">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C67">
+        <v>4</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>4</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67">
+        <v>4</v>
+      </c>
+      <c r="I67">
+        <v>4</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+      <c r="K67">
+        <v>4</v>
+      </c>
+      <c r="L67">
+        <v>4</v>
+      </c>
+      <c r="M67">
+        <v>3</v>
+      </c>
+      <c r="N67">
+        <v>3</v>
+      </c>
+      <c r="O67">
+        <v>4</v>
+      </c>
+      <c r="P67">
+        <v>3</v>
+      </c>
+      <c r="Q67">
+        <v>4</v>
+      </c>
+      <c r="R67">
+        <v>4</v>
+      </c>
+      <c r="S67">
+        <v>3</v>
+      </c>
+      <c r="T67">
+        <v>4</v>
+      </c>
+      <c r="U67">
+        <v>2</v>
+      </c>
+      <c r="V67">
+        <v>4</v>
+      </c>
+      <c r="W67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
+        <v>13</v>
+      </c>
+      <c r="B68">
+        <v>6</v>
+      </c>
+      <c r="C68">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>6</v>
+      </c>
+      <c r="F68">
+        <v>6</v>
+      </c>
+      <c r="G68">
+        <v>6</v>
+      </c>
+      <c r="H68">
+        <v>6</v>
+      </c>
+      <c r="I68">
+        <v>6</v>
+      </c>
+      <c r="J68">
+        <v>3</v>
+      </c>
+      <c r="K68">
+        <v>6</v>
+      </c>
+      <c r="L68">
+        <v>6</v>
+      </c>
+      <c r="M68">
+        <v>6</v>
+      </c>
+      <c r="N68">
+        <v>2</v>
+      </c>
+      <c r="O68">
+        <v>5</v>
+      </c>
+      <c r="P68">
+        <v>6</v>
+      </c>
+      <c r="Q68">
+        <v>6</v>
+      </c>
+      <c r="R68">
+        <v>2</v>
+      </c>
+      <c r="S68">
+        <v>4</v>
+      </c>
+      <c r="T68">
+        <v>6</v>
+      </c>
+      <c r="U68">
+        <v>6</v>
+      </c>
+      <c r="V68">
+        <v>6</v>
+      </c>
+      <c r="W68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A69">
         <v>14</v>
       </c>
-      <c r="B68">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
+      <c r="B69">
+        <v>6</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>6</v>
+      </c>
+      <c r="F69">
+        <v>6</v>
+      </c>
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>6</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69">
+        <v>4</v>
+      </c>
+      <c r="L69">
+        <v>3</v>
+      </c>
+      <c r="M69">
+        <v>6</v>
+      </c>
+      <c r="N69">
+        <v>2</v>
+      </c>
+      <c r="O69">
+        <v>4</v>
+      </c>
+      <c r="P69">
+        <v>6</v>
+      </c>
+      <c r="Q69">
+        <v>6</v>
+      </c>
+      <c r="R69">
+        <v>3</v>
+      </c>
+      <c r="S69">
+        <v>5</v>
+      </c>
+      <c r="T69">
+        <v>5</v>
+      </c>
+      <c r="U69">
+        <v>6</v>
+      </c>
+      <c r="V69">
+        <v>5</v>
+      </c>
+      <c r="W69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B69">
-        <f t="shared" ref="B69:W69" si="12">SUM(B55:B68)</f>
+      <c r="B70">
+        <f t="shared" ref="B70:W70" si="15">SUM(B56:B69)</f>
         <v>100</v>
       </c>
-      <c r="C69">
-        <f t="shared" ref="C69" si="13">SUM(C55:C68)</f>
-        <v>0</v>
-      </c>
-      <c r="D69">
-        <f t="shared" ref="D69" si="14">SUM(D55:D68)</f>
-        <v>0</v>
-      </c>
-      <c r="E69">
-        <f t="shared" ref="E69" si="15">SUM(E55:E68)</f>
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <f t="shared" ref="F69" si="16">SUM(F55:F68)</f>
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <f t="shared" ref="G69" si="17">SUM(G55:G68)</f>
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <f t="shared" ref="H69" si="18">SUM(H55:H68)</f>
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <f t="shared" ref="I69" si="19">SUM(I55:I68)</f>
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <f t="shared" ref="J69" si="20">SUM(J55:J68)</f>
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <f t="shared" ref="K69" si="21">SUM(K55:K68)</f>
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <f t="shared" ref="L69" si="22">SUM(L55:L68)</f>
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <f t="shared" ref="M69" si="23">SUM(M55:M68)</f>
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <f t="shared" ref="N69" si="24">SUM(N55:N68)</f>
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <f t="shared" ref="O69" si="25">SUM(O55:O68)</f>
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <f t="shared" ref="P69" si="26">SUM(P55:P68)</f>
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <f t="shared" ref="Q69" si="27">SUM(Q55:Q68)</f>
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <f t="shared" ref="R69" si="28">SUM(R55:R68)</f>
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <f t="shared" ref="S69" si="29">SUM(S55:S68)</f>
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <f t="shared" ref="T69" si="30">SUM(T55:T68)</f>
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <f t="shared" ref="U69" si="31">SUM(U55:U68)</f>
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <f t="shared" ref="V69" si="32">SUM(V55:V68)</f>
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <f t="shared" ref="W69" si="33">SUM(W55:W68)</f>
-        <v>0</v>
+      <c r="C70">
+        <f t="shared" si="15"/>
+        <v>93</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="15"/>
+        <v>87</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="15"/>
+        <v>98</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="15"/>
+        <v>99</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="15"/>
+        <v>86</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="15"/>
+        <v>90</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="15"/>
+        <v>100</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="15"/>
+        <v>85</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="15"/>
+        <v>95</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="15"/>
+        <v>94</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="15"/>
+        <v>90</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="15"/>
+        <v>72</v>
+      </c>
+      <c r="O70">
+        <f t="shared" si="15"/>
+        <v>88</v>
+      </c>
+      <c r="P70">
+        <f t="shared" si="15"/>
+        <v>96</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="15"/>
+        <v>100</v>
+      </c>
+      <c r="R70">
+        <f t="shared" si="15"/>
+        <v>65</v>
+      </c>
+      <c r="S70">
+        <f t="shared" si="15"/>
+        <v>81</v>
+      </c>
+      <c r="T70">
+        <f t="shared" si="15"/>
+        <v>93</v>
+      </c>
+      <c r="U70">
+        <f t="shared" si="15"/>
+        <v>81</v>
+      </c>
+      <c r="V70">
+        <f t="shared" si="15"/>
+        <v>86</v>
+      </c>
+      <c r="W70">
+        <f t="shared" si="15"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="P72">
+        <v>96</v>
+      </c>
+      <c r="Q72">
+        <v>100</v>
+      </c>
+      <c r="R72">
+        <v>65</v>
+      </c>
+      <c r="S72">
+        <v>81</v>
+      </c>
+      <c r="T72">
+        <v>93</v>
+      </c>
+      <c r="U72">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB762813-E62C-B843-BDE2-5B0026104145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC476B5-0951-6341-A889-498931FFE043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20700" yWindow="4580" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4700" yWindow="760" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -825,13 +825,16 @@
       <c r="G5">
         <v>93</v>
       </c>
+      <c r="K5">
+        <v>99</v>
+      </c>
       <c r="O5">
         <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
-        <v>31.68</v>
+        <v>36.630000000000003</v>
       </c>
       <c r="P5" s="2">
         <f>O5/$N$2</f>
-        <v>85.621621621621628</v>
+        <v>99.000000000000014</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -884,13 +887,16 @@
       <c r="G7">
         <v>98</v>
       </c>
+      <c r="K7">
+        <v>98</v>
+      </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>33.120000000000005</v>
+        <v>38.020000000000003</v>
       </c>
       <c r="P7" s="2">
         <f t="shared" si="1"/>
-        <v>89.51351351351353</v>
+        <v>102.75675675675677</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -912,13 +918,16 @@
       <c r="G8">
         <v>99</v>
       </c>
+      <c r="K8">
+        <v>99</v>
+      </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>33.44</v>
+        <v>38.39</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="1"/>
-        <v>90.378378378378372</v>
+        <v>103.75675675675676</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -1030,13 +1039,16 @@
       <c r="G12">
         <v>85</v>
       </c>
+      <c r="K12">
+        <v>92</v>
+      </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>29.12</v>
+        <v>33.72</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="1"/>
-        <v>78.702702702702709</v>
+        <v>91.13513513513513</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -1058,13 +1070,16 @@
       <c r="G13">
         <v>95</v>
       </c>
+      <c r="K13">
+        <v>97</v>
+      </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>31.84</v>
+        <v>36.69</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="1"/>
-        <v>86.054054054054049</v>
+        <v>99.162162162162161</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1117,13 +1132,16 @@
       <c r="G15">
         <v>90</v>
       </c>
+      <c r="K15">
+        <v>99</v>
+      </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>32.32</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="1"/>
-        <v>87.351351351351354</v>
+        <v>100.72972972972974</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1176,13 +1194,16 @@
       <c r="G17">
         <v>88</v>
       </c>
+      <c r="K17">
+        <v>98</v>
+      </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>28.48</v>
+        <v>33.380000000000003</v>
       </c>
       <c r="P17" s="2">
         <f t="shared" si="1"/>
-        <v>76.972972972972968</v>
+        <v>90.216216216216225</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -1238,13 +1259,16 @@
       <c r="G20">
         <v>100</v>
       </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
       <c r="O20">
         <f t="shared" ref="O20:O24" si="3">(F20+F$33)*F$2+G$2*(G20+G$33)+H$2*(H20+H$33)+I$2*(I20+I$33)+J$2*(J20+J$33)+K$2*(K20+K$33)+L$2*(L20+L$33)+M$2*(M20+M$33)</f>
-        <v>32.96</v>
+        <v>37.96</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="1"/>
-        <v>89.081081081081081</v>
+        <v>102.5945945945946</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -1266,13 +1290,16 @@
       <c r="G21">
         <v>65</v>
       </c>
+      <c r="K21">
+        <v>90</v>
+      </c>
       <c r="O21">
         <f t="shared" si="3"/>
-        <v>23.520000000000003</v>
+        <v>28.020000000000003</v>
       </c>
       <c r="P21" s="2">
         <f t="shared" si="1"/>
-        <v>63.567567567567579</v>
+        <v>75.72972972972974</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -1294,13 +1321,16 @@
       <c r="G22">
         <v>81</v>
       </c>
+      <c r="K22">
+        <v>91</v>
+      </c>
       <c r="O22">
         <f t="shared" si="3"/>
-        <v>29.28</v>
+        <v>33.83</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="1"/>
-        <v>79.135135135135144</v>
+        <v>91.432432432432435</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -1353,13 +1383,16 @@
       <c r="G24">
         <v>81</v>
       </c>
+      <c r="K24">
+        <v>96</v>
+      </c>
       <c r="O24">
         <f t="shared" si="3"/>
-        <v>27.36</v>
+        <v>32.159999999999997</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="1"/>
-        <v>73.945945945945951</v>
+        <v>86.918918918918905</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -1492,7 +1525,7 @@
       </c>
       <c r="K31">
         <f t="shared" si="5"/>
-        <v>91.125</v>
+        <v>94.10526315789474</v>
       </c>
       <c r="L31" t="e">
         <f t="shared" si="5"/>
@@ -1533,7 +1566,7 @@
       </c>
       <c r="K32">
         <f t="shared" si="7"/>
-        <v>8.3569902305965211</v>
+        <v>6.410882560512114</v>
       </c>
       <c r="L32" t="e">
         <f t="shared" si="7"/>
@@ -1592,7 +1625,7 @@
       </c>
       <c r="K34">
         <f t="shared" ref="K34" si="10">K31+K33</f>
-        <v>91.125</v>
+        <v>94.10526315789474</v>
       </c>
       <c r="L34" t="e">
         <f t="shared" ref="L34" si="11">L31+L33</f>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC476B5-0951-6341-A889-498931FFE043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD08C70-6821-9347-8E77-91E96B98DF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="760" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15840" yWindow="3440" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
   <si>
     <t>First name</t>
   </si>
@@ -719,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
@@ -949,13 +949,16 @@
       <c r="G9">
         <v>86</v>
       </c>
+      <c r="K9">
+        <v>94</v>
+      </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>27.840000000000003</v>
+        <v>32.540000000000006</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="1"/>
-        <v>75.243243243243256</v>
+        <v>87.945945945945965</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -1525,7 +1528,7 @@
       </c>
       <c r="K31">
         <f t="shared" si="5"/>
-        <v>94.10526315789474</v>
+        <v>94.1</v>
       </c>
       <c r="L31" t="e">
         <f t="shared" si="5"/>
@@ -1566,7 +1569,7 @@
       </c>
       <c r="K32">
         <f t="shared" si="7"/>
-        <v>6.410882560512114</v>
+        <v>6.239939270959546</v>
       </c>
       <c r="L32" t="e">
         <f t="shared" si="7"/>
@@ -1625,7 +1628,7 @@
       </c>
       <c r="K34">
         <f t="shared" ref="K34" si="10">K31+K33</f>
-        <v>94.10526315789474</v>
+        <v>94.1</v>
       </c>
       <c r="L34" t="e">
         <f t="shared" ref="L34" si="11">L31+L33</f>
@@ -4022,23 +4025,276 @@
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="P72">
+      <c r="B72" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S72" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V72" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Q72">
+      <c r="W72" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>2</v>
+      </c>
+      <c r="B74">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="B75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>4</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>5</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="B79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>8</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>9</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>10</v>
+      </c>
+      <c r="B82">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>11</v>
+      </c>
+      <c r="B83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>12</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>13</v>
+      </c>
+      <c r="B85">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>14</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87">
+        <f t="shared" ref="B87:W87" si="16">SUM(B73:B86)</f>
         <v>100</v>
       </c>
-      <c r="R72">
-        <v>65</v>
-      </c>
-      <c r="S72">
-        <v>81</v>
-      </c>
-      <c r="T72">
-        <v>93</v>
-      </c>
-      <c r="U72">
-        <v>81</v>
+      <c r="C87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD08C70-6821-9347-8E77-91E96B98DF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15840" yWindow="3440" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15840" yWindow="780" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD08C70-6821-9347-8E77-91E96B98DF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C56DEF-8716-6D46-845E-3576BE3C7B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15840" yWindow="780" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25180" yWindow="2040" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -719,16 +719,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W87"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="H1">
-        <v>0.16</v>
-      </c>
       <c r="I1">
         <v>0.16</v>
       </c>
@@ -752,12 +749,15 @@
       <c r="G2">
         <v>0.16</v>
       </c>
+      <c r="H2">
+        <v>0.16</v>
+      </c>
       <c r="K2">
         <v>0.05</v>
       </c>
       <c r="N2">
         <f>SUM(F2:M2)</f>
-        <v>0.37</v>
+        <v>0.53</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>101</v>
@@ -825,16 +825,19 @@
       <c r="G5">
         <v>93</v>
       </c>
+      <c r="H5">
+        <v>87</v>
+      </c>
       <c r="K5">
         <v>99</v>
       </c>
       <c r="O5">
         <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
-        <v>36.630000000000003</v>
+        <v>51.510000000000005</v>
       </c>
       <c r="P5" s="2">
         <f>O5/$N$2</f>
-        <v>99.000000000000014</v>
+        <v>97.188679245283026</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -856,16 +859,19 @@
       <c r="G6">
         <v>87</v>
       </c>
+      <c r="H6">
+        <v>72</v>
+      </c>
       <c r="K6">
         <v>88</v>
       </c>
       <c r="O6">
         <f t="shared" ref="O6:O17" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
-        <v>33.200000000000003</v>
+        <v>45.68</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" ref="P6:P24" si="1">O6/$N$2</f>
-        <v>89.72972972972974</v>
+        <v>86.188679245283012</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -887,16 +893,19 @@
       <c r="G7">
         <v>98</v>
       </c>
+      <c r="H7">
+        <v>89</v>
+      </c>
       <c r="K7">
         <v>98</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>38.020000000000003</v>
+        <v>53.220000000000006</v>
       </c>
       <c r="P7" s="2">
         <f t="shared" si="1"/>
-        <v>102.75675675675677</v>
+        <v>100.41509433962264</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -918,16 +927,19 @@
       <c r="G8">
         <v>99</v>
       </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
       <c r="K8">
         <v>99</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>38.39</v>
+        <v>55.35</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="1"/>
-        <v>103.75675675675676</v>
+        <v>104.43396226415094</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -949,16 +961,19 @@
       <c r="G9">
         <v>86</v>
       </c>
+      <c r="H9">
+        <v>53</v>
+      </c>
       <c r="K9">
         <v>94</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>32.540000000000006</v>
+        <v>41.980000000000004</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="1"/>
-        <v>87.945945945945965</v>
+        <v>79.20754716981132</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -980,16 +995,19 @@
       <c r="G10">
         <v>90</v>
       </c>
+      <c r="H10">
+        <v>84</v>
+      </c>
       <c r="K10">
         <v>98</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>36.26</v>
+        <v>50.66</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>95.584905660377345</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -1011,16 +1029,19 @@
       <c r="G11">
         <v>100</v>
       </c>
+      <c r="H11">
+        <v>98</v>
+      </c>
       <c r="K11">
         <v>91</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>37.51</v>
+        <v>54.15</v>
       </c>
       <c r="P11" s="2">
         <f t="shared" si="1"/>
-        <v>101.37837837837837</v>
+        <v>102.1698113207547</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -1042,16 +1063,19 @@
       <c r="G12">
         <v>85</v>
       </c>
+      <c r="H12">
+        <v>72</v>
+      </c>
       <c r="K12">
         <v>92</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>33.72</v>
+        <v>46.2</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="1"/>
-        <v>91.13513513513513</v>
+        <v>87.169811320754718</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -1073,16 +1097,19 @@
       <c r="G13">
         <v>95</v>
       </c>
+      <c r="H13">
+        <v>89</v>
+      </c>
       <c r="K13">
         <v>97</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>36.69</v>
+        <v>51.89</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="1"/>
-        <v>99.162162162162161</v>
+        <v>97.905660377358487</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1104,16 +1131,19 @@
       <c r="G14">
         <v>94</v>
       </c>
+      <c r="H14">
+        <v>96</v>
+      </c>
       <c r="K14">
         <v>98</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>36.74</v>
+        <v>53.059999999999995</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="1"/>
-        <v>99.297297297297305</v>
+        <v>100.11320754716979</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -1135,16 +1165,19 @@
       <c r="G15">
         <v>90</v>
       </c>
+      <c r="H15">
+        <v>86</v>
+      </c>
       <c r="K15">
         <v>99</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>37.270000000000003</v>
+        <v>51.99</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="1"/>
-        <v>100.72972972972974</v>
+        <v>98.094339622641513</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1166,16 +1199,19 @@
       <c r="G16">
         <v>72</v>
       </c>
+      <c r="H16">
+        <v>55</v>
+      </c>
       <c r="K16">
         <v>85</v>
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>25.85</v>
+        <v>35.61</v>
       </c>
       <c r="P16" s="2">
         <f t="shared" si="1"/>
-        <v>69.86486486486487</v>
+        <v>67.188679245283012</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -1197,16 +1233,19 @@
       <c r="G17">
         <v>88</v>
       </c>
+      <c r="H17">
+        <v>76</v>
+      </c>
       <c r="K17">
         <v>98</v>
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>33.380000000000003</v>
+        <v>46.5</v>
       </c>
       <c r="P17" s="2">
         <f t="shared" si="1"/>
-        <v>90.216216216216225</v>
+        <v>87.735849056603769</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -1231,16 +1270,19 @@
       <c r="G19">
         <v>96</v>
       </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="O19">
-        <f t="shared" ref="O19" si="2">(F19+F$33)*F$2+G$2*(G19+G$33)+H$2*(H19+H$33)+I$2*(I19+I$33)+J$2*(J19+J$33)+K$2*(K19+K$33)+L$2*(L19+L$33)+M$2*(M19+M$33)</f>
-        <v>38.28</v>
+        <f>(F19+F$33)*F$2+G$2*(G19+G$33)+H$2*(H19+H$33)+I$2*(I19+I$33)+J$2*(J19+J$33)+K$2*(K19+K$33)+L$2*(L19+L$33)+M$2*(M19+M$33)</f>
+        <v>55.24</v>
       </c>
       <c r="P19" s="2">
         <f t="shared" si="1"/>
-        <v>103.45945945945947</v>
+        <v>104.22641509433961</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
@@ -1262,16 +1304,19 @@
       <c r="G20">
         <v>100</v>
       </c>
+      <c r="H20">
+        <v>96</v>
+      </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="O20">
-        <f t="shared" ref="O20:O24" si="3">(F20+F$33)*F$2+G$2*(G20+G$33)+H$2*(H20+H$33)+I$2*(I20+I$33)+J$2*(J20+J$33)+K$2*(K20+K$33)+L$2*(L20+L$33)+M$2*(M20+M$33)</f>
-        <v>37.96</v>
+        <f t="shared" ref="O20:O24" si="2">(F20+F$33)*F$2+G$2*(G20+G$33)+H$2*(H20+H$33)+I$2*(I20+I$33)+J$2*(J20+J$33)+K$2*(K20+K$33)+L$2*(L20+L$33)+M$2*(M20+M$33)</f>
+        <v>54.28</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="1"/>
-        <v>102.5945945945946</v>
+        <v>102.41509433962264</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -1297,12 +1342,12 @@
         <v>90</v>
       </c>
       <c r="O21">
-        <f t="shared" si="3"/>
-        <v>28.020000000000003</v>
+        <f t="shared" si="2"/>
+        <v>28.980000000000004</v>
       </c>
       <c r="P21" s="2">
         <f t="shared" si="1"/>
-        <v>75.72972972972974</v>
+        <v>54.679245283018872</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -1324,16 +1369,19 @@
       <c r="G22">
         <v>81</v>
       </c>
+      <c r="H22">
+        <v>90</v>
+      </c>
       <c r="K22">
         <v>91</v>
       </c>
       <c r="O22">
-        <f t="shared" si="3"/>
-        <v>33.83</v>
+        <f t="shared" si="2"/>
+        <v>49.19</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="1"/>
-        <v>91.432432432432435</v>
+        <v>92.811320754716974</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -1355,16 +1403,19 @@
       <c r="G23">
         <v>93</v>
       </c>
+      <c r="H23">
+        <v>86</v>
+      </c>
       <c r="K23">
         <v>94</v>
       </c>
       <c r="O23">
-        <f t="shared" si="3"/>
-        <v>35.260000000000005</v>
+        <f t="shared" si="2"/>
+        <v>49.980000000000004</v>
       </c>
       <c r="P23" s="2">
         <f t="shared" si="1"/>
-        <v>95.297297297297305</v>
+        <v>94.301886792452834</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -1386,16 +1437,19 @@
       <c r="G24">
         <v>81</v>
       </c>
+      <c r="H24">
+        <v>82</v>
+      </c>
       <c r="K24">
         <v>96</v>
       </c>
       <c r="O24">
-        <f t="shared" si="3"/>
-        <v>32.159999999999997</v>
+        <f t="shared" si="2"/>
+        <v>46.239999999999995</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="1"/>
-        <v>86.918918918918905</v>
+        <v>87.245283018867909</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -1429,12 +1483,15 @@
       <c r="G27">
         <v>0.2</v>
       </c>
+      <c r="H27">
+        <v>0.2</v>
+      </c>
       <c r="K27">
         <v>0.05</v>
       </c>
       <c r="N27">
         <f>SUM(F27:M27)</f>
-        <v>0.45</v>
+        <v>0.65000000000000013</v>
       </c>
       <c r="P27" s="2"/>
     </row>
@@ -1457,16 +1514,19 @@
       <c r="G28">
         <v>86</v>
       </c>
+      <c r="H28">
+        <v>85</v>
+      </c>
       <c r="K28">
         <v>75</v>
       </c>
       <c r="O28">
         <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
-        <v>37.75</v>
+        <v>55.95</v>
       </c>
       <c r="P28" s="2">
         <f>O28/$N$27</f>
-        <v>83.888888888888886</v>
+        <v>86.076923076923066</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
@@ -1490,11 +1550,11 @@
       </c>
       <c r="O29">
         <f>(F29+F$33)*F$27+G$27*(G29+G$33)+H$27*(H29+H$33)+I$27*(I29+I$33)+J$27*(J29+J$33)+K$27*(K29+K$33)+L$27*(L29+L$33)+M$27*(M29+M$33)</f>
-        <v>9.8000000000000007</v>
+        <v>11</v>
       </c>
       <c r="P29" s="2">
         <f>O29/$N$27</f>
-        <v>21.777777777777779</v>
+        <v>16.92307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
@@ -1511,35 +1571,35 @@
         <v>82.952380952380949</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31:I31" si="4">AVERAGE(G5:G24,G28:G29)</f>
+        <f t="shared" ref="G31:I31" si="3">AVERAGE(G5:G24,G28:G29)</f>
         <v>85.523809523809518</v>
       </c>
-      <c r="H31" t="e">
+      <c r="H31">
+        <f t="shared" si="3"/>
+        <v>84</v>
+      </c>
+      <c r="I31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J31" t="e">
+        <f t="shared" ref="J31:N31" si="4">AVERAGE(J5:J24,J28:J29)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="4"/>
+        <v>94.1</v>
+      </c>
+      <c r="L31" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I31" t="e">
+      <c r="M31" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J31" t="e">
-        <f t="shared" ref="J31:N31" si="5">AVERAGE(J5:J24,J28:J29)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="5"/>
-        <v>94.1</v>
-      </c>
-      <c r="L31" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="N31" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1552,35 +1612,35 @@
         <v>18.829434910469786</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32:I32" si="6">STDEV(G5:G24,G28:G29)</f>
+        <f t="shared" ref="G32:I32" si="5">STDEV(G5:G24,G28:G29)</f>
         <v>18.06825682687473</v>
       </c>
-      <c r="H32" t="e">
+      <c r="H32">
+        <f t="shared" si="5"/>
+        <v>13.45362404707371</v>
+      </c>
+      <c r="I32" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J32" t="e">
+        <f t="shared" ref="J32:N32" si="6">STDEV(J5:J24,J28:J29)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="6"/>
+        <v>6.239939270959546</v>
+      </c>
+      <c r="L32" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I32" t="e">
+      <c r="M32" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J32" t="e">
-        <f t="shared" ref="J32:N32" si="7">STDEV(J5:J24,J28:J29)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="7"/>
-        <v>6.239939270959546</v>
-      </c>
-      <c r="L32" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="N32" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1594,7 +1654,9 @@
       <c r="G33" s="1">
         <v>5</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="1">
+        <v>6</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1611,35 +1673,35 @@
         <v>89.952380952380949</v>
       </c>
       <c r="G34">
-        <f t="shared" ref="G34:I34" si="8">G31+G33</f>
+        <f t="shared" ref="G34:I34" si="7">G31+G33</f>
         <v>90.523809523809518</v>
       </c>
-      <c r="H34" t="e">
-        <f t="shared" si="8"/>
+      <c r="H34">
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="I34" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I34" t="e">
-        <f t="shared" si="8"/>
+      <c r="J34" t="e">
+        <f t="shared" ref="J34" si="8">J31+J33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J34" t="e">
-        <f t="shared" ref="J34" si="9">J31+J33</f>
+      <c r="K34">
+        <f t="shared" ref="K34" si="9">K31+K33</f>
+        <v>94.1</v>
+      </c>
+      <c r="L34" t="e">
+        <f t="shared" ref="L34" si="10">L31+L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K34">
-        <f t="shared" ref="K34" si="10">K31+K33</f>
-        <v>94.1</v>
-      </c>
-      <c r="L34" t="e">
-        <f t="shared" ref="L34" si="11">L31+L33</f>
+      <c r="M34" t="e">
+        <f t="shared" ref="M34" si="11">M31+M33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M34" t="e">
-        <f t="shared" ref="M34" si="12">M31+M33</f>
-        <v>#DIV/0!</v>
-      </c>
       <c r="N34" t="e">
-        <f t="shared" ref="N34" si="13">N31+N33</f>
+        <f t="shared" ref="N34" si="12">N31+N33</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2781,91 +2843,91 @@
         <v>76</v>
       </c>
       <c r="B53">
-        <f t="shared" ref="B53:W53" si="14">SUM(B38:B52)</f>
+        <f t="shared" ref="B53:W53" si="13">SUM(B38:B52)</f>
         <v>100</v>
       </c>
       <c r="C53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>93</v>
       </c>
       <c r="D53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>81</v>
       </c>
       <c r="E53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>97</v>
       </c>
       <c r="F53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>98</v>
       </c>
       <c r="G53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>76</v>
       </c>
       <c r="H53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>94</v>
       </c>
       <c r="I53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>94</v>
       </c>
       <c r="J53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>85</v>
       </c>
       <c r="K53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>92</v>
       </c>
       <c r="L53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>93</v>
       </c>
       <c r="M53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="N53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>51</v>
       </c>
       <c r="O53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>78</v>
       </c>
       <c r="P53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>94</v>
       </c>
       <c r="R53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="S53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>90</v>
       </c>
       <c r="T53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>86</v>
       </c>
       <c r="U53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>78</v>
       </c>
       <c r="V53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>72</v>
       </c>
       <c r="W53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
@@ -3936,91 +3998,91 @@
         <v>76</v>
       </c>
       <c r="B70">
-        <f t="shared" ref="B70:W70" si="15">SUM(B56:B69)</f>
+        <f t="shared" ref="B70:W70" si="14">SUM(B56:B69)</f>
         <v>100</v>
       </c>
       <c r="C70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>93</v>
       </c>
       <c r="D70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>87</v>
       </c>
       <c r="E70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>98</v>
       </c>
       <c r="F70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>99</v>
       </c>
       <c r="G70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>86</v>
       </c>
       <c r="H70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>90</v>
       </c>
       <c r="I70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
       <c r="J70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>85</v>
       </c>
       <c r="K70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>95</v>
       </c>
       <c r="L70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>94</v>
       </c>
       <c r="M70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>90</v>
       </c>
       <c r="N70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>72</v>
       </c>
       <c r="O70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>88</v>
       </c>
       <c r="P70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
       <c r="R70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>65</v>
       </c>
       <c r="S70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>81</v>
       </c>
       <c r="T70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>93</v>
       </c>
       <c r="U70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>81</v>
       </c>
       <c r="V70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>86</v>
       </c>
       <c r="W70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>17</v>
       </c>
     </row>
@@ -4099,6 +4161,63 @@
       <c r="B73">
         <v>10</v>
       </c>
+      <c r="C73">
+        <v>10</v>
+      </c>
+      <c r="D73">
+        <v>9</v>
+      </c>
+      <c r="E73">
+        <v>9</v>
+      </c>
+      <c r="F73">
+        <v>10</v>
+      </c>
+      <c r="G73">
+        <v>3</v>
+      </c>
+      <c r="H73">
+        <v>10</v>
+      </c>
+      <c r="I73">
+        <v>10</v>
+      </c>
+      <c r="J73">
+        <v>8</v>
+      </c>
+      <c r="K73">
+        <v>6</v>
+      </c>
+      <c r="L73">
+        <v>10</v>
+      </c>
+      <c r="M73">
+        <v>9</v>
+      </c>
+      <c r="N73">
+        <v>3</v>
+      </c>
+      <c r="O73">
+        <v>7</v>
+      </c>
+      <c r="P73">
+        <v>10</v>
+      </c>
+      <c r="Q73">
+        <v>10</v>
+      </c>
+      <c r="S73">
+        <v>9</v>
+      </c>
+      <c r="T73">
+        <v>7</v>
+      </c>
+      <c r="U73">
+        <v>9</v>
+      </c>
+      <c r="V73">
+        <v>8</v>
+      </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74">
@@ -4107,6 +4226,63 @@
       <c r="B74">
         <v>8</v>
       </c>
+      <c r="C74">
+        <v>8</v>
+      </c>
+      <c r="D74">
+        <v>7</v>
+      </c>
+      <c r="E74">
+        <v>8</v>
+      </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
+      <c r="G74">
+        <v>6</v>
+      </c>
+      <c r="H74">
+        <v>8</v>
+      </c>
+      <c r="I74">
+        <v>8</v>
+      </c>
+      <c r="J74">
+        <v>6</v>
+      </c>
+      <c r="K74">
+        <v>6</v>
+      </c>
+      <c r="L74">
+        <v>7</v>
+      </c>
+      <c r="M74">
+        <v>8</v>
+      </c>
+      <c r="N74">
+        <v>5</v>
+      </c>
+      <c r="O74">
+        <v>5</v>
+      </c>
+      <c r="P74">
+        <v>8</v>
+      </c>
+      <c r="Q74">
+        <v>8</v>
+      </c>
+      <c r="S74">
+        <v>8</v>
+      </c>
+      <c r="T74">
+        <v>5</v>
+      </c>
+      <c r="U74">
+        <v>6</v>
+      </c>
+      <c r="V74">
+        <v>8</v>
+      </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
@@ -4115,6 +4291,63 @@
       <c r="B75">
         <v>8</v>
       </c>
+      <c r="C75">
+        <v>6</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75">
+        <v>8</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75">
+        <v>3</v>
+      </c>
+      <c r="H75">
+        <v>8</v>
+      </c>
+      <c r="I75">
+        <v>6</v>
+      </c>
+      <c r="J75">
+        <v>7</v>
+      </c>
+      <c r="K75">
+        <v>8</v>
+      </c>
+      <c r="L75">
+        <v>6</v>
+      </c>
+      <c r="M75">
+        <v>6</v>
+      </c>
+      <c r="N75">
+        <v>4</v>
+      </c>
+      <c r="O75">
+        <v>8</v>
+      </c>
+      <c r="P75">
+        <v>8</v>
+      </c>
+      <c r="Q75">
+        <v>5</v>
+      </c>
+      <c r="S75">
+        <v>8</v>
+      </c>
+      <c r="T75">
+        <v>6</v>
+      </c>
+      <c r="U75">
+        <v>4</v>
+      </c>
+      <c r="V75">
+        <v>6</v>
+      </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
@@ -4123,6 +4356,63 @@
       <c r="B76">
         <v>4</v>
       </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <v>4</v>
+      </c>
+      <c r="G76">
+        <v>4</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
+      </c>
+      <c r="J76">
+        <v>4</v>
+      </c>
+      <c r="K76">
+        <v>4</v>
+      </c>
+      <c r="L76">
+        <v>4</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>3</v>
+      </c>
+      <c r="O76">
+        <v>4</v>
+      </c>
+      <c r="P76">
+        <v>4</v>
+      </c>
+      <c r="Q76">
+        <v>4</v>
+      </c>
+      <c r="S76">
+        <v>4</v>
+      </c>
+      <c r="T76">
+        <v>4</v>
+      </c>
+      <c r="U76">
+        <v>4</v>
+      </c>
+      <c r="V76">
+        <v>4</v>
+      </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
@@ -4131,6 +4421,63 @@
       <c r="B77">
         <v>5</v>
       </c>
+      <c r="C77">
+        <v>4</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>5</v>
+      </c>
+      <c r="G77">
+        <v>4</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+      <c r="I77">
+        <v>5</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77">
+        <v>5</v>
+      </c>
+      <c r="L77">
+        <v>5</v>
+      </c>
+      <c r="M77">
+        <v>4</v>
+      </c>
+      <c r="N77">
+        <v>2</v>
+      </c>
+      <c r="O77">
+        <v>4</v>
+      </c>
+      <c r="P77">
+        <v>5</v>
+      </c>
+      <c r="Q77">
+        <v>5</v>
+      </c>
+      <c r="S77">
+        <v>4</v>
+      </c>
+      <c r="T77">
+        <v>4</v>
+      </c>
+      <c r="U77">
+        <v>3</v>
+      </c>
+      <c r="V77">
+        <v>3</v>
+      </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
@@ -4138,6 +4485,63 @@
       </c>
       <c r="B78">
         <v>3</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>3</v>
+      </c>
+      <c r="K78">
+        <v>3</v>
+      </c>
+      <c r="L78">
+        <v>3</v>
+      </c>
+      <c r="M78">
+        <v>3</v>
+      </c>
+      <c r="N78">
+        <v>3</v>
+      </c>
+      <c r="O78">
+        <v>2</v>
+      </c>
+      <c r="P78">
+        <v>3</v>
+      </c>
+      <c r="Q78">
+        <v>3</v>
+      </c>
+      <c r="S78">
+        <v>3</v>
+      </c>
+      <c r="T78">
+        <v>3</v>
+      </c>
+      <c r="U78">
+        <v>3</v>
+      </c>
+      <c r="V78">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.2">
@@ -4147,12 +4551,126 @@
       <c r="B79">
         <v>10</v>
       </c>
+      <c r="C79">
+        <v>10</v>
+      </c>
+      <c r="D79">
+        <v>10</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <v>8</v>
+      </c>
+      <c r="H79">
+        <v>10</v>
+      </c>
+      <c r="I79">
+        <v>10</v>
+      </c>
+      <c r="J79">
+        <v>10</v>
+      </c>
+      <c r="K79">
+        <v>10</v>
+      </c>
+      <c r="L79">
+        <v>10</v>
+      </c>
+      <c r="M79">
+        <v>10</v>
+      </c>
+      <c r="N79">
+        <v>4</v>
+      </c>
+      <c r="O79">
+        <v>10</v>
+      </c>
+      <c r="P79">
+        <v>10</v>
+      </c>
+      <c r="Q79">
+        <v>10</v>
+      </c>
+      <c r="S79">
+        <v>8</v>
+      </c>
+      <c r="T79">
+        <v>10</v>
+      </c>
+      <c r="U79">
+        <v>10</v>
+      </c>
+      <c r="V79">
+        <v>10</v>
+      </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>8</v>
       </c>
       <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80">
+        <v>7</v>
+      </c>
+      <c r="E80">
+        <v>8</v>
+      </c>
+      <c r="F80">
+        <v>8</v>
+      </c>
+      <c r="G80">
+        <v>8</v>
+      </c>
+      <c r="H80">
+        <v>6</v>
+      </c>
+      <c r="I80">
+        <v>8</v>
+      </c>
+      <c r="J80">
+        <v>5</v>
+      </c>
+      <c r="K80">
+        <v>8</v>
+      </c>
+      <c r="L80">
+        <v>8</v>
+      </c>
+      <c r="M80">
+        <v>8</v>
+      </c>
+      <c r="N80">
+        <v>4</v>
+      </c>
+      <c r="O80">
+        <v>6</v>
+      </c>
+      <c r="P80">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>8</v>
+      </c>
+      <c r="S80">
+        <v>8</v>
+      </c>
+      <c r="T80">
+        <v>8</v>
+      </c>
+      <c r="U80">
+        <v>8</v>
+      </c>
+      <c r="V80">
         <v>8</v>
       </c>
     </row>
@@ -4163,6 +4681,63 @@
       <c r="B81">
         <v>5</v>
       </c>
+      <c r="C81">
+        <v>4</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+      <c r="E81">
+        <v>5</v>
+      </c>
+      <c r="F81">
+        <v>5</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>4</v>
+      </c>
+      <c r="I81">
+        <v>5</v>
+      </c>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81">
+        <v>4</v>
+      </c>
+      <c r="L81">
+        <v>5</v>
+      </c>
+      <c r="M81">
+        <v>4</v>
+      </c>
+      <c r="N81">
+        <v>5</v>
+      </c>
+      <c r="O81">
+        <v>5</v>
+      </c>
+      <c r="P81">
+        <v>5</v>
+      </c>
+      <c r="Q81">
+        <v>5</v>
+      </c>
+      <c r="S81">
+        <v>5</v>
+      </c>
+      <c r="T81">
+        <v>5</v>
+      </c>
+      <c r="U81">
+        <v>5</v>
+      </c>
+      <c r="V81">
+        <v>5</v>
+      </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82">
@@ -4171,6 +4746,63 @@
       <c r="B82">
         <v>8</v>
       </c>
+      <c r="C82">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>8</v>
+      </c>
+      <c r="E82">
+        <v>6</v>
+      </c>
+      <c r="F82">
+        <v>8</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>8</v>
+      </c>
+      <c r="I82">
+        <v>8</v>
+      </c>
+      <c r="J82">
+        <v>7</v>
+      </c>
+      <c r="K82">
+        <v>8</v>
+      </c>
+      <c r="L82">
+        <v>8</v>
+      </c>
+      <c r="M82">
+        <v>8</v>
+      </c>
+      <c r="N82">
+        <v>4</v>
+      </c>
+      <c r="O82">
+        <v>7</v>
+      </c>
+      <c r="P82">
+        <v>8</v>
+      </c>
+      <c r="Q82">
+        <v>8</v>
+      </c>
+      <c r="S82">
+        <v>8</v>
+      </c>
+      <c r="T82">
+        <v>8</v>
+      </c>
+      <c r="U82">
+        <v>8</v>
+      </c>
+      <c r="V82">
+        <v>7</v>
+      </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83">
@@ -4179,6 +4811,63 @@
       <c r="B83">
         <v>6</v>
       </c>
+      <c r="C83">
+        <v>4</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <v>6</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
+      </c>
+      <c r="G83">
+        <v>5</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
+      </c>
+      <c r="I83">
+        <v>6</v>
+      </c>
+      <c r="J83">
+        <v>3</v>
+      </c>
+      <c r="K83">
+        <v>6</v>
+      </c>
+      <c r="L83">
+        <v>5</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83">
+        <v>4</v>
+      </c>
+      <c r="O83">
+        <v>4</v>
+      </c>
+      <c r="P83">
+        <v>6</v>
+      </c>
+      <c r="Q83">
+        <v>6</v>
+      </c>
+      <c r="S83">
+        <v>5</v>
+      </c>
+      <c r="T83">
+        <v>6</v>
+      </c>
+      <c r="U83">
+        <v>4</v>
+      </c>
+      <c r="V83">
+        <v>6</v>
+      </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84">
@@ -4187,6 +4876,63 @@
       <c r="B84">
         <v>8</v>
       </c>
+      <c r="C84">
+        <v>5</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84">
+        <v>8</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>8</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>6</v>
+      </c>
+      <c r="L84">
+        <v>8</v>
+      </c>
+      <c r="M84">
+        <v>3</v>
+      </c>
+      <c r="N84">
+        <v>5</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>8</v>
+      </c>
+      <c r="Q84">
+        <v>7</v>
+      </c>
+      <c r="S84">
+        <v>5</v>
+      </c>
+      <c r="T84">
+        <v>5</v>
+      </c>
+      <c r="U84">
+        <v>5</v>
+      </c>
+      <c r="V84">
+        <v>3</v>
+      </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85">
@@ -4195,6 +4941,63 @@
       <c r="B85">
         <v>12</v>
       </c>
+      <c r="C85">
+        <v>11</v>
+      </c>
+      <c r="D85">
+        <v>8</v>
+      </c>
+      <c r="E85">
+        <v>12</v>
+      </c>
+      <c r="F85">
+        <v>12</v>
+      </c>
+      <c r="G85">
+        <v>7</v>
+      </c>
+      <c r="H85">
+        <v>11</v>
+      </c>
+      <c r="I85">
+        <v>12</v>
+      </c>
+      <c r="J85">
+        <v>7</v>
+      </c>
+      <c r="K85">
+        <v>10</v>
+      </c>
+      <c r="L85">
+        <v>12</v>
+      </c>
+      <c r="M85">
+        <v>11</v>
+      </c>
+      <c r="N85">
+        <v>7</v>
+      </c>
+      <c r="O85">
+        <v>8</v>
+      </c>
+      <c r="P85">
+        <v>12</v>
+      </c>
+      <c r="Q85">
+        <v>12</v>
+      </c>
+      <c r="S85">
+        <v>10</v>
+      </c>
+      <c r="T85">
+        <v>10</v>
+      </c>
+      <c r="U85">
+        <v>9</v>
+      </c>
+      <c r="V85">
+        <v>11</v>
+      </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86">
@@ -4203,98 +5006,217 @@
       <c r="B86">
         <v>5</v>
       </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>5</v>
+      </c>
+      <c r="I86">
+        <v>5</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+      <c r="K86">
+        <v>5</v>
+      </c>
+      <c r="L86">
+        <v>5</v>
+      </c>
+      <c r="M86">
+        <v>4</v>
+      </c>
+      <c r="N86">
+        <v>2</v>
+      </c>
+      <c r="O86">
+        <v>5</v>
+      </c>
+      <c r="P86">
+        <v>5</v>
+      </c>
+      <c r="Q86">
+        <v>5</v>
+      </c>
+      <c r="S86">
+        <v>5</v>
+      </c>
+      <c r="T86">
+        <v>5</v>
+      </c>
+      <c r="U86">
+        <v>4</v>
+      </c>
+      <c r="V86">
+        <v>5</v>
+      </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B87">
-        <f t="shared" ref="B87:W87" si="16">SUM(B73:B86)</f>
+        <f t="shared" ref="B87:W87" si="15">SUM(B73:B86)</f>
         <v>100</v>
       </c>
       <c r="C87">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
+        <v>87</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="15"/>
+        <v>72</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="15"/>
+        <v>89</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="15"/>
+        <v>100</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="15"/>
+        <v>53</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="15"/>
+        <v>84</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="15"/>
+        <v>98</v>
+      </c>
+      <c r="J87">
+        <f t="shared" si="15"/>
+        <v>72</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="15"/>
+        <v>89</v>
+      </c>
+      <c r="L87">
+        <f t="shared" si="15"/>
+        <v>96</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="15"/>
+        <v>86</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="15"/>
+        <v>55</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="15"/>
+        <v>76</v>
+      </c>
+      <c r="P87">
+        <f t="shared" si="15"/>
+        <v>100</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="15"/>
+        <v>96</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="D87">
-        <f t="shared" si="16"/>
+      <c r="S87">
+        <f t="shared" si="15"/>
+        <v>90</v>
+      </c>
+      <c r="T87">
+        <f t="shared" si="15"/>
+        <v>86</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="15"/>
+        <v>82</v>
+      </c>
+      <c r="V87">
+        <f t="shared" si="15"/>
+        <v>85</v>
+      </c>
+      <c r="W87">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="E87">
-        <f t="shared" si="16"/>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C89">
+        <v>87</v>
+      </c>
+      <c r="D89">
+        <v>72</v>
+      </c>
+      <c r="E89">
+        <v>89</v>
+      </c>
+      <c r="F89">
+        <v>100</v>
+      </c>
+      <c r="G89">
+        <v>53</v>
+      </c>
+      <c r="H89">
+        <v>84</v>
+      </c>
+      <c r="I89">
+        <v>98</v>
+      </c>
+      <c r="J89">
+        <v>72</v>
+      </c>
+      <c r="K89">
+        <v>89</v>
+      </c>
+      <c r="L89">
+        <v>96</v>
+      </c>
+      <c r="M89">
+        <v>86</v>
+      </c>
+      <c r="N89">
+        <v>55</v>
+      </c>
+      <c r="O89">
+        <v>76</v>
+      </c>
+      <c r="P89">
+        <v>100</v>
+      </c>
+      <c r="Q89">
+        <v>96</v>
+      </c>
+      <c r="R89">
         <v>0</v>
       </c>
-      <c r="F87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="S87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <f t="shared" si="16"/>
-        <v>0</v>
+      <c r="S89">
+        <v>90</v>
+      </c>
+      <c r="T89">
+        <v>86</v>
+      </c>
+      <c r="U89">
+        <v>82</v>
+      </c>
+      <c r="V89">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C56DEF-8716-6D46-845E-3576BE3C7B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25180" yWindow="2040" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16980" yWindow="780" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C56DEF-8716-6D46-845E-3576BE3C7B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81413555-8544-9641-90C2-90117066DF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16980" yWindow="780" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10740" yWindow="780" windowWidth="23980" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="104">
   <si>
     <t>First name</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>Grade</t>
+  </si>
+  <si>
+    <t>Class eval</t>
+  </si>
+  <si>
+    <t>Survey</t>
   </si>
 </sst>
 </file>
@@ -719,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:W91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
@@ -1575,12 +1581,11 @@
         <v>85.523809523809518</v>
       </c>
       <c r="H31">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(H5:H24,H28:H29)</f>
         <v>84</v>
       </c>
-      <c r="I31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+      <c r="I31">
+        <v>85</v>
       </c>
       <c r="J31" t="e">
         <f t="shared" ref="J31:N31" si="4">AVERAGE(J5:J24,J28:J29)</f>
@@ -1666,403 +1671,289 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="E35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="E36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <f>F31+F33</f>
         <v>89.952380952380949</v>
       </c>
-      <c r="G34">
-        <f t="shared" ref="G34:I34" si="7">G31+G33</f>
+      <c r="G36">
+        <f t="shared" ref="G36:I36" si="7">G31+G33</f>
         <v>90.523809523809518</v>
       </c>
-      <c r="H34">
+      <c r="H36">
         <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="I34" t="e">
-        <f t="shared" si="7"/>
+      <c r="I36">
+        <f>I31+SUM(I33:I35)</f>
+        <v>85</v>
+      </c>
+      <c r="J36" t="e">
+        <f t="shared" ref="J36" si="8">J31+J33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J34" t="e">
-        <f t="shared" ref="J34" si="8">J31+J33</f>
+      <c r="K36">
+        <f t="shared" ref="K36" si="9">K31+K33</f>
+        <v>94.1</v>
+      </c>
+      <c r="L36" t="e">
+        <f t="shared" ref="L36" si="10">L31+L33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K34">
-        <f t="shared" ref="K34" si="9">K31+K33</f>
-        <v>94.1</v>
-      </c>
-      <c r="L34" t="e">
-        <f t="shared" ref="L34" si="10">L31+L33</f>
+      <c r="M36" t="e">
+        <f t="shared" ref="M36" si="11">M31+M33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M34" t="e">
-        <f t="shared" ref="M34" si="11">M31+M33</f>
+      <c r="N36" t="e">
+        <f t="shared" ref="N36" si="12">N31+N33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N34" t="e">
-        <f t="shared" ref="N34" si="12">N31+N33</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K39" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="M39" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="N39" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O37" s="1" t="s">
+      <c r="O39" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="P39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q37" s="1" t="s">
+      <c r="Q39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R37" s="1" t="s">
+      <c r="R39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S37" s="1" t="s">
+      <c r="S39" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T37" s="1" t="s">
+      <c r="T39" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U37" s="1" t="s">
+      <c r="U39" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="V37" s="1" t="s">
+      <c r="V39" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W37" s="1" t="s">
+      <c r="W39" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>1</v>
-      </c>
-      <c r="B38">
-        <v>12</v>
-      </c>
-      <c r="C38">
-        <v>10</v>
-      </c>
-      <c r="D38">
-        <v>9</v>
-      </c>
-      <c r="E38">
-        <v>10</v>
-      </c>
-      <c r="F38">
-        <v>11</v>
-      </c>
-      <c r="G38">
-        <v>11</v>
-      </c>
-      <c r="H38">
-        <v>12</v>
-      </c>
-      <c r="I38">
-        <v>12</v>
-      </c>
-      <c r="J38">
-        <v>10</v>
-      </c>
-      <c r="K38">
-        <v>12</v>
-      </c>
-      <c r="L38">
-        <v>11</v>
-      </c>
-      <c r="M38">
-        <v>12</v>
-      </c>
-      <c r="N38">
-        <v>11</v>
-      </c>
-      <c r="O38">
-        <v>7</v>
-      </c>
-      <c r="P38">
-        <v>12</v>
-      </c>
-      <c r="Q38">
-        <v>11</v>
-      </c>
-      <c r="R38">
-        <v>6</v>
-      </c>
-      <c r="S38">
-        <v>12</v>
-      </c>
-      <c r="T38">
-        <v>6</v>
-      </c>
-      <c r="U38">
-        <v>11</v>
-      </c>
-      <c r="V38">
-        <v>9</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>2</v>
-      </c>
-      <c r="B39">
-        <v>18</v>
-      </c>
-      <c r="C39">
-        <v>18</v>
-      </c>
-      <c r="D39">
-        <v>18</v>
-      </c>
-      <c r="E39">
-        <v>18</v>
-      </c>
-      <c r="F39">
-        <v>18</v>
-      </c>
-      <c r="G39">
-        <v>14</v>
-      </c>
-      <c r="H39">
-        <v>16</v>
-      </c>
-      <c r="I39">
-        <v>16</v>
-      </c>
-      <c r="J39">
-        <v>18</v>
-      </c>
-      <c r="K39">
-        <v>18</v>
-      </c>
-      <c r="L39">
-        <v>16</v>
-      </c>
-      <c r="M39">
-        <v>18</v>
-      </c>
-      <c r="N39">
-        <v>17</v>
-      </c>
-      <c r="O39">
-        <v>18</v>
-      </c>
-      <c r="P39">
-        <v>18</v>
-      </c>
-      <c r="Q39">
-        <v>16</v>
-      </c>
-      <c r="R39">
-        <v>14</v>
-      </c>
-      <c r="S39">
-        <v>18</v>
-      </c>
-      <c r="T39">
-        <v>14</v>
-      </c>
-      <c r="U39">
-        <v>10</v>
-      </c>
-      <c r="V39">
-        <v>6</v>
-      </c>
-      <c r="W39">
-        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="F40">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>11</v>
+      </c>
+      <c r="H40">
+        <v>12</v>
+      </c>
+      <c r="I40">
+        <v>12</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+      <c r="K40">
+        <v>12</v>
+      </c>
+      <c r="L40">
+        <v>11</v>
+      </c>
+      <c r="M40">
+        <v>12</v>
+      </c>
+      <c r="N40">
+        <v>11</v>
+      </c>
+      <c r="O40">
         <v>7</v>
       </c>
-      <c r="F40">
-        <v>8</v>
-      </c>
-      <c r="G40">
-        <v>6</v>
-      </c>
-      <c r="H40">
-        <v>7</v>
-      </c>
-      <c r="I40">
-        <v>6</v>
-      </c>
-      <c r="J40">
-        <v>4</v>
-      </c>
-      <c r="K40">
-        <v>7</v>
-      </c>
-      <c r="L40">
-        <v>5</v>
-      </c>
-      <c r="M40">
-        <v>8</v>
-      </c>
-      <c r="N40">
-        <v>8</v>
-      </c>
-      <c r="O40">
-        <v>6</v>
-      </c>
       <c r="P40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q40">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S40">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H41">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K41">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="Q41">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="S41">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V41">
         <v>6</v>
       </c>
       <c r="W41">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -2071,129 +1962,129 @@
         <v>6</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I42">
         <v>6</v>
       </c>
       <c r="J42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L42">
         <v>5</v>
       </c>
       <c r="M42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N43">
         <v>4</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>5</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W43">
         <v>1</v>
@@ -2201,291 +2092,291 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O44">
         <v>5</v>
       </c>
       <c r="P44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>6</v>
       </c>
       <c r="V44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G45">
+        <v>5</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45">
+        <v>5</v>
+      </c>
+      <c r="L45">
+        <v>5</v>
+      </c>
+      <c r="M45">
+        <v>5</v>
+      </c>
+      <c r="N45">
+        <v>4</v>
+      </c>
+      <c r="O45">
+        <v>4</v>
+      </c>
+      <c r="P45">
+        <v>5</v>
+      </c>
+      <c r="Q45">
+        <v>5</v>
+      </c>
+      <c r="R45">
+        <v>3</v>
+      </c>
+      <c r="S45">
+        <v>5</v>
+      </c>
+      <c r="T45">
+        <v>5</v>
+      </c>
+      <c r="U45">
+        <v>5</v>
+      </c>
+      <c r="V45">
+        <v>3</v>
+      </c>
+      <c r="W45">
         <v>1</v>
-      </c>
-      <c r="H45">
-        <v>4</v>
-      </c>
-      <c r="I45">
-        <v>3</v>
-      </c>
-      <c r="J45">
-        <v>3</v>
-      </c>
-      <c r="K45">
-        <v>4</v>
-      </c>
-      <c r="L45">
-        <v>4</v>
-      </c>
-      <c r="M45">
-        <v>4</v>
-      </c>
-      <c r="N45">
-        <v>3</v>
-      </c>
-      <c r="O45">
-        <v>2</v>
-      </c>
-      <c r="P45">
-        <v>4</v>
-      </c>
-      <c r="Q45">
-        <v>4</v>
-      </c>
-      <c r="R45">
-        <v>3</v>
-      </c>
-      <c r="S45">
-        <v>3</v>
-      </c>
-      <c r="T45">
-        <v>4</v>
-      </c>
-      <c r="U45">
-        <v>2</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <v>8</v>
+      </c>
+      <c r="G46">
+        <v>8</v>
+      </c>
+      <c r="H46">
+        <v>8</v>
+      </c>
+      <c r="I46">
+        <v>8</v>
+      </c>
+      <c r="J46">
+        <v>8</v>
+      </c>
+      <c r="K46">
+        <v>7</v>
+      </c>
+      <c r="L46">
+        <v>8</v>
+      </c>
+      <c r="M46">
+        <v>8</v>
+      </c>
+      <c r="N46">
+        <v>4</v>
+      </c>
+      <c r="O46">
+        <v>5</v>
+      </c>
+      <c r="P46">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>8</v>
+      </c>
+      <c r="R46">
+        <v>5</v>
+      </c>
+      <c r="S46">
+        <v>7</v>
+      </c>
+      <c r="T46">
+        <v>8</v>
+      </c>
+      <c r="U46">
+        <v>6</v>
+      </c>
+      <c r="V46">
+        <v>8</v>
+      </c>
+      <c r="W46">
         <v>1</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-      <c r="F46">
-        <v>4</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46">
-        <v>3</v>
-      </c>
-      <c r="I46">
-        <v>4</v>
-      </c>
-      <c r="J46">
-        <v>3</v>
-      </c>
-      <c r="K46">
-        <v>2</v>
-      </c>
-      <c r="L46">
-        <v>4</v>
-      </c>
-      <c r="M46">
-        <v>4</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>4</v>
-      </c>
-      <c r="P46">
-        <v>4</v>
-      </c>
-      <c r="Q46">
-        <v>4</v>
-      </c>
-      <c r="R46">
-        <v>1</v>
-      </c>
-      <c r="S46">
-        <v>4</v>
-      </c>
-      <c r="T46">
-        <v>4</v>
-      </c>
-      <c r="U46">
-        <v>1</v>
-      </c>
-      <c r="V46">
-        <v>2</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N47">
+        <v>3</v>
+      </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
+      <c r="P47">
+        <v>4</v>
+      </c>
+      <c r="Q47">
+        <v>4</v>
+      </c>
+      <c r="R47">
+        <v>3</v>
+      </c>
+      <c r="S47">
+        <v>3</v>
+      </c>
+      <c r="T47">
+        <v>4</v>
+      </c>
+      <c r="U47">
+        <v>2</v>
+      </c>
+      <c r="V47">
         <v>0</v>
       </c>
-      <c r="O47">
-        <v>5</v>
-      </c>
-      <c r="P47">
-        <v>6</v>
-      </c>
-      <c r="Q47">
-        <v>6</v>
-      </c>
-      <c r="R47">
-        <v>6</v>
-      </c>
-      <c r="S47">
-        <v>6</v>
-      </c>
-      <c r="T47">
-        <v>6</v>
-      </c>
-      <c r="U47">
-        <v>4</v>
-      </c>
-      <c r="V47">
-        <v>6</v>
-      </c>
       <c r="W47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B48">
         <v>4</v>
@@ -2494,7 +2385,7 @@
         <v>4</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -2503,19 +2394,19 @@
         <v>4</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I48">
         <v>4</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48">
         <v>4</v>
@@ -2536,1103 +2427,1103 @@
         <v>4</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T48">
         <v>4</v>
       </c>
       <c r="U48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V48">
+        <v>2</v>
+      </c>
+      <c r="W48">
         <v>0</v>
-      </c>
-      <c r="W48">
-        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N49">
         <v>0</v>
       </c>
       <c r="O49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S49">
+        <v>6</v>
+      </c>
+      <c r="T49">
+        <v>6</v>
+      </c>
+      <c r="U49">
+        <v>4</v>
+      </c>
+      <c r="V49">
+        <v>6</v>
+      </c>
+      <c r="W49">
         <v>1</v>
-      </c>
-      <c r="T49">
-        <v>4</v>
-      </c>
-      <c r="U49">
-        <v>4</v>
-      </c>
-      <c r="V49">
-        <v>3</v>
-      </c>
-      <c r="W49">
-        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H51">
         <v>4</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51">
         <v>4</v>
       </c>
       <c r="K51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51">
         <v>0</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N52">
         <v>0</v>
       </c>
       <c r="O52">
+        <v>5</v>
+      </c>
+      <c r="P52">
+        <v>6</v>
+      </c>
+      <c r="Q52">
+        <v>6</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="P52">
-        <v>4</v>
-      </c>
-      <c r="Q52">
-        <v>4</v>
-      </c>
-      <c r="R52">
-        <v>4</v>
-      </c>
       <c r="S52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W52">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+      <c r="A53">
+        <v>14</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>4</v>
+      </c>
+      <c r="K53">
+        <v>5</v>
+      </c>
+      <c r="L53">
+        <v>5</v>
+      </c>
+      <c r="M53">
+        <v>5</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>4</v>
+      </c>
+      <c r="P53">
+        <v>5</v>
+      </c>
+      <c r="Q53">
+        <v>5</v>
+      </c>
+      <c r="R53">
+        <v>5</v>
+      </c>
+      <c r="S53">
+        <v>4</v>
+      </c>
+      <c r="T53">
+        <v>5</v>
+      </c>
+      <c r="U53">
+        <v>3</v>
+      </c>
+      <c r="V53">
+        <v>5</v>
+      </c>
+      <c r="W53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>15</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54">
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54">
+        <v>4</v>
+      </c>
+      <c r="M54">
+        <v>4</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54">
+        <v>4</v>
+      </c>
+      <c r="Q54">
+        <v>4</v>
+      </c>
+      <c r="R54">
+        <v>4</v>
+      </c>
+      <c r="S54">
+        <v>4</v>
+      </c>
+      <c r="T54">
+        <v>4</v>
+      </c>
+      <c r="U54">
+        <v>3</v>
+      </c>
+      <c r="V54">
+        <v>4</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B53">
-        <f t="shared" ref="B53:W53" si="13">SUM(B38:B52)</f>
+      <c r="B55">
+        <f t="shared" ref="B55:W55" si="13">SUM(B40:B54)</f>
         <v>100</v>
       </c>
-      <c r="C53">
+      <c r="C55">
         <f t="shared" si="13"/>
         <v>93</v>
       </c>
-      <c r="D53">
+      <c r="D55">
         <f t="shared" si="13"/>
         <v>81</v>
       </c>
-      <c r="E53">
+      <c r="E55">
         <f t="shared" si="13"/>
         <v>97</v>
       </c>
-      <c r="F53">
+      <c r="F55">
         <f t="shared" si="13"/>
         <v>98</v>
       </c>
-      <c r="G53">
+      <c r="G55">
         <f t="shared" si="13"/>
         <v>76</v>
       </c>
-      <c r="H53">
+      <c r="H55">
         <f t="shared" si="13"/>
         <v>94</v>
       </c>
-      <c r="I53">
+      <c r="I55">
         <f t="shared" si="13"/>
         <v>94</v>
       </c>
-      <c r="J53">
+      <c r="J55">
         <f t="shared" si="13"/>
         <v>85</v>
       </c>
-      <c r="K53">
+      <c r="K55">
         <f t="shared" si="13"/>
         <v>92</v>
       </c>
-      <c r="L53">
+      <c r="L55">
         <f t="shared" si="13"/>
         <v>93</v>
       </c>
-      <c r="M53">
+      <c r="M55">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="N53">
+      <c r="N55">
         <f t="shared" si="13"/>
         <v>51</v>
       </c>
-      <c r="O53">
+      <c r="O55">
         <f t="shared" si="13"/>
         <v>78</v>
       </c>
-      <c r="P53">
+      <c r="P55">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="Q53">
+      <c r="Q55">
         <f t="shared" si="13"/>
         <v>94</v>
       </c>
-      <c r="R53">
+      <c r="R55">
         <f t="shared" si="13"/>
         <v>70</v>
       </c>
-      <c r="S53">
+      <c r="S55">
         <f t="shared" si="13"/>
         <v>90</v>
       </c>
-      <c r="T53">
+      <c r="T55">
         <f t="shared" si="13"/>
         <v>86</v>
       </c>
-      <c r="U53">
+      <c r="U55">
         <f t="shared" si="13"/>
         <v>78</v>
       </c>
-      <c r="V53">
+      <c r="V55">
         <f t="shared" si="13"/>
         <v>72</v>
       </c>
-      <c r="W53">
+      <c r="W55">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K57" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L55" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N55" s="1" t="s">
+      <c r="N57" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O55" s="1" t="s">
+      <c r="O57" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P55" s="1" t="s">
+      <c r="P57" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q55" s="1" t="s">
+      <c r="Q57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R55" s="1" t="s">
+      <c r="R57" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S55" s="1" t="s">
+      <c r="S57" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T55" s="1" t="s">
+      <c r="T57" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U55" s="1" t="s">
+      <c r="U57" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="V55" s="1" t="s">
+      <c r="V57" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W55" s="1" t="s">
+      <c r="W57" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>1</v>
-      </c>
-      <c r="B56">
-        <v>10</v>
-      </c>
-      <c r="C56">
-        <v>10</v>
-      </c>
-      <c r="D56">
-        <v>10</v>
-      </c>
-      <c r="E56">
-        <v>10</v>
-      </c>
-      <c r="F56">
-        <v>10</v>
-      </c>
-      <c r="G56">
-        <v>6</v>
-      </c>
-      <c r="H56">
-        <v>9</v>
-      </c>
-      <c r="I56">
-        <v>10</v>
-      </c>
-      <c r="J56">
-        <v>9</v>
-      </c>
-      <c r="K56">
-        <v>10</v>
-      </c>
-      <c r="L56">
-        <v>9</v>
-      </c>
-      <c r="M56">
-        <v>10</v>
-      </c>
-      <c r="N56">
-        <v>7</v>
-      </c>
-      <c r="O56">
-        <v>10</v>
-      </c>
-      <c r="P56">
-        <v>10</v>
-      </c>
-      <c r="Q56">
-        <v>10</v>
-      </c>
-      <c r="R56">
-        <v>4</v>
-      </c>
-      <c r="S56">
-        <v>10</v>
-      </c>
-      <c r="T56">
-        <v>10</v>
-      </c>
-      <c r="U56">
-        <v>6</v>
-      </c>
-      <c r="V56">
-        <v>7</v>
-      </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>2</v>
-      </c>
-      <c r="B57">
-        <v>8</v>
-      </c>
-      <c r="C57">
-        <v>8</v>
-      </c>
-      <c r="D57">
-        <v>8</v>
-      </c>
-      <c r="E57">
-        <v>7</v>
-      </c>
-      <c r="F57">
-        <v>8</v>
-      </c>
-      <c r="G57">
-        <v>8</v>
-      </c>
-      <c r="H57">
-        <v>6</v>
-      </c>
-      <c r="I57">
-        <v>8</v>
-      </c>
-      <c r="J57">
-        <v>8</v>
-      </c>
-      <c r="K57">
-        <v>8</v>
-      </c>
-      <c r="L57">
-        <v>6</v>
-      </c>
-      <c r="M57">
-        <v>5</v>
-      </c>
-      <c r="N57">
-        <v>6</v>
-      </c>
-      <c r="O57">
-        <v>8</v>
-      </c>
-      <c r="P57">
-        <v>6</v>
-      </c>
-      <c r="Q57">
-        <v>8</v>
-      </c>
-      <c r="R57">
-        <v>6</v>
-      </c>
-      <c r="S57">
-        <v>8</v>
-      </c>
-      <c r="T57">
-        <v>8</v>
-      </c>
-      <c r="U57">
-        <v>8</v>
-      </c>
-      <c r="V57">
-        <v>8</v>
-      </c>
-      <c r="W57">
-        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G58">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H58">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J58">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L58">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N58">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R58">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S58">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="U58">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V58">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H59">
         <v>6</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L59">
         <v>6</v>
       </c>
       <c r="M59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N59">
         <v>6</v>
       </c>
       <c r="O59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P59">
         <v>6</v>
       </c>
       <c r="Q59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U59">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G60">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J60">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P60">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R60">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S60">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T60">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="U60">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V60">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61">
         <v>4</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R61">
         <v>4</v>
       </c>
       <c r="S61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V61">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W61">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62">
+        <v>8</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <v>8</v>
+      </c>
+      <c r="G62">
         <v>7</v>
       </c>
-      <c r="B62">
-        <v>8</v>
-      </c>
-      <c r="C62">
+      <c r="H62">
+        <v>8</v>
+      </c>
+      <c r="I62">
+        <v>8</v>
+      </c>
+      <c r="J62">
+        <v>8</v>
+      </c>
+      <c r="K62">
+        <v>8</v>
+      </c>
+      <c r="L62">
+        <v>8</v>
+      </c>
+      <c r="M62">
+        <v>8</v>
+      </c>
+      <c r="N62">
         <v>7</v>
       </c>
-      <c r="D62">
-        <v>6</v>
-      </c>
-      <c r="E62">
-        <v>8</v>
-      </c>
-      <c r="F62">
-        <v>8</v>
-      </c>
-      <c r="G62">
-        <v>6</v>
-      </c>
-      <c r="H62">
-        <v>5</v>
-      </c>
-      <c r="I62">
-        <v>8</v>
-      </c>
-      <c r="J62">
-        <v>6</v>
-      </c>
-      <c r="K62">
-        <v>8</v>
-      </c>
-      <c r="L62">
-        <v>8</v>
-      </c>
-      <c r="M62">
+      <c r="O62">
+        <v>8</v>
+      </c>
+      <c r="P62">
         <v>7</v>
       </c>
-      <c r="N62">
-        <v>4</v>
-      </c>
-      <c r="O62">
-        <v>5</v>
-      </c>
-      <c r="P62">
-        <v>8</v>
-      </c>
       <c r="Q62">
         <v>8</v>
       </c>
       <c r="R62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U62">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V62">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J63">
         <v>3</v>
       </c>
       <c r="K63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T63">
         <v>2</v>
       </c>
       <c r="U63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W63">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q64">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S64">
         <v>4</v>
       </c>
       <c r="T64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W64">
         <v>1</v>
@@ -3640,67 +3531,67 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K65">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N65">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q65">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T65">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V65">
         <v>3</v>
@@ -3711,126 +3602,126 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E66">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H66">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M66">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O66">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U66">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V66">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R67">
         <v>4</v>
@@ -3839,936 +3730,948 @@
         <v>3</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K68">
         <v>6</v>
       </c>
       <c r="L68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O68">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W68">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>4</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J69">
+        <v>4</v>
+      </c>
+      <c r="K69">
+        <v>4</v>
+      </c>
+      <c r="L69">
+        <v>4</v>
+      </c>
+      <c r="M69">
+        <v>3</v>
+      </c>
+      <c r="N69">
+        <v>3</v>
+      </c>
+      <c r="O69">
+        <v>4</v>
+      </c>
+      <c r="P69">
+        <v>3</v>
+      </c>
+      <c r="Q69">
+        <v>4</v>
+      </c>
+      <c r="R69">
+        <v>4</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="T69">
+        <v>4</v>
+      </c>
+      <c r="U69">
         <v>2</v>
       </c>
-      <c r="K69">
-        <v>4</v>
-      </c>
-      <c r="L69">
-        <v>3</v>
-      </c>
-      <c r="M69">
-        <v>6</v>
-      </c>
-      <c r="N69">
-        <v>2</v>
-      </c>
-      <c r="O69">
-        <v>4</v>
-      </c>
-      <c r="P69">
-        <v>6</v>
-      </c>
-      <c r="Q69">
-        <v>6</v>
-      </c>
-      <c r="R69">
-        <v>3</v>
-      </c>
-      <c r="S69">
-        <v>5</v>
-      </c>
-      <c r="T69">
-        <v>5</v>
-      </c>
-      <c r="U69">
-        <v>6</v>
-      </c>
       <c r="V69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W69">
         <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
+      <c r="A70">
+        <v>13</v>
+      </c>
+      <c r="B70">
+        <v>6</v>
+      </c>
+      <c r="C70">
+        <v>5</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70">
+        <v>6</v>
+      </c>
+      <c r="F70">
+        <v>6</v>
+      </c>
+      <c r="G70">
+        <v>6</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="J70">
+        <v>3</v>
+      </c>
+      <c r="K70">
+        <v>6</v>
+      </c>
+      <c r="L70">
+        <v>6</v>
+      </c>
+      <c r="M70">
+        <v>6</v>
+      </c>
+      <c r="N70">
+        <v>2</v>
+      </c>
+      <c r="O70">
+        <v>5</v>
+      </c>
+      <c r="P70">
+        <v>6</v>
+      </c>
+      <c r="Q70">
+        <v>6</v>
+      </c>
+      <c r="R70">
+        <v>2</v>
+      </c>
+      <c r="S70">
+        <v>4</v>
+      </c>
+      <c r="T70">
+        <v>6</v>
+      </c>
+      <c r="U70">
+        <v>6</v>
+      </c>
+      <c r="V70">
+        <v>6</v>
+      </c>
+      <c r="W70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>14</v>
+      </c>
+      <c r="B71">
+        <v>6</v>
+      </c>
+      <c r="C71">
+        <v>4</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71">
+        <v>6</v>
+      </c>
+      <c r="F71">
+        <v>6</v>
+      </c>
+      <c r="G71">
+        <v>6</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>6</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71">
+        <v>4</v>
+      </c>
+      <c r="L71">
+        <v>3</v>
+      </c>
+      <c r="M71">
+        <v>6</v>
+      </c>
+      <c r="N71">
+        <v>2</v>
+      </c>
+      <c r="O71">
+        <v>4</v>
+      </c>
+      <c r="P71">
+        <v>6</v>
+      </c>
+      <c r="Q71">
+        <v>6</v>
+      </c>
+      <c r="R71">
+        <v>3</v>
+      </c>
+      <c r="S71">
+        <v>5</v>
+      </c>
+      <c r="T71">
+        <v>5</v>
+      </c>
+      <c r="U71">
+        <v>6</v>
+      </c>
+      <c r="V71">
+        <v>5</v>
+      </c>
+      <c r="W71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B70">
-        <f t="shared" ref="B70:W70" si="14">SUM(B56:B69)</f>
+      <c r="B72">
+        <f t="shared" ref="B72:W72" si="14">SUM(B58:B71)</f>
         <v>100</v>
       </c>
-      <c r="C70">
+      <c r="C72">
         <f t="shared" si="14"/>
         <v>93</v>
       </c>
-      <c r="D70">
+      <c r="D72">
         <f t="shared" si="14"/>
         <v>87</v>
       </c>
-      <c r="E70">
+      <c r="E72">
         <f t="shared" si="14"/>
         <v>98</v>
       </c>
-      <c r="F70">
+      <c r="F72">
         <f t="shared" si="14"/>
         <v>99</v>
       </c>
-      <c r="G70">
+      <c r="G72">
         <f t="shared" si="14"/>
         <v>86</v>
       </c>
-      <c r="H70">
+      <c r="H72">
         <f t="shared" si="14"/>
         <v>90</v>
       </c>
-      <c r="I70">
+      <c r="I72">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="J70">
+      <c r="J72">
         <f t="shared" si="14"/>
         <v>85</v>
       </c>
-      <c r="K70">
+      <c r="K72">
         <f t="shared" si="14"/>
         <v>95</v>
       </c>
-      <c r="L70">
+      <c r="L72">
         <f t="shared" si="14"/>
         <v>94</v>
       </c>
-      <c r="M70">
+      <c r="M72">
         <f t="shared" si="14"/>
         <v>90</v>
       </c>
-      <c r="N70">
+      <c r="N72">
         <f t="shared" si="14"/>
         <v>72</v>
       </c>
-      <c r="O70">
+      <c r="O72">
         <f t="shared" si="14"/>
         <v>88</v>
       </c>
-      <c r="P70">
+      <c r="P72">
         <f t="shared" si="14"/>
         <v>96</v>
       </c>
-      <c r="Q70">
+      <c r="Q72">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="R70">
+      <c r="R72">
         <f t="shared" si="14"/>
         <v>65</v>
       </c>
-      <c r="S70">
+      <c r="S72">
         <f t="shared" si="14"/>
         <v>81</v>
       </c>
-      <c r="T70">
+      <c r="T72">
         <f t="shared" si="14"/>
         <v>93</v>
       </c>
-      <c r="U70">
+      <c r="U72">
         <f t="shared" si="14"/>
         <v>81</v>
       </c>
-      <c r="V70">
+      <c r="V72">
         <f t="shared" si="14"/>
         <v>86</v>
       </c>
-      <c r="W70">
+      <c r="W72">
         <f t="shared" si="14"/>
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B72" s="1" t="s">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I74" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L72" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="M74" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N72" s="1" t="s">
+      <c r="N74" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O72" s="1" t="s">
+      <c r="O74" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P72" s="1" t="s">
+      <c r="P74" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q72" s="1" t="s">
+      <c r="Q74" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R72" s="1" t="s">
+      <c r="R74" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S72" s="1" t="s">
+      <c r="S74" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T72" s="1" t="s">
+      <c r="T74" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U72" s="1" t="s">
+      <c r="U74" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="V72" s="1" t="s">
+      <c r="V74" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W72" s="1" t="s">
+      <c r="W74" s="1" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>1</v>
-      </c>
-      <c r="B73">
-        <v>10</v>
-      </c>
-      <c r="C73">
-        <v>10</v>
-      </c>
-      <c r="D73">
-        <v>9</v>
-      </c>
-      <c r="E73">
-        <v>9</v>
-      </c>
-      <c r="F73">
-        <v>10</v>
-      </c>
-      <c r="G73">
-        <v>3</v>
-      </c>
-      <c r="H73">
-        <v>10</v>
-      </c>
-      <c r="I73">
-        <v>10</v>
-      </c>
-      <c r="J73">
-        <v>8</v>
-      </c>
-      <c r="K73">
-        <v>6</v>
-      </c>
-      <c r="L73">
-        <v>10</v>
-      </c>
-      <c r="M73">
-        <v>9</v>
-      </c>
-      <c r="N73">
-        <v>3</v>
-      </c>
-      <c r="O73">
-        <v>7</v>
-      </c>
-      <c r="P73">
-        <v>10</v>
-      </c>
-      <c r="Q73">
-        <v>10</v>
-      </c>
-      <c r="S73">
-        <v>9</v>
-      </c>
-      <c r="T73">
-        <v>7</v>
-      </c>
-      <c r="U73">
-        <v>9</v>
-      </c>
-      <c r="V73">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>2</v>
-      </c>
-      <c r="B74">
-        <v>8</v>
-      </c>
-      <c r="C74">
-        <v>8</v>
-      </c>
-      <c r="D74">
-        <v>7</v>
-      </c>
-      <c r="E74">
-        <v>8</v>
-      </c>
-      <c r="F74">
-        <v>8</v>
-      </c>
-      <c r="G74">
-        <v>6</v>
-      </c>
-      <c r="H74">
-        <v>8</v>
-      </c>
-      <c r="I74">
-        <v>8</v>
-      </c>
-      <c r="J74">
-        <v>6</v>
-      </c>
-      <c r="K74">
-        <v>6</v>
-      </c>
-      <c r="L74">
-        <v>7</v>
-      </c>
-      <c r="M74">
-        <v>8</v>
-      </c>
-      <c r="N74">
-        <v>5</v>
-      </c>
-      <c r="O74">
-        <v>5</v>
-      </c>
-      <c r="P74">
-        <v>8</v>
-      </c>
-      <c r="Q74">
-        <v>8</v>
-      </c>
-      <c r="S74">
-        <v>8</v>
-      </c>
-      <c r="T74">
-        <v>5</v>
-      </c>
-      <c r="U74">
-        <v>6</v>
-      </c>
-      <c r="V74">
-        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B75">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E75">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G75">
         <v>3</v>
       </c>
       <c r="H75">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J75">
+        <v>8</v>
+      </c>
+      <c r="K75">
+        <v>6</v>
+      </c>
+      <c r="L75">
+        <v>10</v>
+      </c>
+      <c r="M75">
+        <v>9</v>
+      </c>
+      <c r="N75">
+        <v>3</v>
+      </c>
+      <c r="O75">
         <v>7</v>
       </c>
-      <c r="K75">
-        <v>8</v>
-      </c>
-      <c r="L75">
-        <v>6</v>
-      </c>
-      <c r="M75">
-        <v>6</v>
-      </c>
-      <c r="N75">
-        <v>4</v>
-      </c>
-      <c r="O75">
-        <v>8</v>
-      </c>
       <c r="P75">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q75">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S75">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U75">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V75">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V76">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K77">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P77">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q77">
         <v>5</v>
       </c>
       <c r="S77">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T77">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <v>3</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N78">
         <v>3</v>
       </c>
       <c r="O78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V78">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E79">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G79">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H79">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J79">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M79">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q79">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S79">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T79">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V79">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O80">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U80">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V80">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C81">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H81">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K81">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S81">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V81">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B82">
         <v>8</v>
       </c>
       <c r="C82">
+        <v>8</v>
+      </c>
+      <c r="D82">
         <v>7</v>
       </c>
-      <c r="D82">
-        <v>8</v>
-      </c>
       <c r="E82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F82">
         <v>8</v>
       </c>
       <c r="G82">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I82">
         <v>8</v>
       </c>
       <c r="J82">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K82">
         <v>8</v>
@@ -4783,7 +4686,7 @@
         <v>4</v>
       </c>
       <c r="O82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P82">
         <v>8</v>
@@ -4801,15 +4704,15 @@
         <v>8</v>
       </c>
       <c r="V82">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83">
         <v>4</v>
@@ -4818,25 +4721,25 @@
         <v>3</v>
       </c>
       <c r="E83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G83">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J83">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L83">
         <v>5</v>
@@ -4845,377 +4748,507 @@
         <v>4</v>
       </c>
       <c r="N83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S83">
         <v>5</v>
       </c>
       <c r="T83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V83">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B84">
         <v>8</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E84">
+        <v>6</v>
+      </c>
+      <c r="F84">
+        <v>8</v>
+      </c>
+      <c r="G84">
         <v>2</v>
       </c>
-      <c r="F84">
-        <v>8</v>
-      </c>
-      <c r="G84">
-        <v>1</v>
-      </c>
       <c r="H84">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I84">
         <v>8</v>
       </c>
       <c r="J84">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K84">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L84">
         <v>8</v>
       </c>
       <c r="M84">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O84">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P84">
         <v>8</v>
       </c>
       <c r="Q84">
+        <v>8</v>
+      </c>
+      <c r="S84">
+        <v>8</v>
+      </c>
+      <c r="T84">
+        <v>8</v>
+      </c>
+      <c r="U84">
+        <v>8</v>
+      </c>
+      <c r="V84">
         <v>7</v>
-      </c>
-      <c r="S84">
-        <v>5</v>
-      </c>
-      <c r="T84">
-        <v>5</v>
-      </c>
-      <c r="U84">
-        <v>5</v>
-      </c>
-      <c r="V84">
-        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C85">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D85">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G85">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H85">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J85">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K85">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L85">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M85">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N85">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q85">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S85">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U85">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V85">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86">
+        <v>12</v>
+      </c>
+      <c r="B86">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86">
+        <v>8</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+      <c r="I86">
+        <v>8</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>6</v>
+      </c>
+      <c r="L86">
+        <v>8</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>5</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+      <c r="P86">
+        <v>8</v>
+      </c>
+      <c r="Q86">
+        <v>7</v>
+      </c>
+      <c r="S86">
+        <v>5</v>
+      </c>
+      <c r="T86">
+        <v>5</v>
+      </c>
+      <c r="U86">
+        <v>5</v>
+      </c>
+      <c r="V86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>13</v>
+      </c>
+      <c r="B87">
+        <v>12</v>
+      </c>
+      <c r="C87">
+        <v>11</v>
+      </c>
+      <c r="D87">
+        <v>8</v>
+      </c>
+      <c r="E87">
+        <v>12</v>
+      </c>
+      <c r="F87">
+        <v>12</v>
+      </c>
+      <c r="G87">
+        <v>7</v>
+      </c>
+      <c r="H87">
+        <v>11</v>
+      </c>
+      <c r="I87">
+        <v>12</v>
+      </c>
+      <c r="J87">
+        <v>7</v>
+      </c>
+      <c r="K87">
+        <v>10</v>
+      </c>
+      <c r="L87">
+        <v>12</v>
+      </c>
+      <c r="M87">
+        <v>11</v>
+      </c>
+      <c r="N87">
+        <v>7</v>
+      </c>
+      <c r="O87">
+        <v>8</v>
+      </c>
+      <c r="P87">
+        <v>12</v>
+      </c>
+      <c r="Q87">
+        <v>12</v>
+      </c>
+      <c r="S87">
+        <v>10</v>
+      </c>
+      <c r="T87">
+        <v>10</v>
+      </c>
+      <c r="U87">
+        <v>9</v>
+      </c>
+      <c r="V87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A88">
         <v>14</v>
       </c>
-      <c r="B86">
-        <v>5</v>
-      </c>
-      <c r="C86">
-        <v>3</v>
-      </c>
-      <c r="D86">
-        <v>4</v>
-      </c>
-      <c r="E86">
-        <v>5</v>
-      </c>
-      <c r="F86">
-        <v>5</v>
-      </c>
-      <c r="G86">
+      <c r="B88">
+        <v>5</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88">
+        <v>5</v>
+      </c>
+      <c r="F88">
+        <v>5</v>
+      </c>
+      <c r="G88">
         <v>0</v>
       </c>
-      <c r="H86">
-        <v>5</v>
-      </c>
-      <c r="I86">
-        <v>5</v>
-      </c>
-      <c r="J86">
-        <v>3</v>
-      </c>
-      <c r="K86">
-        <v>5</v>
-      </c>
-      <c r="L86">
-        <v>5</v>
-      </c>
-      <c r="M86">
-        <v>4</v>
-      </c>
-      <c r="N86">
+      <c r="H88">
+        <v>5</v>
+      </c>
+      <c r="I88">
+        <v>5</v>
+      </c>
+      <c r="J88">
+        <v>3</v>
+      </c>
+      <c r="K88">
+        <v>5</v>
+      </c>
+      <c r="L88">
+        <v>5</v>
+      </c>
+      <c r="M88">
+        <v>4</v>
+      </c>
+      <c r="N88">
         <v>2</v>
       </c>
-      <c r="O86">
-        <v>5</v>
-      </c>
-      <c r="P86">
-        <v>5</v>
-      </c>
-      <c r="Q86">
-        <v>5</v>
-      </c>
-      <c r="S86">
-        <v>5</v>
-      </c>
-      <c r="T86">
-        <v>5</v>
-      </c>
-      <c r="U86">
-        <v>4</v>
-      </c>
-      <c r="V86">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
+      <c r="O88">
+        <v>5</v>
+      </c>
+      <c r="P88">
+        <v>5</v>
+      </c>
+      <c r="Q88">
+        <v>5</v>
+      </c>
+      <c r="S88">
+        <v>5</v>
+      </c>
+      <c r="T88">
+        <v>5</v>
+      </c>
+      <c r="U88">
+        <v>4</v>
+      </c>
+      <c r="V88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B87">
-        <f t="shared" ref="B87:W87" si="15">SUM(B73:B86)</f>
+      <c r="B89">
+        <f t="shared" ref="B89:W89" si="15">SUM(B75:B88)</f>
         <v>100</v>
       </c>
-      <c r="C87">
+      <c r="C89">
         <f t="shared" si="15"/>
         <v>87</v>
       </c>
-      <c r="D87">
+      <c r="D89">
         <f t="shared" si="15"/>
         <v>72</v>
       </c>
-      <c r="E87">
+      <c r="E89">
         <f t="shared" si="15"/>
         <v>89</v>
       </c>
-      <c r="F87">
+      <c r="F89">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
-      <c r="G87">
+      <c r="G89">
         <f t="shared" si="15"/>
         <v>53</v>
       </c>
-      <c r="H87">
+      <c r="H89">
         <f t="shared" si="15"/>
         <v>84</v>
       </c>
-      <c r="I87">
+      <c r="I89">
         <f t="shared" si="15"/>
         <v>98</v>
       </c>
-      <c r="J87">
+      <c r="J89">
         <f t="shared" si="15"/>
         <v>72</v>
       </c>
-      <c r="K87">
+      <c r="K89">
         <f t="shared" si="15"/>
         <v>89</v>
       </c>
-      <c r="L87">
+      <c r="L89">
         <f t="shared" si="15"/>
         <v>96</v>
       </c>
-      <c r="M87">
+      <c r="M89">
         <f t="shared" si="15"/>
         <v>86</v>
       </c>
-      <c r="N87">
+      <c r="N89">
         <f t="shared" si="15"/>
         <v>55</v>
       </c>
-      <c r="O87">
+      <c r="O89">
         <f t="shared" si="15"/>
         <v>76</v>
       </c>
-      <c r="P87">
+      <c r="P89">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
-      <c r="Q87">
+      <c r="Q89">
         <f t="shared" si="15"/>
         <v>96</v>
       </c>
-      <c r="R87">
+      <c r="R89">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S87">
+      <c r="S89">
         <f t="shared" si="15"/>
         <v>90</v>
       </c>
-      <c r="T87">
+      <c r="T89">
         <f t="shared" si="15"/>
         <v>86</v>
       </c>
-      <c r="U87">
+      <c r="U89">
         <f t="shared" si="15"/>
         <v>82</v>
       </c>
-      <c r="V87">
+      <c r="V89">
         <f t="shared" si="15"/>
         <v>85</v>
       </c>
-      <c r="W87">
+      <c r="W89">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="C89">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C91">
         <v>87</v>
       </c>
-      <c r="D89">
+      <c r="D91">
         <v>72</v>
       </c>
-      <c r="E89">
+      <c r="E91">
         <v>89</v>
       </c>
-      <c r="F89">
+      <c r="F91">
         <v>100</v>
       </c>
-      <c r="G89">
+      <c r="G91">
         <v>53</v>
       </c>
-      <c r="H89">
+      <c r="H91">
         <v>84</v>
       </c>
-      <c r="I89">
+      <c r="I91">
         <v>98</v>
       </c>
-      <c r="J89">
+      <c r="J91">
         <v>72</v>
       </c>
-      <c r="K89">
+      <c r="K91">
         <v>89</v>
       </c>
-      <c r="L89">
+      <c r="L91">
         <v>96</v>
       </c>
-      <c r="M89">
+      <c r="M91">
         <v>86</v>
       </c>
-      <c r="N89">
+      <c r="N91">
         <v>55</v>
       </c>
-      <c r="O89">
+      <c r="O91">
         <v>76</v>
       </c>
-      <c r="P89">
+      <c r="P91">
         <v>100</v>
       </c>
-      <c r="Q89">
+      <c r="Q91">
         <v>96</v>
       </c>
-      <c r="R89">
+      <c r="R91">
         <v>0</v>
       </c>
-      <c r="S89">
+      <c r="S91">
         <v>90</v>
       </c>
-      <c r="T89">
+      <c r="T91">
         <v>86</v>
       </c>
-      <c r="U89">
+      <c r="U91">
         <v>82</v>
       </c>
-      <c r="V89">
+      <c r="V91">
         <v>85</v>
       </c>
     </row>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05017CC7-97EB-6542-BE5E-47803A620C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B741F966-7B85-1E46-95A0-729F2A392049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10740" yWindow="780" windowWidth="27040" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21140" yWindow="4840" windowWidth="27200" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="104">
   <si>
     <t>First name</t>
   </si>
@@ -725,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:W104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
@@ -735,15 +735,6 @@
       <c r="I1">
         <v>0.16</v>
       </c>
-      <c r="J1">
-        <v>0.16</v>
-      </c>
-      <c r="K1">
-        <v>0.05</v>
-      </c>
-      <c r="L1">
-        <v>0.05</v>
-      </c>
       <c r="M1">
         <v>0.1</v>
       </c>
@@ -758,12 +749,18 @@
       <c r="H2">
         <v>0.16</v>
       </c>
+      <c r="J2">
+        <v>0.16</v>
+      </c>
       <c r="K2">
         <v>0.05</v>
       </c>
+      <c r="L2">
+        <v>0.05</v>
+      </c>
       <c r="N2">
         <f>SUM(F2:M2)</f>
-        <v>0.53</v>
+        <v>0.7400000000000001</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>101</v>
@@ -840,16 +837,22 @@
       <c r="H5">
         <v>87</v>
       </c>
+      <c r="J5">
+        <v>98</v>
+      </c>
       <c r="K5">
         <v>99</v>
       </c>
+      <c r="L5">
+        <v>98</v>
+      </c>
       <c r="O5">
         <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33+R5+S5)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
-        <v>51.510000000000005</v>
+        <v>72.09</v>
       </c>
       <c r="P5" s="2">
         <f>O5/$N$2</f>
-        <v>97.188679245283026</v>
+        <v>97.418918918918905</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -874,16 +877,25 @@
       <c r="H6">
         <v>72</v>
       </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
       <c r="K6">
         <v>88</v>
       </c>
+      <c r="L6">
+        <v>96</v>
+      </c>
       <c r="O6">
         <f t="shared" ref="O6:O24" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+R6+S6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
-        <v>45.68</v>
+        <v>66.48</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" ref="P6:P24" si="1">O6/$N$2</f>
-        <v>86.188679245283012</v>
+        <v>89.837837837837824</v>
+      </c>
+      <c r="R6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -908,16 +920,25 @@
       <c r="H7">
         <v>89</v>
       </c>
+      <c r="J7">
+        <v>92</v>
+      </c>
       <c r="K7">
         <v>98</v>
       </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>53.220000000000006</v>
+        <v>72.940000000000012</v>
       </c>
       <c r="P7" s="2">
         <f t="shared" si="1"/>
-        <v>100.41509433962264</v>
+        <v>98.567567567567565</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -942,16 +963,28 @@
       <c r="H8">
         <v>100</v>
       </c>
+      <c r="J8">
+        <v>97</v>
+      </c>
       <c r="K8">
         <v>99</v>
       </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>55.35</v>
+        <v>75.87</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="1"/>
-        <v>104.43396226415094</v>
+        <v>102.52702702702702</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -976,16 +1009,22 @@
       <c r="H9">
         <v>53</v>
       </c>
+      <c r="J9">
+        <v>96</v>
+      </c>
       <c r="K9">
         <v>94</v>
       </c>
+      <c r="L9">
+        <v>95</v>
+      </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>41.980000000000004</v>
+        <v>62.09</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="1"/>
-        <v>79.20754716981132</v>
+        <v>83.905405405405403</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -1010,16 +1049,25 @@
       <c r="H10">
         <v>84</v>
       </c>
+      <c r="J10">
+        <v>94</v>
+      </c>
       <c r="K10">
         <v>98</v>
       </c>
+      <c r="L10">
+        <v>99</v>
+      </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>50.66</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="1"/>
-        <v>95.584905660377345</v>
+        <v>95.472972972972968</v>
+      </c>
+      <c r="R10">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -1044,16 +1092,28 @@
       <c r="H11">
         <v>98</v>
       </c>
+      <c r="J11">
+        <v>99</v>
+      </c>
       <c r="K11">
         <v>91</v>
       </c>
+      <c r="L11">
+        <v>92</v>
+      </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>54.15</v>
+        <v>74.589999999999989</v>
       </c>
       <c r="P11" s="2">
         <f t="shared" si="1"/>
-        <v>102.1698113207547</v>
+        <v>100.79729729729726</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -1078,16 +1138,22 @@
       <c r="H12">
         <v>72</v>
       </c>
+      <c r="J12">
+        <v>94</v>
+      </c>
       <c r="K12">
         <v>92</v>
       </c>
+      <c r="L12">
+        <v>91</v>
+      </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>46.2</v>
+        <v>65.790000000000006</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="1"/>
-        <v>87.169811320754718</v>
+        <v>88.905405405405403</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -1112,18 +1178,27 @@
       <c r="H13">
         <v>89</v>
       </c>
+      <c r="J13">
+        <v>99</v>
+      </c>
       <c r="K13">
         <v>97</v>
       </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>51.89</v>
+        <v>72.72999999999999</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="1"/>
-        <v>97.905660377358487</v>
+        <v>98.283783783783761</v>
       </c>
       <c r="R13">
+        <v>3</v>
+      </c>
+      <c r="S13">
         <v>3</v>
       </c>
     </row>
@@ -1149,16 +1224,28 @@
       <c r="H14">
         <v>96</v>
       </c>
+      <c r="J14">
+        <v>95</v>
+      </c>
       <c r="K14">
         <v>98</v>
       </c>
+      <c r="L14">
+        <v>100</v>
+      </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>53.059999999999995</v>
+        <v>73.260000000000005</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="1"/>
-        <v>100.11320754716979</v>
+        <v>99</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -1183,16 +1270,22 @@
       <c r="H15">
         <v>86</v>
       </c>
+      <c r="J15">
+        <v>98</v>
+      </c>
       <c r="K15">
         <v>99</v>
       </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>51.99</v>
+        <v>72.67</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="1"/>
-        <v>98.094339622641513</v>
+        <v>98.202702702702695</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -1217,22 +1310,28 @@
       <c r="H16">
         <v>55</v>
       </c>
+      <c r="J16">
+        <v>91</v>
+      </c>
       <c r="K16">
         <v>85</v>
       </c>
+      <c r="L16">
+        <v>87</v>
+      </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>35.61</v>
+        <v>54.52</v>
       </c>
       <c r="P16" s="2">
         <f t="shared" si="1"/>
-        <v>67.188679245283012</v>
+        <v>73.675675675675663</v>
       </c>
       <c r="R16">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1254,22 +1353,28 @@
       <c r="H17">
         <v>76</v>
       </c>
+      <c r="J17">
+        <v>93</v>
+      </c>
       <c r="K17">
         <v>98</v>
       </c>
+      <c r="L17">
+        <v>93</v>
+      </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>66.03</v>
       </c>
       <c r="P17" s="2">
         <f t="shared" si="1"/>
-        <v>87.735849056603769</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+        <v>89.229729729729712</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1291,19 +1396,31 @@
       <c r="H19">
         <v>100</v>
       </c>
+      <c r="J19">
+        <v>98</v>
+      </c>
       <c r="K19">
         <v>100</v>
       </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
       <c r="O19">
         <f t="shared" si="0"/>
-        <v>55.24</v>
+        <v>75.92</v>
       </c>
       <c r="P19" s="2">
         <f t="shared" si="1"/>
-        <v>104.22641509433961</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+        <v>102.59459459459458</v>
+      </c>
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1325,19 +1442,28 @@
       <c r="H20">
         <v>96</v>
       </c>
+      <c r="J20">
+        <v>96</v>
+      </c>
       <c r="K20">
         <v>100</v>
       </c>
+      <c r="L20">
+        <v>95</v>
+      </c>
       <c r="O20">
         <f t="shared" si="0"/>
-        <v>54.28</v>
+        <v>74.39</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="1"/>
-        <v>102.41509433962264</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+        <v>100.52702702702702</v>
+      </c>
+      <c r="R20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1365,10 +1491,10 @@
       </c>
       <c r="P21" s="2">
         <f t="shared" si="1"/>
-        <v>54.679245283018872</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+        <v>39.162162162162161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1390,22 +1516,28 @@
       <c r="H22">
         <v>90</v>
       </c>
+      <c r="J22">
+        <v>92</v>
+      </c>
       <c r="K22">
         <v>91</v>
       </c>
+      <c r="L22">
+        <v>92</v>
+      </c>
       <c r="O22">
         <f t="shared" si="0"/>
-        <v>49.19</v>
+        <v>68.509999999999991</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="1"/>
-        <v>92.811320754716974</v>
+        <v>92.581081081081052</v>
       </c>
       <c r="R22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1427,19 +1559,25 @@
       <c r="H23">
         <v>86</v>
       </c>
+      <c r="J23">
+        <v>90</v>
+      </c>
       <c r="K23">
         <v>94</v>
       </c>
+      <c r="L23">
+        <v>98</v>
+      </c>
       <c r="O23">
         <f t="shared" si="0"/>
-        <v>49.980000000000004</v>
+        <v>69.28</v>
       </c>
       <c r="P23" s="2">
         <f t="shared" si="1"/>
-        <v>94.301886792452834</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+        <v>93.621621621621614</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1461,40 +1599,37 @@
       <c r="H24">
         <v>82</v>
       </c>
+      <c r="J24">
+        <v>95</v>
+      </c>
       <c r="K24">
         <v>96</v>
       </c>
+      <c r="L24">
+        <v>92</v>
+      </c>
       <c r="O24">
-        <f t="shared" si="0"/>
-        <v>46.239999999999995</v>
+        <f>(F24+F$33)*F$2+G$2*(G24+G$33)+H$2*(H24+H$33)+I$2*(I24+I$33+R24+S24)+J$2*(J24+J$33)+K$2*(K24+K$33)+L$2*(L24+L$33)+M$2*(M24+M$33)</f>
+        <v>66.039999999999992</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="1"/>
-        <v>87.245283018867909</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+        <v>89.243243243243214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="H26">
-        <v>0.2</v>
-      </c>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="I26">
         <v>0.2</v>
       </c>
-      <c r="K26">
-        <v>0.05</v>
-      </c>
-      <c r="L26">
-        <v>0.05</v>
-      </c>
       <c r="M26">
         <v>0.1</v>
       </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>70</v>
       </c>
@@ -1510,13 +1645,16 @@
       <c r="K27">
         <v>0.05</v>
       </c>
+      <c r="L27">
+        <v>0.05</v>
+      </c>
       <c r="N27">
         <f>SUM(F27:M27)</f>
-        <v>0.65000000000000013</v>
+        <v>0.70000000000000018</v>
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>20</v>
       </c>
@@ -1541,16 +1679,25 @@
       <c r="K28">
         <v>75</v>
       </c>
+      <c r="L28">
+        <v>85</v>
+      </c>
       <c r="O28">
-        <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
-        <v>55.95</v>
+        <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33+R28+S28)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
+        <v>60.2</v>
       </c>
       <c r="P28" s="2">
         <f>O28/$N$27</f>
-        <v>86.076923076923066</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+        <v>85.999999999999986</v>
+      </c>
+      <c r="R28">
+        <v>3</v>
+      </c>
+      <c r="S28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>21</v>
       </c>
@@ -1575,15 +1722,15 @@
       </c>
       <c r="P29" s="2">
         <f>O29/$N$27</f>
-        <v>16.92307692307692</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+        <v>15.71428571428571</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="E31" s="1" t="s">
         <v>98</v>
       </c>
@@ -1602,17 +1749,17 @@
       <c r="I31">
         <v>85</v>
       </c>
-      <c r="J31" t="e">
-        <f t="shared" ref="J31:N31" si="3">AVERAGE(J5:J24,J28:J29)</f>
-        <v>#DIV/0!</v>
+      <c r="J31">
+        <f>AVERAGE(J5:J24,J28:J29)</f>
+        <v>95.388888888888886</v>
       </c>
       <c r="K31">
+        <f t="shared" ref="J31:N31" si="3">AVERAGE(K5:K24,K28:K29)</f>
+        <v>94.1</v>
+      </c>
+      <c r="L31">
         <f t="shared" si="3"/>
-        <v>94.1</v>
-      </c>
-      <c r="L31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>95.421052631578945</v>
       </c>
       <c r="M31" t="e">
         <f t="shared" si="3"/>
@@ -1622,8 +1769,12 @@
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R31">
+        <f>COUNT(R5:R17,R28)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
         <v>100</v>
       </c>
@@ -1643,17 +1794,17 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J32" t="e">
+      <c r="J32">
         <f t="shared" ref="J32:N32" si="5">STDEV(J5:J24,J28:J29)</f>
-        <v>#DIV/0!</v>
+        <v>2.992911014358643</v>
       </c>
       <c r="K32">
         <f t="shared" si="5"/>
         <v>6.239939270959546</v>
       </c>
-      <c r="L32" t="e">
+      <c r="L32">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>4.670424552123289</v>
       </c>
       <c r="M32" t="e">
         <f t="shared" si="5"/>
@@ -1704,17 +1855,17 @@
         <f>I31+SUM(I33:I33)</f>
         <v>85</v>
       </c>
-      <c r="J34" t="e">
+      <c r="J34">
         <f>J31+J33</f>
-        <v>#DIV/0!</v>
+        <v>95.388888888888886</v>
       </c>
       <c r="K34">
         <f>K31+K33</f>
         <v>94.1</v>
       </c>
-      <c r="L34" t="e">
+      <c r="L34">
         <f>L31+L33</f>
-        <v>#DIV/0!</v>
+        <v>95.421052631578945</v>
       </c>
       <c r="M34" t="e">
         <f>M31+M33</f>
@@ -5178,65 +5329,273 @@
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="C89">
+      <c r="B89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D89">
-        <v>72</v>
-      </c>
-      <c r="E89">
+      <c r="N89" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O89" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F89">
+      <c r="P89" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V89" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W89" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>1</v>
+      </c>
+      <c r="B90">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>2</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>3</v>
+      </c>
+      <c r="B92">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>4</v>
+      </c>
+      <c r="B93">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>5</v>
+      </c>
+      <c r="B94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>6</v>
+      </c>
+      <c r="B95">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>7</v>
+      </c>
+      <c r="B96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>8</v>
+      </c>
+      <c r="B97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>9</v>
+      </c>
+      <c r="B98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>10</v>
+      </c>
+      <c r="B99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>11</v>
+      </c>
+      <c r="B100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>12</v>
+      </c>
+      <c r="B101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>13</v>
+      </c>
+      <c r="B102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104">
+        <f t="shared" ref="B104:W104" si="9">SUM(B90:B103)</f>
         <v>100</v>
       </c>
-      <c r="G89">
-        <v>53</v>
-      </c>
-      <c r="H89">
-        <v>84</v>
-      </c>
-      <c r="I89">
-        <v>98</v>
-      </c>
-      <c r="J89">
-        <v>72</v>
-      </c>
-      <c r="K89">
-        <v>89</v>
-      </c>
-      <c r="L89">
-        <v>96</v>
-      </c>
-      <c r="M89">
-        <v>86</v>
-      </c>
-      <c r="N89">
-        <v>55</v>
-      </c>
-      <c r="O89">
-        <v>76</v>
-      </c>
-      <c r="P89">
-        <v>100</v>
-      </c>
-      <c r="Q89">
-        <v>96</v>
-      </c>
-      <c r="R89">
+      <c r="C104">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S89">
-        <v>90</v>
-      </c>
-      <c r="T89">
-        <v>86</v>
-      </c>
-      <c r="U89">
-        <v>82</v>
-      </c>
-      <c r="V89">
-        <v>85</v>
+      <c r="D104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V104">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W104">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B741F966-7B85-1E46-95A0-729F2A392049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1429C-7A14-C448-A3D7-26BBDAF287C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21140" yWindow="4840" windowWidth="27200" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13760" yWindow="780" windowWidth="27200" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -887,7 +887,7 @@
         <v>96</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O24" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+R6+S6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
+        <f t="shared" ref="O6:O23" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+R6+S6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
         <v>66.48</v>
       </c>
       <c r="P6" s="2">
@@ -1069,6 +1069,9 @@
       <c r="R10">
         <v>3</v>
       </c>
+      <c r="S10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -1330,6 +1333,9 @@
       <c r="R16">
         <v>3</v>
       </c>
+      <c r="S16">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17">
@@ -1460,6 +1466,9 @@
         <v>100.52702702702702</v>
       </c>
       <c r="R20">
+        <v>3</v>
+      </c>
+      <c r="S20">
         <v>3</v>
       </c>
     </row>
@@ -1754,7 +1763,7 @@
         <v>95.388888888888886</v>
       </c>
       <c r="K31">
-        <f t="shared" ref="J31:N31" si="3">AVERAGE(K5:K24,K28:K29)</f>
+        <f t="shared" ref="K31:N31" si="3">AVERAGE(K5:K24,K28:K29)</f>
         <v>94.1</v>
       </c>
       <c r="L31">
@@ -1771,6 +1780,10 @@
       </c>
       <c r="R31">
         <f>COUNT(R5:R17,R28)</f>
+        <v>8</v>
+      </c>
+      <c r="S31">
+        <f>COUNT(S5:S17,S28)</f>
         <v>8</v>
       </c>
     </row>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE1429C-7A14-C448-A3D7-26BBDAF287C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844E5C1A-2DAD-7A4B-82A1-EB58DDFF562B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13760" yWindow="780" windowWidth="27200" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1600" yWindow="500" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1323,7 +1323,7 @@
         <v>87</v>
       </c>
       <c r="O16">
-        <f t="shared" si="0"/>
+        <f>(F16+F$33)*F$2+G$2*(G16+G$33)+H$2*(H16+H$33)+I$2*(I16+I$33+R16+S16)+J$2*(J16+J$33)+K$2*(K16+K$33)+L$2*(L16+L$33)+M$2*(M16+M$33)</f>
         <v>54.52</v>
       </c>
       <c r="P16" s="2">
@@ -1624,6 +1624,12 @@
       <c r="P24" s="2">
         <f t="shared" si="1"/>
         <v>89.243243243243214</v>
+      </c>
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -1779,12 +1785,12 @@
         <v>#DIV/0!</v>
       </c>
       <c r="R31">
-        <f>COUNT(R5:R17,R28)</f>
-        <v>8</v>
+        <f>COUNT(R5:R24,R28)</f>
+        <v>12</v>
       </c>
       <c r="S31">
-        <f>COUNT(S5:S17,S28)</f>
-        <v>8</v>
+        <f>COUNT(S5:S24,S28)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
@@ -1841,7 +1847,9 @@
       <c r="H33" s="1">
         <v>6</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1866,7 +1874,7 @@
       </c>
       <c r="I34">
         <f>I31+SUM(I33:I33)</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J34">
         <f>J31+J33</f>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844E5C1A-2DAD-7A4B-82A1-EB58DDFF562B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5A68E-AA79-1A47-BACF-30B8207C3211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="500" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21520" yWindow="1380" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -344,7 +344,7 @@
     <t>Class Eval</t>
   </si>
   <si>
-    <t>Survery</t>
+    <t>Survey</t>
   </si>
 </sst>
 </file>
@@ -854,6 +854,9 @@
         <f>O5/$N$2</f>
         <v>97.418918918918905</v>
       </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -897,6 +900,9 @@
       <c r="R6">
         <v>3</v>
       </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -1026,6 +1032,12 @@
         <f t="shared" si="1"/>
         <v>83.905405405405403</v>
       </c>
+      <c r="R9">
+        <v>3</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -1158,6 +1170,12 @@
         <f t="shared" si="1"/>
         <v>88.905405405405403</v>
       </c>
+      <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="S12">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -1290,6 +1308,9 @@
         <f t="shared" si="1"/>
         <v>98.202702702702695</v>
       </c>
+      <c r="S15">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -1376,6 +1397,9 @@
         <f t="shared" si="1"/>
         <v>89.229729729729712</v>
       </c>
+      <c r="S17">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="P18" s="2"/>
@@ -1545,6 +1569,9 @@
       <c r="R22">
         <v>3</v>
       </c>
+      <c r="S22">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -1584,6 +1611,12 @@
       <c r="P23" s="2">
         <f t="shared" si="1"/>
         <v>93.621621621621614</v>
+      </c>
+      <c r="R23">
+        <v>3</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -1786,11 +1819,11 @@
       </c>
       <c r="R31">
         <f>COUNT(R5:R24,R28)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S31">
         <f>COUNT(S5:S24,S28)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5A68E-AA79-1A47-BACF-30B8207C3211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B96863-9CD5-8B4F-AA2F-A3A94A97F938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21520" yWindow="1380" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13760" yWindow="1380" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="104">
   <si>
     <t>First name</t>
   </si>
@@ -725,16 +725,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W104"/>
+  <dimension ref="A1:W103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="I1">
-        <v>0.16</v>
-      </c>
       <c r="M1">
         <v>0.1</v>
       </c>
@@ -749,6 +746,9 @@
       <c r="H2">
         <v>0.16</v>
       </c>
+      <c r="I2">
+        <v>0.16</v>
+      </c>
       <c r="J2">
         <v>0.16</v>
       </c>
@@ -760,7 +760,7 @@
       </c>
       <c r="N2">
         <f>SUM(F2:M2)</f>
-        <v>0.7400000000000001</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>101</v>
@@ -837,6 +837,9 @@
       <c r="H5">
         <v>87</v>
       </c>
+      <c r="I5">
+        <v>94</v>
+      </c>
       <c r="J5">
         <v>98</v>
       </c>
@@ -848,11 +851,14 @@
       </c>
       <c r="O5">
         <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33+R5+S5)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
-        <v>72.09</v>
+        <v>88.090000000000018</v>
       </c>
       <c r="P5" s="2">
         <f>O5/$N$2</f>
-        <v>97.418918918918905</v>
+        <v>97.87777777777778</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
       </c>
       <c r="S5">
         <v>3</v>
@@ -880,6 +886,9 @@
       <c r="H6">
         <v>72</v>
       </c>
+      <c r="I6">
+        <v>82</v>
+      </c>
       <c r="J6">
         <v>100</v>
       </c>
@@ -891,11 +900,11 @@
       </c>
       <c r="O6">
         <f t="shared" ref="O6:O23" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+R6+S6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
-        <v>66.48</v>
+        <v>80.56</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" ref="P6:P24" si="1">O6/$N$2</f>
-        <v>89.837837837837824</v>
+        <v>89.511111111111106</v>
       </c>
       <c r="R6">
         <v>3</v>
@@ -926,6 +935,9 @@
       <c r="H7">
         <v>89</v>
       </c>
+      <c r="I7">
+        <v>95</v>
+      </c>
       <c r="J7">
         <v>92</v>
       </c>
@@ -936,12 +948,15 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <f t="shared" si="0"/>
-        <v>72.940000000000012</v>
+        <f>(F7+F$33)*F$2+G$2*(G7+G$33)+H$2*(H7+H$33)+I$2*(I7+I$33+R7+S7)+J$2*(J7+J$33)+K$2*(K7+K$33)+L$2*(L7+L$33)+M$2*(M7+M$33)</f>
+        <v>89.100000000000009</v>
       </c>
       <c r="P7" s="2">
-        <f t="shared" si="1"/>
-        <v>98.567567567567565</v>
+        <f>O7/$N$2</f>
+        <v>99</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
       </c>
       <c r="S7">
         <v>3</v>
@@ -969,6 +984,9 @@
       <c r="H8">
         <v>100</v>
       </c>
+      <c r="I8">
+        <v>99</v>
+      </c>
       <c r="J8">
         <v>97</v>
       </c>
@@ -980,11 +998,11 @@
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>75.87</v>
+        <v>92.67</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="1"/>
-        <v>102.52702702702702</v>
+        <v>102.96666666666665</v>
       </c>
       <c r="R8">
         <v>3</v>
@@ -1015,6 +1033,9 @@
       <c r="H9">
         <v>53</v>
       </c>
+      <c r="I9">
+        <v>92</v>
+      </c>
       <c r="J9">
         <v>96</v>
       </c>
@@ -1026,11 +1047,11 @@
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>62.09</v>
+        <v>77.77</v>
       </c>
       <c r="P9" s="2">
-        <f t="shared" si="1"/>
-        <v>83.905405405405403</v>
+        <f>O9/$N$2</f>
+        <v>86.411111111111097</v>
       </c>
       <c r="R9">
         <v>3</v>
@@ -1061,6 +1082,9 @@
       <c r="H10">
         <v>84</v>
       </c>
+      <c r="I10">
+        <v>97</v>
+      </c>
       <c r="J10">
         <v>94</v>
       </c>
@@ -1072,11 +1096,11 @@
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>70.650000000000006</v>
+        <v>87.13000000000001</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="1"/>
-        <v>95.472972972972968</v>
+        <v>96.811111111111103</v>
       </c>
       <c r="R10">
         <v>3</v>
@@ -1107,6 +1131,9 @@
       <c r="H11">
         <v>98</v>
       </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
       <c r="J11">
         <v>99</v>
       </c>
@@ -1118,11 +1145,11 @@
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>74.589999999999989</v>
+        <v>91.55</v>
       </c>
       <c r="P11" s="2">
         <f t="shared" si="1"/>
-        <v>100.79729729729726</v>
+        <v>101.7222222222222</v>
       </c>
       <c r="R11">
         <v>3</v>
@@ -1153,6 +1180,9 @@
       <c r="H12">
         <v>72</v>
       </c>
+      <c r="I12">
+        <v>97</v>
+      </c>
       <c r="J12">
         <v>94</v>
       </c>
@@ -1164,11 +1194,11 @@
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>65.790000000000006</v>
+        <v>82.27</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="1"/>
-        <v>88.905405405405403</v>
+        <v>91.411111111111097</v>
       </c>
       <c r="R12">
         <v>3</v>
@@ -1199,6 +1229,9 @@
       <c r="H13">
         <v>89</v>
       </c>
+      <c r="I13">
+        <v>95</v>
+      </c>
       <c r="J13">
         <v>99</v>
       </c>
@@ -1210,11 +1243,11 @@
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>72.72999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="1"/>
-        <v>98.283783783783761</v>
+        <v>98.766666666666652</v>
       </c>
       <c r="R13">
         <v>3</v>
@@ -1245,6 +1278,9 @@
       <c r="H14">
         <v>96</v>
       </c>
+      <c r="I14">
+        <v>96</v>
+      </c>
       <c r="J14">
         <v>95</v>
       </c>
@@ -1256,11 +1292,11 @@
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>73.260000000000005</v>
+        <v>89.58</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="1"/>
-        <v>99</v>
+        <v>99.533333333333317</v>
       </c>
       <c r="R14">
         <v>3</v>
@@ -1291,6 +1327,9 @@
       <c r="H15">
         <v>86</v>
       </c>
+      <c r="I15">
+        <v>93</v>
+      </c>
       <c r="J15">
         <v>98</v>
       </c>
@@ -1302,11 +1341,11 @@
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>72.67</v>
+        <v>88.03</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="1"/>
-        <v>98.202702702702695</v>
+        <v>97.811111111111103</v>
       </c>
       <c r="S15">
         <v>3</v>
@@ -1334,6 +1373,9 @@
       <c r="H16">
         <v>55</v>
       </c>
+      <c r="I16">
+        <v>85</v>
+      </c>
       <c r="J16">
         <v>91</v>
       </c>
@@ -1345,11 +1387,11 @@
       </c>
       <c r="O16">
         <f>(F16+F$33)*F$2+G$2*(G16+G$33)+H$2*(H16+H$33)+I$2*(I16+I$33+R16+S16)+J$2*(J16+J$33)+K$2*(K16+K$33)+L$2*(L16+L$33)+M$2*(M16+M$33)</f>
-        <v>54.52</v>
+        <v>69.08</v>
       </c>
       <c r="P16" s="2">
         <f t="shared" si="1"/>
-        <v>73.675675675675663</v>
+        <v>76.755555555555546</v>
       </c>
       <c r="R16">
         <v>3</v>
@@ -1380,6 +1422,9 @@
       <c r="H17">
         <v>76</v>
       </c>
+      <c r="I17">
+        <v>86</v>
+      </c>
       <c r="J17">
         <v>93</v>
       </c>
@@ -1391,11 +1436,14 @@
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>66.03</v>
+        <v>80.750000000000014</v>
       </c>
       <c r="P17" s="2">
         <f t="shared" si="1"/>
-        <v>89.229729729729712</v>
+        <v>89.722222222222229</v>
+      </c>
+      <c r="R17">
+        <v>3</v>
       </c>
       <c r="S17">
         <v>3</v>
@@ -1426,6 +1474,9 @@
       <c r="H19">
         <v>100</v>
       </c>
+      <c r="I19">
+        <v>98</v>
+      </c>
       <c r="J19">
         <v>98</v>
       </c>
@@ -1437,11 +1488,11 @@
       </c>
       <c r="O19">
         <f t="shared" si="0"/>
-        <v>75.92</v>
+        <v>92.56</v>
       </c>
       <c r="P19" s="2">
         <f t="shared" si="1"/>
-        <v>102.59459459459458</v>
+        <v>102.84444444444443</v>
       </c>
       <c r="R19">
         <v>3</v>
@@ -1472,6 +1523,9 @@
       <c r="H20">
         <v>96</v>
       </c>
+      <c r="I20">
+        <v>99</v>
+      </c>
       <c r="J20">
         <v>96</v>
       </c>
@@ -1483,11 +1537,11 @@
       </c>
       <c r="O20">
         <f t="shared" si="0"/>
-        <v>74.39</v>
+        <v>91.19</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="1"/>
-        <v>100.52702702702702</v>
+        <v>101.32222222222221</v>
       </c>
       <c r="R20">
         <v>3</v>
@@ -1524,7 +1578,7 @@
       </c>
       <c r="P21" s="2">
         <f t="shared" si="1"/>
-        <v>39.162162162162161</v>
+        <v>32.200000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -1549,6 +1603,9 @@
       <c r="H22">
         <v>90</v>
       </c>
+      <c r="I22">
+        <v>100</v>
+      </c>
       <c r="J22">
         <v>92</v>
       </c>
@@ -1560,11 +1617,11 @@
       </c>
       <c r="O22">
         <f t="shared" si="0"/>
-        <v>68.509999999999991</v>
+        <v>85.47</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="1"/>
-        <v>92.581081081081052</v>
+        <v>94.966666666666654</v>
       </c>
       <c r="R22">
         <v>3</v>
@@ -1595,6 +1652,9 @@
       <c r="H23">
         <v>86</v>
       </c>
+      <c r="I23">
+        <v>93</v>
+      </c>
       <c r="J23">
         <v>90</v>
       </c>
@@ -1606,11 +1666,11 @@
       </c>
       <c r="O23">
         <f t="shared" si="0"/>
-        <v>69.28</v>
+        <v>85.120000000000019</v>
       </c>
       <c r="P23" s="2">
         <f t="shared" si="1"/>
-        <v>93.621621621621614</v>
+        <v>94.577777777777783</v>
       </c>
       <c r="R23">
         <v>3</v>
@@ -1641,6 +1701,9 @@
       <c r="H24">
         <v>82</v>
       </c>
+      <c r="I24">
+        <v>83</v>
+      </c>
       <c r="J24">
         <v>95</v>
       </c>
@@ -1652,11 +1715,11 @@
       </c>
       <c r="O24">
         <f>(F24+F$33)*F$2+G$2*(G24+G$33)+H$2*(H24+H$33)+I$2*(I24+I$33+R24+S24)+J$2*(J24+J$33)+K$2*(K24+K$33)+L$2*(L24+L$33)+M$2*(M24+M$33)</f>
-        <v>66.039999999999992</v>
+        <v>80.279999999999987</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="1"/>
-        <v>89.243243243243214</v>
+        <v>89.199999999999974</v>
       </c>
       <c r="R24">
         <v>3</v>
@@ -1669,9 +1732,6 @@
       <c r="P25" s="2"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="I26">
-        <v>0.2</v>
-      </c>
       <c r="M26">
         <v>0.1</v>
       </c>
@@ -1690,6 +1750,9 @@
       <c r="H27">
         <v>0.2</v>
       </c>
+      <c r="I27">
+        <v>0.2</v>
+      </c>
       <c r="K27">
         <v>0.05</v>
       </c>
@@ -1698,7 +1761,7 @@
       </c>
       <c r="N27">
         <f>SUM(F27:M27)</f>
-        <v>0.70000000000000018</v>
+        <v>0.90000000000000013</v>
       </c>
       <c r="P27" s="2"/>
     </row>
@@ -1724,6 +1787,9 @@
       <c r="H28">
         <v>85</v>
       </c>
+      <c r="I28">
+        <v>92</v>
+      </c>
       <c r="K28">
         <v>75</v>
       </c>
@@ -1732,11 +1798,11 @@
       </c>
       <c r="O28">
         <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33+R28+S28)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
-        <v>60.2</v>
+        <v>79.800000000000011</v>
       </c>
       <c r="P28" s="2">
         <f>O28/$N$27</f>
-        <v>85.999999999999986</v>
+        <v>88.666666666666671</v>
       </c>
       <c r="R28">
         <v>3</v>
@@ -1770,7 +1836,7 @@
       </c>
       <c r="P29" s="2">
         <f>O29/$N$27</f>
-        <v>15.71428571428571</v>
+        <v>12.22222222222222</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -1795,7 +1861,8 @@
         <v>84</v>
       </c>
       <c r="I31">
-        <v>85</v>
+        <f>AVERAGE(I5:I24,I28:I29)</f>
+        <v>93.473684210526315</v>
       </c>
       <c r="J31">
         <f>AVERAGE(J5:J24,J28:J29)</f>
@@ -1819,7 +1886,7 @@
       </c>
       <c r="R31">
         <f>COUNT(R5:R24,R28)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S31">
         <f>COUNT(S5:S24,S28)</f>
@@ -1842,9 +1909,9 @@
         <f t="shared" si="4"/>
         <v>13.45362404707371</v>
       </c>
-      <c r="I32" t="e">
+      <c r="I32">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>5.6604713295373754</v>
       </c>
       <c r="J32">
         <f t="shared" ref="J32:N32" si="5">STDEV(J5:J24,J28:J29)</f>
@@ -1880,9 +1947,7 @@
       <c r="H33" s="1">
         <v>6</v>
       </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
+      <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1907,7 +1972,7 @@
       </c>
       <c r="I34">
         <f>I31+SUM(I33:I33)</f>
-        <v>90</v>
+        <v>93.473684210526315</v>
       </c>
       <c r="J34">
         <f>J31+J33</f>
@@ -5431,9 +5496,7 @@
       <c r="Q89" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R89" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="R89" s="1"/>
       <c r="S89" s="1" t="s">
         <v>93</v>
       </c>
@@ -5446,9 +5509,7 @@
       <c r="V89" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W89" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="W89" s="1"/>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90">
@@ -5457,6 +5518,63 @@
       <c r="B90">
         <v>18</v>
       </c>
+      <c r="C90">
+        <v>18</v>
+      </c>
+      <c r="D90">
+        <v>17</v>
+      </c>
+      <c r="E90">
+        <v>18</v>
+      </c>
+      <c r="F90">
+        <v>18</v>
+      </c>
+      <c r="G90">
+        <v>14</v>
+      </c>
+      <c r="H90">
+        <v>17</v>
+      </c>
+      <c r="I90">
+        <v>18</v>
+      </c>
+      <c r="J90">
+        <v>18</v>
+      </c>
+      <c r="K90">
+        <v>16</v>
+      </c>
+      <c r="L90">
+        <v>18</v>
+      </c>
+      <c r="M90">
+        <v>18</v>
+      </c>
+      <c r="N90">
+        <v>16</v>
+      </c>
+      <c r="O90">
+        <v>18</v>
+      </c>
+      <c r="P90">
+        <v>18</v>
+      </c>
+      <c r="Q90">
+        <v>18</v>
+      </c>
+      <c r="S90">
+        <v>18</v>
+      </c>
+      <c r="T90">
+        <v>17</v>
+      </c>
+      <c r="U90">
+        <v>16</v>
+      </c>
+      <c r="V90">
+        <v>18</v>
+      </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91">
@@ -5465,6 +5583,63 @@
       <c r="B91">
         <v>2</v>
       </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91">
+        <v>2</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="K91">
+        <v>2</v>
+      </c>
+      <c r="L91">
+        <v>2</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91">
+        <v>2</v>
+      </c>
+      <c r="P91">
+        <v>2</v>
+      </c>
+      <c r="Q91">
+        <v>2</v>
+      </c>
+      <c r="S91">
+        <v>2</v>
+      </c>
+      <c r="T91">
+        <v>2</v>
+      </c>
+      <c r="U91">
+        <v>2</v>
+      </c>
+      <c r="V91">
+        <v>2</v>
+      </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92">
@@ -5473,6 +5648,63 @@
       <c r="B92">
         <v>8</v>
       </c>
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>8</v>
+      </c>
+      <c r="F92">
+        <v>8</v>
+      </c>
+      <c r="G92">
+        <v>8</v>
+      </c>
+      <c r="H92">
+        <v>8</v>
+      </c>
+      <c r="I92">
+        <v>8</v>
+      </c>
+      <c r="J92">
+        <v>8</v>
+      </c>
+      <c r="K92">
+        <v>8</v>
+      </c>
+      <c r="L92">
+        <v>8</v>
+      </c>
+      <c r="M92">
+        <v>6</v>
+      </c>
+      <c r="N92">
+        <v>5</v>
+      </c>
+      <c r="O92">
+        <v>8</v>
+      </c>
+      <c r="P92">
+        <v>8</v>
+      </c>
+      <c r="Q92">
+        <v>8</v>
+      </c>
+      <c r="S92">
+        <v>8</v>
+      </c>
+      <c r="T92">
+        <v>8</v>
+      </c>
+      <c r="U92">
+        <v>7</v>
+      </c>
+      <c r="V92">
+        <v>8</v>
+      </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93">
@@ -5481,6 +5713,63 @@
       <c r="B93">
         <v>12</v>
       </c>
+      <c r="C93">
+        <v>11</v>
+      </c>
+      <c r="D93">
+        <v>9</v>
+      </c>
+      <c r="E93">
+        <v>11</v>
+      </c>
+      <c r="F93">
+        <v>12</v>
+      </c>
+      <c r="G93">
+        <v>12</v>
+      </c>
+      <c r="H93">
+        <v>12</v>
+      </c>
+      <c r="I93">
+        <v>12</v>
+      </c>
+      <c r="J93">
+        <v>11</v>
+      </c>
+      <c r="K93">
+        <v>12</v>
+      </c>
+      <c r="L93">
+        <v>11</v>
+      </c>
+      <c r="M93">
+        <v>10</v>
+      </c>
+      <c r="N93">
+        <v>10</v>
+      </c>
+      <c r="O93">
+        <v>9</v>
+      </c>
+      <c r="P93">
+        <v>12</v>
+      </c>
+      <c r="Q93">
+        <v>11</v>
+      </c>
+      <c r="S93">
+        <v>12</v>
+      </c>
+      <c r="T93">
+        <v>11</v>
+      </c>
+      <c r="U93">
+        <v>10</v>
+      </c>
+      <c r="V93">
+        <v>10</v>
+      </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94">
@@ -5489,12 +5778,126 @@
       <c r="B94">
         <v>12</v>
       </c>
+      <c r="C94">
+        <v>10</v>
+      </c>
+      <c r="D94">
+        <v>12</v>
+      </c>
+      <c r="E94">
+        <v>12</v>
+      </c>
+      <c r="F94">
+        <v>12</v>
+      </c>
+      <c r="G94">
+        <v>12</v>
+      </c>
+      <c r="H94">
+        <v>12</v>
+      </c>
+      <c r="I94">
+        <v>12</v>
+      </c>
+      <c r="J94">
+        <v>11</v>
+      </c>
+      <c r="K94">
+        <v>12</v>
+      </c>
+      <c r="L94">
+        <v>12</v>
+      </c>
+      <c r="M94">
+        <v>11</v>
+      </c>
+      <c r="N94">
+        <v>9</v>
+      </c>
+      <c r="O94">
+        <v>10</v>
+      </c>
+      <c r="P94">
+        <v>12</v>
+      </c>
+      <c r="Q94">
+        <v>12</v>
+      </c>
+      <c r="S94">
+        <v>12</v>
+      </c>
+      <c r="T94">
+        <v>12</v>
+      </c>
+      <c r="U94">
+        <v>11</v>
+      </c>
+      <c r="V94">
+        <v>12</v>
+      </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>6</v>
       </c>
       <c r="B95">
+        <v>4</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95">
+        <v>4</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95">
+        <v>4</v>
+      </c>
+      <c r="I95">
+        <v>4</v>
+      </c>
+      <c r="J95">
+        <v>4</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
+      </c>
+      <c r="L95">
+        <v>4</v>
+      </c>
+      <c r="M95">
+        <v>4</v>
+      </c>
+      <c r="N95">
+        <v>3</v>
+      </c>
+      <c r="O95">
+        <v>4</v>
+      </c>
+      <c r="P95">
+        <v>4</v>
+      </c>
+      <c r="Q95">
+        <v>4</v>
+      </c>
+      <c r="S95">
+        <v>4</v>
+      </c>
+      <c r="T95">
+        <v>4</v>
+      </c>
+      <c r="U95">
+        <v>4</v>
+      </c>
+      <c r="V95">
         <v>4</v>
       </c>
     </row>
@@ -5505,151 +5908,537 @@
       <c r="B96">
         <v>6</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C96">
+        <v>6</v>
+      </c>
+      <c r="D96">
+        <v>6</v>
+      </c>
+      <c r="E96">
+        <v>6</v>
+      </c>
+      <c r="F96">
+        <v>6</v>
+      </c>
+      <c r="G96">
+        <v>6</v>
+      </c>
+      <c r="H96">
+        <v>5</v>
+      </c>
+      <c r="I96">
+        <v>6</v>
+      </c>
+      <c r="J96">
+        <v>6</v>
+      </c>
+      <c r="K96">
+        <v>6</v>
+      </c>
+      <c r="L96">
+        <v>6</v>
+      </c>
+      <c r="M96">
+        <v>6</v>
+      </c>
+      <c r="N96">
+        <v>4</v>
+      </c>
+      <c r="O96">
+        <v>4</v>
+      </c>
+      <c r="P96">
+        <v>6</v>
+      </c>
+      <c r="Q96">
+        <v>6</v>
+      </c>
+      <c r="S96">
+        <v>6</v>
+      </c>
+      <c r="T96">
+        <v>4</v>
+      </c>
+      <c r="U96">
+        <v>4</v>
+      </c>
+      <c r="V96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>8</v>
       </c>
       <c r="B97">
         <v>6</v>
       </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C97">
+        <v>6</v>
+      </c>
+      <c r="D97">
+        <v>5</v>
+      </c>
+      <c r="E97">
+        <v>6</v>
+      </c>
+      <c r="F97">
+        <v>6</v>
+      </c>
+      <c r="G97">
+        <v>6</v>
+      </c>
+      <c r="H97">
+        <v>6</v>
+      </c>
+      <c r="I97">
+        <v>6</v>
+      </c>
+      <c r="J97">
+        <v>6</v>
+      </c>
+      <c r="K97">
+        <v>6</v>
+      </c>
+      <c r="L97">
+        <v>6</v>
+      </c>
+      <c r="M97">
+        <v>6</v>
+      </c>
+      <c r="N97">
+        <v>6</v>
+      </c>
+      <c r="O97">
+        <v>2</v>
+      </c>
+      <c r="P97">
+        <v>6</v>
+      </c>
+      <c r="Q97">
+        <v>6</v>
+      </c>
+      <c r="S97">
+        <v>6</v>
+      </c>
+      <c r="T97">
+        <v>6</v>
+      </c>
+      <c r="U97">
+        <v>4</v>
+      </c>
+      <c r="V97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>9</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C98">
+        <v>5</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <v>5</v>
+      </c>
+      <c r="F98">
+        <v>5</v>
+      </c>
+      <c r="G98">
+        <v>5</v>
+      </c>
+      <c r="H98">
+        <v>5</v>
+      </c>
+      <c r="I98">
+        <v>6</v>
+      </c>
+      <c r="J98">
+        <v>6</v>
+      </c>
+      <c r="K98">
+        <v>6</v>
+      </c>
+      <c r="L98">
+        <v>5</v>
+      </c>
+      <c r="M98">
+        <v>5</v>
+      </c>
+      <c r="N98">
+        <v>6</v>
+      </c>
+      <c r="O98">
+        <v>5</v>
+      </c>
+      <c r="P98">
+        <v>5</v>
+      </c>
+      <c r="Q98">
+        <v>6</v>
+      </c>
+      <c r="S98">
+        <v>6</v>
+      </c>
+      <c r="T98">
+        <v>5</v>
+      </c>
+      <c r="U98">
+        <v>5</v>
+      </c>
+      <c r="V98">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>10</v>
       </c>
       <c r="B99">
         <v>6</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C99">
+        <v>6</v>
+      </c>
+      <c r="D99">
+        <v>6</v>
+      </c>
+      <c r="E99">
+        <v>6</v>
+      </c>
+      <c r="F99">
+        <v>6</v>
+      </c>
+      <c r="G99">
+        <v>3</v>
+      </c>
+      <c r="H99">
+        <v>6</v>
+      </c>
+      <c r="I99">
+        <v>6</v>
+      </c>
+      <c r="J99">
+        <v>6</v>
+      </c>
+      <c r="K99">
+        <v>5</v>
+      </c>
+      <c r="L99">
+        <v>6</v>
+      </c>
+      <c r="M99">
+        <v>6</v>
+      </c>
+      <c r="N99">
+        <v>5</v>
+      </c>
+      <c r="O99">
+        <v>6</v>
+      </c>
+      <c r="P99">
+        <v>6</v>
+      </c>
+      <c r="Q99">
+        <v>6</v>
+      </c>
+      <c r="S99">
+        <v>6</v>
+      </c>
+      <c r="T99">
+        <v>6</v>
+      </c>
+      <c r="U99">
+        <v>4</v>
+      </c>
+      <c r="V99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>11</v>
       </c>
       <c r="B100">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C100">
+        <v>5</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100">
+        <v>6</v>
+      </c>
+      <c r="F100">
+        <v>6</v>
+      </c>
+      <c r="G100">
+        <v>6</v>
+      </c>
+      <c r="H100">
+        <v>6</v>
+      </c>
+      <c r="I100">
+        <v>6</v>
+      </c>
+      <c r="J100">
+        <v>6</v>
+      </c>
+      <c r="K100">
+        <v>6</v>
+      </c>
+      <c r="L100">
+        <v>6</v>
+      </c>
+      <c r="M100">
+        <v>5</v>
+      </c>
+      <c r="N100">
+        <v>6</v>
+      </c>
+      <c r="O100">
+        <v>6</v>
+      </c>
+      <c r="P100">
+        <v>5</v>
+      </c>
+      <c r="Q100">
+        <v>6</v>
+      </c>
+      <c r="S100">
+        <v>6</v>
+      </c>
+      <c r="T100">
+        <v>6</v>
+      </c>
+      <c r="U100">
+        <v>6</v>
+      </c>
+      <c r="V100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>12</v>
       </c>
       <c r="B101">
         <v>6</v>
       </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="C101">
+        <v>6</v>
+      </c>
+      <c r="D101">
+        <v>6</v>
+      </c>
+      <c r="E101">
+        <v>6</v>
+      </c>
+      <c r="F101">
+        <v>6</v>
+      </c>
+      <c r="G101">
+        <v>6</v>
+      </c>
+      <c r="H101">
+        <v>6</v>
+      </c>
+      <c r="I101">
+        <v>6</v>
+      </c>
+      <c r="J101">
+        <v>6</v>
+      </c>
+      <c r="K101">
+        <v>6</v>
+      </c>
+      <c r="L101">
+        <v>6</v>
+      </c>
+      <c r="M101">
+        <v>6</v>
+      </c>
+      <c r="N101">
+        <v>6</v>
+      </c>
+      <c r="O101">
+        <v>4</v>
+      </c>
+      <c r="P101">
+        <v>6</v>
+      </c>
+      <c r="Q101">
+        <v>6</v>
+      </c>
+      <c r="S101">
+        <v>6</v>
+      </c>
+      <c r="T101">
+        <v>6</v>
+      </c>
+      <c r="U101">
+        <v>5</v>
+      </c>
+      <c r="V101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>13</v>
       </c>
       <c r="B102">
         <v>8</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A103">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
+      <c r="C102">
+        <v>7</v>
+      </c>
+      <c r="D102">
+        <v>6</v>
+      </c>
+      <c r="E102">
+        <v>5</v>
+      </c>
+      <c r="F102">
+        <v>8</v>
+      </c>
+      <c r="G102">
+        <v>8</v>
+      </c>
+      <c r="H102">
+        <v>8</v>
+      </c>
+      <c r="I102">
+        <v>8</v>
+      </c>
+      <c r="J102">
+        <v>7</v>
+      </c>
+      <c r="K102">
+        <v>6</v>
+      </c>
+      <c r="L102">
+        <v>6</v>
+      </c>
+      <c r="M102">
+        <v>8</v>
+      </c>
+      <c r="N102">
+        <v>8</v>
+      </c>
+      <c r="O102">
+        <v>8</v>
+      </c>
+      <c r="P102">
+        <v>8</v>
+      </c>
+      <c r="Q102">
+        <v>8</v>
+      </c>
+      <c r="S102">
+        <v>8</v>
+      </c>
+      <c r="T102">
+        <v>6</v>
+      </c>
+      <c r="U102">
+        <v>5</v>
+      </c>
+      <c r="V102">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B104">
-        <f t="shared" ref="B104:W104" si="9">SUM(B90:B103)</f>
+      <c r="B103">
+        <f>SUM(B90:B102)</f>
         <v>100</v>
       </c>
-      <c r="C104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="D104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="S104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="U104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V104">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="W104">
-        <f t="shared" si="9"/>
-        <v>0</v>
+      <c r="C103">
+        <f>SUM(C90:C102)</f>
+        <v>94</v>
+      </c>
+      <c r="D103">
+        <f>SUM(D90:D102)</f>
+        <v>82</v>
+      </c>
+      <c r="E103">
+        <f>SUM(E90:E102)</f>
+        <v>95</v>
+      </c>
+      <c r="F103">
+        <f>SUM(F90:F102)</f>
+        <v>99</v>
+      </c>
+      <c r="G103">
+        <f>SUM(G90:G102)</f>
+        <v>92</v>
+      </c>
+      <c r="H103">
+        <f>SUM(H90:H102)</f>
+        <v>97</v>
+      </c>
+      <c r="I103">
+        <f>SUM(I90:I102)</f>
+        <v>100</v>
+      </c>
+      <c r="J103">
+        <f>SUM(J90:J102)</f>
+        <v>97</v>
+      </c>
+      <c r="K103">
+        <f>SUM(K90:K102)</f>
+        <v>95</v>
+      </c>
+      <c r="L103">
+        <f>SUM(L90:L102)</f>
+        <v>96</v>
+      </c>
+      <c r="M103">
+        <f>SUM(M90:M102)</f>
+        <v>93</v>
+      </c>
+      <c r="N103">
+        <f>SUM(N90:N102)</f>
+        <v>85</v>
+      </c>
+      <c r="O103">
+        <f>SUM(O90:O102)</f>
+        <v>86</v>
+      </c>
+      <c r="P103">
+        <f>SUM(P90:P102)</f>
+        <v>98</v>
+      </c>
+      <c r="Q103">
+        <f>SUM(Q90:Q102)</f>
+        <v>99</v>
+      </c>
+      <c r="S103">
+        <f>SUM(S90:S102)</f>
+        <v>100</v>
+      </c>
+      <c r="T103">
+        <f>SUM(T90:T102)</f>
+        <v>93</v>
+      </c>
+      <c r="U103">
+        <f>SUM(U90:U102)</f>
+        <v>83</v>
+      </c>
+      <c r="V103">
+        <f>SUM(V90:V102)</f>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B96863-9CD5-8B4F-AA2F-A3A94A97F938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EB49B5-C15B-304B-B72B-CCAB4960CFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13760" yWindow="1380" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13760" yWindow="1360" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="132">
   <si>
     <t>First name</t>
   </si>
@@ -345,6 +345,90 @@
   </si>
   <si>
     <t>Survey</t>
+  </si>
+  <si>
+    <t>Final Grade</t>
+  </si>
+  <si>
+    <t>97 ≤</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>≤ 100</t>
+  </si>
+  <si>
+    <t>93 ≤</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 97</t>
+  </si>
+  <si>
+    <t>90 ≤</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 93</t>
+  </si>
+  <si>
+    <t>87 ≤</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 90</t>
+  </si>
+  <si>
+    <t>83 ≤</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 87</t>
+  </si>
+  <si>
+    <t>80 ≤</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 83</t>
+  </si>
+  <si>
+    <t>77 ≤</t>
+  </si>
+  <si>
+    <t>C+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 80</t>
+  </si>
+  <si>
+    <t>73 ≤</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 77</t>
+  </si>
+  <si>
+    <t>70 ≤</t>
+  </si>
+  <si>
+    <t>C-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &lt; 73</t>
   </si>
 </sst>
 </file>
@@ -354,7 +438,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -366,6 +450,11 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -375,7 +464,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -383,14 +472,78 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -725,18 +878,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W103"/>
+  <dimension ref="A1:X103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="M1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F2">
         <v>0.16</v>
       </c>
@@ -766,7 +919,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>71</v>
       </c>
@@ -794,14 +947,18 @@
       <c r="M3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -815,7 +972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -850,21 +1007,30 @@
         <v>98</v>
       </c>
       <c r="O5">
-        <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33+R5+S5)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
+        <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33+S5+T5)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
         <v>88.090000000000018</v>
       </c>
       <c r="P5" s="2">
         <f>O5/$N$2</f>
         <v>97.87777777777778</v>
       </c>
-      <c r="R5">
-        <v>3</v>
-      </c>
       <c r="S5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -899,21 +1065,30 @@
         <v>96</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O23" si="0">(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+R6+S6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
+        <f>(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+S6+T6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
         <v>80.56</v>
       </c>
       <c r="P6" s="2">
-        <f t="shared" ref="P6:P24" si="1">O6/$N$2</f>
+        <f t="shared" ref="P6:P24" si="0">O6/$N$2</f>
         <v>89.511111111111106</v>
       </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
       <c r="S6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -948,21 +1123,30 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <f>(F7+F$33)*F$2+G$2*(G7+G$33)+H$2*(H7+H$33)+I$2*(I7+I$33+R7+S7)+J$2*(J7+J$33)+K$2*(K7+K$33)+L$2*(L7+L$33)+M$2*(M7+M$33)</f>
+        <f>(F7+F$33)*F$2+G$2*(G7+G$33)+H$2*(H7+H$33)+I$2*(I7+I$33+S7+T7)+J$2*(J7+J$33)+K$2*(K7+K$33)+L$2*(L7+L$33)+M$2*(M7+M$33)</f>
         <v>89.100000000000009</v>
       </c>
       <c r="P7" s="2">
         <f>O7/$N$2</f>
         <v>99</v>
       </c>
-      <c r="R7">
-        <v>3</v>
-      </c>
       <c r="S7">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="X7" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -997,21 +1181,30 @@
         <v>100</v>
       </c>
       <c r="O8">
+        <f>(F8+F$33)*F$2+G$2*(G8+G$33)+H$2*(H8+H$33)+I$2*(I8+I$33+S8+T8)+J$2*(J8+J$33)+K$2*(K8+K$33)+L$2*(L8+L$33)+M$2*(M8+M$33)</f>
+        <v>92.67</v>
+      </c>
+      <c r="P8" s="2">
         <f t="shared" si="0"/>
-        <v>92.67</v>
-      </c>
-      <c r="P8" s="2">
-        <f t="shared" si="1"/>
         <v>102.96666666666665</v>
       </c>
-      <c r="R8">
-        <v>3</v>
-      </c>
       <c r="S8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1046,21 +1239,30 @@
         <v>95</v>
       </c>
       <c r="O9">
-        <f t="shared" si="0"/>
+        <f>(F9+F$33)*F$2+G$2*(G9+G$33)+H$2*(H9+H$33)+I$2*(I9+I$33+S9+T9)+J$2*(J9+J$33)+K$2*(K9+K$33)+L$2*(L9+L$33)+M$2*(M9+M$33)</f>
         <v>77.77</v>
       </c>
       <c r="P9" s="2">
         <f>O9/$N$2</f>
         <v>86.411111111111097</v>
       </c>
-      <c r="R9">
-        <v>3</v>
-      </c>
       <c r="S9">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -1095,21 +1297,30 @@
         <v>99</v>
       </c>
       <c r="O10">
+        <f>(F10+F$33)*F$2+G$2*(G10+G$33)+H$2*(H10+H$33)+I$2*(I10+I$33+S10+T10)+J$2*(J10+J$33)+K$2*(K10+K$33)+L$2*(L10+L$33)+M$2*(M10+M$33)</f>
+        <v>87.13000000000001</v>
+      </c>
+      <c r="P10" s="2">
         <f t="shared" si="0"/>
-        <v>87.13000000000001</v>
-      </c>
-      <c r="P10" s="2">
-        <f t="shared" si="1"/>
         <v>96.811111111111103</v>
       </c>
-      <c r="R10">
-        <v>3</v>
-      </c>
       <c r="S10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10">
+        <v>3</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="X10" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
@@ -1144,21 +1355,30 @@
         <v>92</v>
       </c>
       <c r="O11">
+        <f>(F11+F$33)*F$2+G$2*(G11+G$33)+H$2*(H11+H$33)+I$2*(I11+I$33+S11+T11)+J$2*(J11+J$33)+K$2*(K11+K$33)+L$2*(L11+L$33)+M$2*(M11+M$33)</f>
+        <v>91.55</v>
+      </c>
+      <c r="P11" s="2">
         <f t="shared" si="0"/>
-        <v>91.55</v>
-      </c>
-      <c r="P11" s="2">
-        <f t="shared" si="1"/>
         <v>101.7222222222222</v>
       </c>
-      <c r="R11">
-        <v>3</v>
-      </c>
       <c r="S11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1193,21 +1413,30 @@
         <v>91</v>
       </c>
       <c r="O12">
+        <f>(F12+F$33)*F$2+G$2*(G12+G$33)+H$2*(H12+H$33)+I$2*(I12+I$33+S12+T12)+J$2*(J12+J$33)+K$2*(K12+K$33)+L$2*(L12+L$33)+M$2*(M12+M$33)</f>
+        <v>82.27</v>
+      </c>
+      <c r="P12" s="2">
         <f t="shared" si="0"/>
-        <v>82.27</v>
-      </c>
-      <c r="P12" s="2">
-        <f t="shared" si="1"/>
         <v>91.411111111111097</v>
       </c>
-      <c r="R12">
-        <v>3</v>
-      </c>
       <c r="S12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="X12" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1242,21 +1471,30 @@
         <v>100</v>
       </c>
       <c r="O13">
+        <f>(F13+F$33)*F$2+G$2*(G13+G$33)+H$2*(H13+H$33)+I$2*(I13+I$33+S13+T13)+J$2*(J13+J$33)+K$2*(K13+K$33)+L$2*(L13+L$33)+M$2*(M13+M$33)</f>
+        <v>88.89</v>
+      </c>
+      <c r="P13" s="2">
         <f t="shared" si="0"/>
-        <v>88.89</v>
-      </c>
-      <c r="P13" s="2">
-        <f t="shared" si="1"/>
         <v>98.766666666666652</v>
       </c>
-      <c r="R13">
-        <v>3</v>
-      </c>
       <c r="S13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1291,21 +1529,21 @@
         <v>100</v>
       </c>
       <c r="O14">
+        <f>(F14+F$33)*F$2+G$2*(G14+G$33)+H$2*(H14+H$33)+I$2*(I14+I$33+S14+T14)+J$2*(J14+J$33)+K$2*(K14+K$33)+L$2*(L14+L$33)+M$2*(M14+M$33)</f>
+        <v>89.58</v>
+      </c>
+      <c r="P14" s="2">
         <f t="shared" si="0"/>
-        <v>89.58</v>
-      </c>
-      <c r="P14" s="2">
-        <f t="shared" si="1"/>
         <v>99.533333333333317</v>
       </c>
-      <c r="R14">
-        <v>3</v>
-      </c>
       <c r="S14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>11</v>
       </c>
@@ -1340,18 +1578,18 @@
         <v>100</v>
       </c>
       <c r="O15">
+        <f>(F15+F$33)*F$2+G$2*(G15+G$33)+H$2*(H15+H$33)+I$2*(I15+I$33+S15+T15)+J$2*(J15+J$33)+K$2*(K15+K$33)+L$2*(L15+L$33)+M$2*(M15+M$33)</f>
+        <v>88.03</v>
+      </c>
+      <c r="P15" s="2">
         <f t="shared" si="0"/>
-        <v>88.03</v>
-      </c>
-      <c r="P15" s="2">
-        <f t="shared" si="1"/>
         <v>97.811111111111103</v>
       </c>
-      <c r="S15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>12</v>
       </c>
@@ -1386,21 +1624,21 @@
         <v>87</v>
       </c>
       <c r="O16">
-        <f>(F16+F$33)*F$2+G$2*(G16+G$33)+H$2*(H16+H$33)+I$2*(I16+I$33+R16+S16)+J$2*(J16+J$33)+K$2*(K16+K$33)+L$2*(L16+L$33)+M$2*(M16+M$33)</f>
+        <f>(F16+F$33)*F$2+G$2*(G16+G$33)+H$2*(H16+H$33)+I$2*(I16+I$33+S16+T16)+J$2*(J16+J$33)+K$2*(K16+K$33)+L$2*(L16+L$33)+M$2*(M16+M$33)</f>
         <v>69.08</v>
       </c>
       <c r="P16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>76.755555555555546</v>
       </c>
-      <c r="R16">
-        <v>3</v>
-      </c>
       <c r="S16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1435,24 +1673,24 @@
         <v>93</v>
       </c>
       <c r="O17">
+        <f>(F17+F$33)*F$2+G$2*(G17+G$33)+H$2*(H17+H$33)+I$2*(I17+I$33+S17+T17)+J$2*(J17+J$33)+K$2*(K17+K$33)+L$2*(L17+L$33)+M$2*(M17+M$33)</f>
+        <v>80.750000000000014</v>
+      </c>
+      <c r="P17" s="2">
         <f t="shared" si="0"/>
-        <v>80.750000000000014</v>
-      </c>
-      <c r="P17" s="2">
-        <f t="shared" si="1"/>
         <v>89.722222222222229</v>
       </c>
-      <c r="R17">
-        <v>3</v>
-      </c>
       <c r="S17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>14</v>
       </c>
@@ -1487,21 +1725,21 @@
         <v>100</v>
       </c>
       <c r="O19">
+        <f>(F19+F$33)*F$2+G$2*(G19+G$33)+H$2*(H19+H$33)+I$2*(I19+I$33+S19+T19)+J$2*(J19+J$33)+K$2*(K19+K$33)+L$2*(L19+L$33)+M$2*(M19+M$33)</f>
+        <v>92.56</v>
+      </c>
+      <c r="P19" s="2">
         <f t="shared" si="0"/>
-        <v>92.56</v>
-      </c>
-      <c r="P19" s="2">
-        <f t="shared" si="1"/>
         <v>102.84444444444443</v>
       </c>
-      <c r="R19">
-        <v>3</v>
-      </c>
       <c r="S19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>15</v>
       </c>
@@ -1536,21 +1774,21 @@
         <v>95</v>
       </c>
       <c r="O20">
+        <f>(F20+F$33)*F$2+G$2*(G20+G$33)+H$2*(H20+H$33)+I$2*(I20+I$33+S20+T20)+J$2*(J20+J$33)+K$2*(K20+K$33)+L$2*(L20+L$33)+M$2*(M20+M$33)</f>
+        <v>91.19</v>
+      </c>
+      <c r="P20" s="2">
         <f t="shared" si="0"/>
-        <v>91.19</v>
-      </c>
-      <c r="P20" s="2">
-        <f t="shared" si="1"/>
         <v>101.32222222222221</v>
       </c>
-      <c r="R20">
-        <v>3</v>
-      </c>
       <c r="S20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="T20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1573,15 +1811,15 @@
         <v>90</v>
       </c>
       <c r="O21">
+        <f>(F21+F$33)*F$2+G$2*(G21+G$33)+H$2*(H21+H$33)+I$2*(I21+I$33+S21+T21)+J$2*(J21+J$33)+K$2*(K21+K$33)+L$2*(L21+L$33)+M$2*(M21+M$33)</f>
+        <v>28.980000000000004</v>
+      </c>
+      <c r="P21" s="2">
         <f t="shared" si="0"/>
-        <v>28.980000000000004</v>
-      </c>
-      <c r="P21" s="2">
-        <f t="shared" si="1"/>
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>17</v>
       </c>
@@ -1616,21 +1854,21 @@
         <v>92</v>
       </c>
       <c r="O22">
+        <f>(F22+F$33)*F$2+G$2*(G22+G$33)+H$2*(H22+H$33)+I$2*(I22+I$33+S22+T22)+J$2*(J22+J$33)+K$2*(K22+K$33)+L$2*(L22+L$33)+M$2*(M22+M$33)</f>
+        <v>85.47</v>
+      </c>
+      <c r="P22" s="2">
         <f t="shared" si="0"/>
-        <v>85.47</v>
-      </c>
-      <c r="P22" s="2">
-        <f t="shared" si="1"/>
         <v>94.966666666666654</v>
       </c>
-      <c r="R22">
-        <v>3</v>
-      </c>
       <c r="S22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>18</v>
       </c>
@@ -1665,21 +1903,21 @@
         <v>98</v>
       </c>
       <c r="O23">
+        <f>(F23+F$33)*F$2+G$2*(G23+G$33)+H$2*(H23+H$33)+I$2*(I23+I$33+S23+T23)+J$2*(J23+J$33)+K$2*(K23+K$33)+L$2*(L23+L$33)+M$2*(M23+M$33)</f>
+        <v>85.120000000000019</v>
+      </c>
+      <c r="P23" s="2">
         <f t="shared" si="0"/>
-        <v>85.120000000000019</v>
-      </c>
-      <c r="P23" s="2">
-        <f t="shared" si="1"/>
         <v>94.577777777777783</v>
       </c>
-      <c r="R23">
-        <v>3</v>
-      </c>
       <c r="S23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>19</v>
       </c>
@@ -1714,30 +1952,30 @@
         <v>92</v>
       </c>
       <c r="O24">
-        <f>(F24+F$33)*F$2+G$2*(G24+G$33)+H$2*(H24+H$33)+I$2*(I24+I$33+R24+S24)+J$2*(J24+J$33)+K$2*(K24+K$33)+L$2*(L24+L$33)+M$2*(M24+M$33)</f>
+        <f>(F24+F$33)*F$2+G$2*(G24+G$33)+H$2*(H24+H$33)+I$2*(I24+I$33+S24+T24)+J$2*(J24+J$33)+K$2*(K24+K$33)+L$2*(L24+L$33)+M$2*(M24+M$33)</f>
         <v>80.279999999999987</v>
       </c>
       <c r="P24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>89.199999999999974</v>
       </c>
-      <c r="R24">
-        <v>3</v>
-      </c>
       <c r="S24">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="M26">
         <v>0.1</v>
       </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
         <v>70</v>
       </c>
@@ -1765,7 +2003,7 @@
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>20</v>
       </c>
@@ -1797,21 +2035,21 @@
         <v>85</v>
       </c>
       <c r="O28">
-        <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33+R28+S28)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
+        <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33+S28+T28)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
         <v>79.800000000000011</v>
       </c>
       <c r="P28" s="2">
         <f>O28/$N$27</f>
         <v>88.666666666666671</v>
       </c>
-      <c r="R28">
-        <v>3</v>
-      </c>
       <c r="S28">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+      <c r="T28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>21</v>
       </c>
@@ -1839,12 +2077,12 @@
         <v>12.22222222222222</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E31" s="1" t="s">
         <v>98</v>
       </c>
@@ -1853,7 +2091,7 @@
         <v>82.952380952380949</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="2">AVERAGE(G5:G24,G28:G29)</f>
+        <f t="shared" ref="G31" si="1">AVERAGE(G5:G24,G28:G29)</f>
         <v>85.523809523809518</v>
       </c>
       <c r="H31">
@@ -1869,31 +2107,31 @@
         <v>95.388888888888886</v>
       </c>
       <c r="K31">
-        <f t="shared" ref="K31:N31" si="3">AVERAGE(K5:K24,K28:K29)</f>
+        <f t="shared" ref="K31:N31" si="2">AVERAGE(K5:K24,K28:K29)</f>
         <v>94.1</v>
       </c>
       <c r="L31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>95.421052631578945</v>
       </c>
       <c r="M31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N31" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
-      </c>
-      <c r="R31">
-        <f>COUNT(R5:R24,R28)</f>
-        <v>18</v>
       </c>
       <c r="S31">
         <f>COUNT(S5:S24,S28)</f>
+        <v>18</v>
+      </c>
+      <c r="T31">
+        <f>COUNT(T5:T24,T28)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
         <v>100</v>
       </c>
@@ -1902,35 +2140,35 @@
         <v>18.829434910469786</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32:I32" si="4">STDEV(G5:G24,G28:G29)</f>
+        <f t="shared" ref="G32:I32" si="3">STDEV(G5:G24,G28:G29)</f>
         <v>18.06825682687473</v>
       </c>
       <c r="H32">
+        <f t="shared" si="3"/>
+        <v>13.45362404707371</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>5.6604713295373754</v>
+      </c>
+      <c r="J32">
+        <f t="shared" ref="J32:N32" si="4">STDEV(J5:J24,J28:J29)</f>
+        <v>2.992911014358643</v>
+      </c>
+      <c r="K32">
         <f t="shared" si="4"/>
-        <v>13.45362404707371</v>
-      </c>
-      <c r="I32">
+        <v>6.239939270959546</v>
+      </c>
+      <c r="L32">
         <f t="shared" si="4"/>
-        <v>5.6604713295373754</v>
-      </c>
-      <c r="J32">
-        <f t="shared" ref="J32:N32" si="5">STDEV(J5:J24,J28:J29)</f>
-        <v>2.992911014358643</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="5"/>
-        <v>6.239939270959546</v>
-      </c>
-      <c r="L32">
-        <f t="shared" si="5"/>
         <v>4.670424552123289</v>
       </c>
       <c r="M32" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N32" t="e">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3133,91 +3371,91 @@
         <v>76</v>
       </c>
       <c r="B53">
-        <f t="shared" ref="B53:W53" si="6">SUM(B38:B52)</f>
+        <f t="shared" ref="B53:W53" si="5">SUM(B38:B52)</f>
         <v>100</v>
       </c>
       <c r="C53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>93</v>
       </c>
       <c r="D53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>81</v>
       </c>
       <c r="E53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>97</v>
       </c>
       <c r="F53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>98</v>
       </c>
       <c r="G53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>76</v>
       </c>
       <c r="H53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>94</v>
       </c>
       <c r="I53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>94</v>
       </c>
       <c r="J53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>85</v>
       </c>
       <c r="K53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>92</v>
       </c>
       <c r="L53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>93</v>
       </c>
       <c r="M53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="N53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="O53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>78</v>
       </c>
       <c r="P53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>94</v>
       </c>
       <c r="R53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="S53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>90</v>
       </c>
       <c r="T53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>86</v>
       </c>
       <c r="U53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>78</v>
       </c>
       <c r="V53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>72</v>
       </c>
       <c r="W53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
     </row>
@@ -4288,91 +4526,91 @@
         <v>76</v>
       </c>
       <c r="B70">
-        <f t="shared" ref="B70:W70" si="7">SUM(B56:B69)</f>
+        <f t="shared" ref="B70:W70" si="6">SUM(B56:B69)</f>
         <v>100</v>
       </c>
       <c r="C70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>93</v>
       </c>
       <c r="D70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>87</v>
       </c>
       <c r="E70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>98</v>
       </c>
       <c r="F70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>99</v>
       </c>
       <c r="G70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="H70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="I70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="J70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>85</v>
       </c>
       <c r="K70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="L70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>94</v>
       </c>
       <c r="M70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="N70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="O70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>88</v>
       </c>
       <c r="P70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>96</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="R70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>65</v>
       </c>
       <c r="S70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>81</v>
       </c>
       <c r="T70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>93</v>
       </c>
       <c r="U70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>81</v>
       </c>
       <c r="V70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="W70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
     </row>
@@ -5359,91 +5597,91 @@
         <v>76</v>
       </c>
       <c r="B87">
-        <f t="shared" ref="B87:W87" si="8">SUM(B73:B86)</f>
+        <f t="shared" ref="B87:W87" si="7">SUM(B73:B86)</f>
         <v>100</v>
       </c>
       <c r="C87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>87</v>
       </c>
       <c r="D87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>72</v>
       </c>
       <c r="E87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>89</v>
       </c>
       <c r="F87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="G87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>53</v>
       </c>
       <c r="H87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="I87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>98</v>
       </c>
       <c r="J87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>72</v>
       </c>
       <c r="K87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>89</v>
       </c>
       <c r="L87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>96</v>
       </c>
       <c r="M87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="N87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>55</v>
       </c>
       <c r="O87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="P87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="Q87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>96</v>
       </c>
       <c r="R87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="T87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="U87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>82</v>
       </c>
       <c r="V87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
       <c r="W87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -6361,67 +6599,67 @@
         <v>76</v>
       </c>
       <c r="B103">
-        <f>SUM(B90:B102)</f>
+        <f t="shared" ref="B103:Q103" si="8">SUM(B90:B102)</f>
         <v>100</v>
       </c>
       <c r="C103">
-        <f>SUM(C90:C102)</f>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="D103">
-        <f>SUM(D90:D102)</f>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="E103">
-        <f>SUM(E90:E102)</f>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="F103">
-        <f>SUM(F90:F102)</f>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="G103">
-        <f>SUM(G90:G102)</f>
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
       <c r="H103">
-        <f>SUM(H90:H102)</f>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="I103">
-        <f>SUM(I90:I102)</f>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="J103">
-        <f>SUM(J90:J102)</f>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="K103">
-        <f>SUM(K90:K102)</f>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="L103">
-        <f>SUM(L90:L102)</f>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="M103">
-        <f>SUM(M90:M102)</f>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="N103">
-        <f>SUM(N90:N102)</f>
+        <f t="shared" si="8"/>
         <v>85</v>
       </c>
       <c r="O103">
-        <f>SUM(O90:O102)</f>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="P103">
-        <f>SUM(P90:P102)</f>
+        <f t="shared" si="8"/>
         <v>98</v>
       </c>
       <c r="Q103">
-        <f>SUM(Q90:Q102)</f>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="S103">

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EB49B5-C15B-304B-B72B-CCAB4960CFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8B0325-F2B2-A74A-B2BE-E0E319A5B1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13760" yWindow="1360" windowWidth="27200" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1600" yWindow="500" windowWidth="23220" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="132">
   <si>
     <t>First name</t>
   </si>
@@ -528,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -544,6 +544,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -878,17 +879,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X103"/>
+  <dimension ref="A2:X103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="M1">
-        <v>0.1</v>
-      </c>
-    </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F2">
         <v>0.16</v>
@@ -911,9 +907,12 @@
       <c r="L2">
         <v>0.05</v>
       </c>
+      <c r="M2">
+        <v>0.1</v>
+      </c>
       <c r="N2">
         <f>SUM(F2:M2)</f>
-        <v>0.90000000000000013</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>101</v>
@@ -1006,13 +1005,19 @@
       <c r="L5">
         <v>98</v>
       </c>
+      <c r="M5">
+        <v>99</v>
+      </c>
       <c r="O5">
-        <f>(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33+S5+T5)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
-        <v>88.090000000000018</v>
-      </c>
-      <c r="P5" s="2">
+        <f t="shared" ref="O5:O17" si="0">(F5+F$33)*F$2+G$2*(G5+G$33)+H$2*(H5+H$33)+I$2*(I5+I$33+S5+T5)+J$2*(J5+J$33)+K$2*(K5+K$33)+L$2*(L5+L$33)+M$2*(M5+M$33)</f>
+        <v>97.990000000000023</v>
+      </c>
+      <c r="P5" s="7">
         <f>O5/$N$2</f>
-        <v>97.87777777777778</v>
+        <v>97.99</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S5">
         <v>3</v>
@@ -1064,13 +1069,19 @@
       <c r="L6">
         <v>96</v>
       </c>
+      <c r="M6">
+        <v>96</v>
+      </c>
       <c r="O6">
-        <f>(F6+F$33)*F$2+G$2*(G6+G$33)+H$2*(H6+H$33)+I$2*(I6+I$33+S6+T6)+J$2*(J6+J$33)+K$2*(K6+K$33)+L$2*(L6+L$33)+M$2*(M6+M$33)</f>
-        <v>80.56</v>
-      </c>
-      <c r="P6" s="2">
-        <f t="shared" ref="P6:P24" si="0">O6/$N$2</f>
-        <v>89.511111111111106</v>
+        <f t="shared" si="0"/>
+        <v>90.16</v>
+      </c>
+      <c r="P6" s="7">
+        <f t="shared" ref="P6:P24" si="1">O6/$N$2</f>
+        <v>90.159999999999982</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="S6">
         <v>3</v>
@@ -1122,13 +1133,19 @@
       <c r="L7">
         <v>100</v>
       </c>
+      <c r="M7">
+        <v>100</v>
+      </c>
       <c r="O7">
-        <f>(F7+F$33)*F$2+G$2*(G7+G$33)+H$2*(H7+H$33)+I$2*(I7+I$33+S7+T7)+J$2*(J7+J$33)+K$2*(K7+K$33)+L$2*(L7+L$33)+M$2*(M7+M$33)</f>
-        <v>89.100000000000009</v>
-      </c>
-      <c r="P7" s="2">
+        <f t="shared" si="0"/>
+        <v>99.100000000000009</v>
+      </c>
+      <c r="P7" s="7">
         <f>O7/$N$2</f>
-        <v>99</v>
+        <v>99.09999999999998</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S7">
         <v>3</v>
@@ -1180,13 +1197,19 @@
       <c r="L8">
         <v>100</v>
       </c>
+      <c r="M8">
+        <v>100</v>
+      </c>
       <c r="O8">
-        <f>(F8+F$33)*F$2+G$2*(G8+G$33)+H$2*(H8+H$33)+I$2*(I8+I$33+S8+T8)+J$2*(J8+J$33)+K$2*(K8+K$33)+L$2*(L8+L$33)+M$2*(M8+M$33)</f>
-        <v>92.67</v>
-      </c>
-      <c r="P8" s="2">
         <f t="shared" si="0"/>
-        <v>102.96666666666665</v>
+        <v>102.67</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="1"/>
+        <v>102.66999999999997</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S8">
         <v>3</v>
@@ -1238,13 +1261,19 @@
       <c r="L9">
         <v>95</v>
       </c>
+      <c r="M9">
+        <v>90</v>
+      </c>
       <c r="O9">
-        <f>(F9+F$33)*F$2+G$2*(G9+G$33)+H$2*(H9+H$33)+I$2*(I9+I$33+S9+T9)+J$2*(J9+J$33)+K$2*(K9+K$33)+L$2*(L9+L$33)+M$2*(M9+M$33)</f>
-        <v>77.77</v>
-      </c>
-      <c r="P9" s="2">
+        <f t="shared" si="0"/>
+        <v>86.77</v>
+      </c>
+      <c r="P9" s="7">
         <f>O9/$N$2</f>
-        <v>86.411111111111097</v>
+        <v>86.769999999999982</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="S9">
         <v>3</v>
@@ -1296,13 +1325,19 @@
       <c r="L10">
         <v>99</v>
       </c>
+      <c r="M10">
+        <v>100</v>
+      </c>
       <c r="O10">
-        <f>(F10+F$33)*F$2+G$2*(G10+G$33)+H$2*(H10+H$33)+I$2*(I10+I$33+S10+T10)+J$2*(J10+J$33)+K$2*(K10+K$33)+L$2*(L10+L$33)+M$2*(M10+M$33)</f>
-        <v>87.13000000000001</v>
-      </c>
-      <c r="P10" s="2">
         <f t="shared" si="0"/>
-        <v>96.811111111111103</v>
+        <v>97.13000000000001</v>
+      </c>
+      <c r="P10" s="7">
+        <f t="shared" si="1"/>
+        <v>97.129999999999981</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S10">
         <v>3</v>
@@ -1354,13 +1389,19 @@
       <c r="L11">
         <v>92</v>
       </c>
+      <c r="M11">
+        <v>92</v>
+      </c>
       <c r="O11">
-        <f>(F11+F$33)*F$2+G$2*(G11+G$33)+H$2*(H11+H$33)+I$2*(I11+I$33+S11+T11)+J$2*(J11+J$33)+K$2*(K11+K$33)+L$2*(L11+L$33)+M$2*(M11+M$33)</f>
-        <v>91.55</v>
-      </c>
-      <c r="P11" s="2">
         <f t="shared" si="0"/>
-        <v>101.7222222222222</v>
+        <v>100.75</v>
+      </c>
+      <c r="P11" s="7">
+        <f t="shared" si="1"/>
+        <v>100.74999999999997</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S11">
         <v>3</v>
@@ -1412,13 +1453,19 @@
       <c r="L12">
         <v>91</v>
       </c>
+      <c r="M12">
+        <v>85</v>
+      </c>
       <c r="O12">
-        <f>(F12+F$33)*F$2+G$2*(G12+G$33)+H$2*(H12+H$33)+I$2*(I12+I$33+S12+T12)+J$2*(J12+J$33)+K$2*(K12+K$33)+L$2*(L12+L$33)+M$2*(M12+M$33)</f>
-        <v>82.27</v>
-      </c>
-      <c r="P12" s="2">
         <f t="shared" si="0"/>
-        <v>91.411111111111097</v>
+        <v>90.77</v>
+      </c>
+      <c r="P12" s="7">
+        <f t="shared" si="1"/>
+        <v>90.769999999999982</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="S12">
         <v>3</v>
@@ -1470,13 +1517,19 @@
       <c r="L13">
         <v>100</v>
       </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
       <c r="O13">
-        <f>(F13+F$33)*F$2+G$2*(G13+G$33)+H$2*(H13+H$33)+I$2*(I13+I$33+S13+T13)+J$2*(J13+J$33)+K$2*(K13+K$33)+L$2*(L13+L$33)+M$2*(M13+M$33)</f>
-        <v>88.89</v>
-      </c>
-      <c r="P13" s="2">
         <f t="shared" si="0"/>
-        <v>98.766666666666652</v>
+        <v>98.89</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" si="1"/>
+        <v>98.889999999999972</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S13">
         <v>3</v>
@@ -1528,13 +1581,19 @@
       <c r="L14">
         <v>100</v>
       </c>
+      <c r="M14">
+        <v>100</v>
+      </c>
       <c r="O14">
-        <f>(F14+F$33)*F$2+G$2*(G14+G$33)+H$2*(H14+H$33)+I$2*(I14+I$33+S14+T14)+J$2*(J14+J$33)+K$2*(K14+K$33)+L$2*(L14+L$33)+M$2*(M14+M$33)</f>
-        <v>89.58</v>
-      </c>
-      <c r="P14" s="2">
         <f t="shared" si="0"/>
-        <v>99.533333333333317</v>
+        <v>99.58</v>
+      </c>
+      <c r="P14" s="7">
+        <f t="shared" si="1"/>
+        <v>99.57999999999997</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S14">
         <v>3</v>
@@ -1577,13 +1636,19 @@
       <c r="L15">
         <v>100</v>
       </c>
+      <c r="M15">
+        <v>99</v>
+      </c>
       <c r="O15">
-        <f>(F15+F$33)*F$2+G$2*(G15+G$33)+H$2*(H15+H$33)+I$2*(I15+I$33+S15+T15)+J$2*(J15+J$33)+K$2*(K15+K$33)+L$2*(L15+L$33)+M$2*(M15+M$33)</f>
-        <v>88.03</v>
-      </c>
-      <c r="P15" s="2">
         <f t="shared" si="0"/>
-        <v>97.811111111111103</v>
+        <v>97.93</v>
+      </c>
+      <c r="P15" s="7">
+        <f t="shared" si="1"/>
+        <v>97.929999999999978</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="T15">
         <v>3</v>
@@ -1623,13 +1688,19 @@
       <c r="L16">
         <v>87</v>
       </c>
+      <c r="M16">
+        <v>80</v>
+      </c>
       <c r="O16">
-        <f>(F16+F$33)*F$2+G$2*(G16+G$33)+H$2*(H16+H$33)+I$2*(I16+I$33+S16+T16)+J$2*(J16+J$33)+K$2*(K16+K$33)+L$2*(L16+L$33)+M$2*(M16+M$33)</f>
-        <v>69.08</v>
-      </c>
-      <c r="P16" s="2">
         <f t="shared" si="0"/>
-        <v>76.755555555555546</v>
+        <v>77.08</v>
+      </c>
+      <c r="P16" s="7">
+        <f t="shared" si="1"/>
+        <v>77.079999999999984</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="S16">
         <v>3</v>
@@ -1672,13 +1743,19 @@
       <c r="L17">
         <v>93</v>
       </c>
+      <c r="M17">
+        <v>92</v>
+      </c>
       <c r="O17">
-        <f>(F17+F$33)*F$2+G$2*(G17+G$33)+H$2*(H17+H$33)+I$2*(I17+I$33+S17+T17)+J$2*(J17+J$33)+K$2*(K17+K$33)+L$2*(L17+L$33)+M$2*(M17+M$33)</f>
-        <v>80.750000000000014</v>
-      </c>
-      <c r="P17" s="2">
         <f t="shared" si="0"/>
-        <v>89.722222222222229</v>
+        <v>89.950000000000017</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="1"/>
+        <v>89.95</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="S17">
         <v>3</v>
@@ -1688,7 +1765,7 @@
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="P18" s="2"/>
+      <c r="P18" s="7"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19">
@@ -1724,13 +1801,19 @@
       <c r="L19">
         <v>100</v>
       </c>
+      <c r="M19">
+        <v>98</v>
+      </c>
       <c r="O19">
-        <f>(F19+F$33)*F$2+G$2*(G19+G$33)+H$2*(H19+H$33)+I$2*(I19+I$33+S19+T19)+J$2*(J19+J$33)+K$2*(K19+K$33)+L$2*(L19+L$33)+M$2*(M19+M$33)</f>
-        <v>92.56</v>
-      </c>
-      <c r="P19" s="2">
-        <f t="shared" si="0"/>
-        <v>102.84444444444443</v>
+        <f t="shared" ref="O19:O24" si="2">(F19+F$33)*F$2+G$2*(G19+G$33)+H$2*(H19+H$33)+I$2*(I19+I$33+S19+T19)+J$2*(J19+J$33)+K$2*(K19+K$33)+L$2*(L19+L$33)+M$2*(M19+M$33)</f>
+        <v>102.36</v>
+      </c>
+      <c r="P19" s="7">
+        <f t="shared" si="1"/>
+        <v>102.35999999999997</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S19">
         <v>3</v>
@@ -1773,13 +1856,19 @@
       <c r="L20">
         <v>95</v>
       </c>
+      <c r="M20">
+        <v>96</v>
+      </c>
       <c r="O20">
-        <f>(F20+F$33)*F$2+G$2*(G20+G$33)+H$2*(H20+H$33)+I$2*(I20+I$33+S20+T20)+J$2*(J20+J$33)+K$2*(K20+K$33)+L$2*(L20+L$33)+M$2*(M20+M$33)</f>
-        <v>91.19</v>
-      </c>
-      <c r="P20" s="2">
-        <f t="shared" si="0"/>
-        <v>101.32222222222221</v>
+        <f t="shared" si="2"/>
+        <v>100.78999999999999</v>
+      </c>
+      <c r="P20" s="7">
+        <f t="shared" si="1"/>
+        <v>100.78999999999996</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="S20">
         <v>3</v>
@@ -1811,12 +1900,12 @@
         <v>90</v>
       </c>
       <c r="O21">
-        <f>(F21+F$33)*F$2+G$2*(G21+G$33)+H$2*(H21+H$33)+I$2*(I21+I$33+S21+T21)+J$2*(J21+J$33)+K$2*(K21+K$33)+L$2*(L21+L$33)+M$2*(M21+M$33)</f>
+        <f t="shared" si="2"/>
         <v>28.980000000000004</v>
       </c>
-      <c r="P21" s="2">
-        <f t="shared" si="0"/>
-        <v>32.200000000000003</v>
+      <c r="P21" s="7">
+        <f t="shared" si="1"/>
+        <v>28.979999999999997</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -1853,13 +1942,19 @@
       <c r="L22">
         <v>92</v>
       </c>
+      <c r="M22">
+        <v>94</v>
+      </c>
       <c r="O22">
-        <f>(F22+F$33)*F$2+G$2*(G22+G$33)+H$2*(H22+H$33)+I$2*(I22+I$33+S22+T22)+J$2*(J22+J$33)+K$2*(K22+K$33)+L$2*(L22+L$33)+M$2*(M22+M$33)</f>
-        <v>85.47</v>
-      </c>
-      <c r="P22" s="2">
-        <f t="shared" si="0"/>
-        <v>94.966666666666654</v>
+        <f t="shared" si="2"/>
+        <v>94.87</v>
+      </c>
+      <c r="P22" s="7">
+        <f t="shared" si="1"/>
+        <v>94.86999999999999</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="S22">
         <v>3</v>
@@ -1902,13 +1997,19 @@
       <c r="L23">
         <v>98</v>
       </c>
+      <c r="M23">
+        <v>97</v>
+      </c>
       <c r="O23">
-        <f>(F23+F$33)*F$2+G$2*(G23+G$33)+H$2*(H23+H$33)+I$2*(I23+I$33+S23+T23)+J$2*(J23+J$33)+K$2*(K23+K$33)+L$2*(L23+L$33)+M$2*(M23+M$33)</f>
-        <v>85.120000000000019</v>
-      </c>
-      <c r="P23" s="2">
-        <f t="shared" si="0"/>
-        <v>94.577777777777783</v>
+        <f t="shared" si="2"/>
+        <v>94.820000000000022</v>
+      </c>
+      <c r="P23" s="7">
+        <f t="shared" si="1"/>
+        <v>94.820000000000007</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="S23">
         <v>3</v>
@@ -1951,13 +2052,19 @@
       <c r="L24">
         <v>92</v>
       </c>
+      <c r="M24">
+        <v>85</v>
+      </c>
       <c r="O24">
-        <f>(F24+F$33)*F$2+G$2*(G24+G$33)+H$2*(H24+H$33)+I$2*(I24+I$33+S24+T24)+J$2*(J24+J$33)+K$2*(K24+K$33)+L$2*(L24+L$33)+M$2*(M24+M$33)</f>
-        <v>80.279999999999987</v>
-      </c>
-      <c r="P24" s="2">
-        <f t="shared" si="0"/>
-        <v>89.199999999999974</v>
+        <f t="shared" si="2"/>
+        <v>88.779999999999987</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" si="1"/>
+        <v>88.779999999999973</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="S24">
         <v>3</v>
@@ -1967,13 +2074,10 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="P25" s="2"/>
+      <c r="P25" s="7"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="M26">
-        <v>0.1</v>
-      </c>
-      <c r="P26" s="2"/>
+      <c r="P26" s="7"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
@@ -1997,11 +2101,14 @@
       <c r="L27">
         <v>0.05</v>
       </c>
+      <c r="M27">
+        <v>0.1</v>
+      </c>
       <c r="N27">
         <f>SUM(F27:M27)</f>
-        <v>0.90000000000000013</v>
-      </c>
-      <c r="P27" s="2"/>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="P27" s="7"/>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28">
@@ -2034,13 +2141,19 @@
       <c r="L28">
         <v>85</v>
       </c>
+      <c r="M28">
+        <v>75</v>
+      </c>
       <c r="O28">
         <f>(F28+F$33)*F$27+G$27*(G28+G$33)+H$27*(H28+H$33)+I$27*(I28+I$33+S28+T28)+J$27*(J28+J$33)+K$27*(K28+K$33)+L$27*(L28+L$33)+M$27*(M28+M$33)</f>
-        <v>79.800000000000011</v>
-      </c>
-      <c r="P28" s="2">
+        <v>87.300000000000011</v>
+      </c>
+      <c r="P28" s="7">
         <f>O28/$N$27</f>
-        <v>88.666666666666671</v>
+        <v>87.3</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="S28">
         <v>3</v>
@@ -2074,7 +2187,7 @@
       </c>
       <c r="P29" s="2">
         <f>O29/$N$27</f>
-        <v>12.22222222222222</v>
+        <v>10.999999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
@@ -2091,7 +2204,7 @@
         <v>82.952380952380949</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="1">AVERAGE(G5:G24,G28:G29)</f>
+        <f t="shared" ref="G31" si="3">AVERAGE(G5:G24,G28:G29)</f>
         <v>85.523809523809518</v>
       </c>
       <c r="H31">
@@ -2107,19 +2220,19 @@
         <v>95.388888888888886</v>
       </c>
       <c r="K31">
-        <f t="shared" ref="K31:N31" si="2">AVERAGE(K5:K24,K28:K29)</f>
+        <f t="shared" ref="K31:N31" si="4">AVERAGE(K5:K24,K28:K29)</f>
         <v>94.1</v>
       </c>
       <c r="L31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95.421052631578945</v>
       </c>
-      <c r="M31" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="M31">
+        <f t="shared" si="4"/>
+        <v>93.578947368421055</v>
       </c>
       <c r="N31" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S31">
@@ -2140,35 +2253,35 @@
         <v>18.829434910469786</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32:I32" si="3">STDEV(G5:G24,G28:G29)</f>
+        <f t="shared" ref="G32:I32" si="5">STDEV(G5:G24,G28:G29)</f>
         <v>18.06825682687473</v>
       </c>
       <c r="H32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13.45362404707371</v>
       </c>
       <c r="I32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.6604713295373754</v>
       </c>
       <c r="J32">
-        <f t="shared" ref="J32:N32" si="4">STDEV(J5:J24,J28:J29)</f>
+        <f t="shared" ref="J32:N32" si="6">STDEV(J5:J24,J28:J29)</f>
         <v>2.992911014358643</v>
       </c>
       <c r="K32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.239939270959546</v>
       </c>
       <c r="L32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4.670424552123289</v>
       </c>
-      <c r="M32" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+      <c r="M32">
+        <f t="shared" si="6"/>
+        <v>7.4633607969844871</v>
       </c>
       <c r="N32" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2224,9 +2337,9 @@
         <f>L31+L33</f>
         <v>95.421052631578945</v>
       </c>
-      <c r="M34" t="e">
+      <c r="M34">
         <f>M31+M33</f>
-        <v>#DIV/0!</v>
+        <v>93.578947368421055</v>
       </c>
       <c r="N34" t="e">
         <f>N31+N33</f>
@@ -3371,91 +3484,91 @@
         <v>76</v>
       </c>
       <c r="B53">
-        <f t="shared" ref="B53:W53" si="5">SUM(B38:B52)</f>
+        <f t="shared" ref="B53:W53" si="7">SUM(B38:B52)</f>
         <v>100</v>
       </c>
       <c r="C53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="D53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>81</v>
       </c>
       <c r="E53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>97</v>
       </c>
       <c r="F53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>98</v>
       </c>
       <c r="G53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="H53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="I53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="J53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
       <c r="K53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="L53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>93</v>
       </c>
       <c r="M53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="N53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>51</v>
       </c>
       <c r="O53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>78</v>
       </c>
       <c r="P53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="Q53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="R53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>70</v>
       </c>
       <c r="S53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
       <c r="T53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="U53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>78</v>
       </c>
       <c r="V53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>72</v>
       </c>
       <c r="W53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
@@ -4526,91 +4639,91 @@
         <v>76</v>
       </c>
       <c r="B70">
-        <f t="shared" ref="B70:W70" si="6">SUM(B56:B69)</f>
+        <f t="shared" ref="B70:W70" si="8">SUM(B56:B69)</f>
         <v>100</v>
       </c>
       <c r="C70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="D70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="E70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>98</v>
       </c>
       <c r="F70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="G70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="H70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="I70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="J70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>85</v>
       </c>
       <c r="K70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="L70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="M70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="N70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>72</v>
       </c>
       <c r="O70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="P70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="R70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="S70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>81</v>
       </c>
       <c r="T70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="U70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>81</v>
       </c>
       <c r="V70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="W70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
     </row>
@@ -5597,91 +5710,91 @@
         <v>76</v>
       </c>
       <c r="B87">
-        <f t="shared" ref="B87:W87" si="7">SUM(B73:B86)</f>
+        <f t="shared" ref="B87:W87" si="9">SUM(B73:B86)</f>
         <v>100</v>
       </c>
       <c r="C87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>87</v>
       </c>
       <c r="D87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="E87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="F87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="G87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>53</v>
       </c>
       <c r="H87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>84</v>
       </c>
       <c r="I87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>98</v>
       </c>
       <c r="J87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>72</v>
       </c>
       <c r="K87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>89</v>
       </c>
       <c r="L87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="M87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="N87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>55</v>
       </c>
       <c r="O87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>76</v>
       </c>
       <c r="P87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="Q87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>96</v>
       </c>
       <c r="R87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="T87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="U87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>82</v>
       </c>
       <c r="V87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>85</v>
       </c>
       <c r="W87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -6599,67 +6712,67 @@
         <v>76</v>
       </c>
       <c r="B103">
-        <f t="shared" ref="B103:Q103" si="8">SUM(B90:B102)</f>
+        <f t="shared" ref="B103:Q103" si="10">SUM(B90:B102)</f>
         <v>100</v>
       </c>
       <c r="C103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>94</v>
       </c>
       <c r="D103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>82</v>
       </c>
       <c r="E103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>95</v>
       </c>
       <c r="F103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>99</v>
       </c>
       <c r="G103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>92</v>
       </c>
       <c r="H103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
       <c r="I103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="J103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>97</v>
       </c>
       <c r="K103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>95</v>
       </c>
       <c r="L103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>96</v>
       </c>
       <c r="M103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>93</v>
       </c>
       <c r="N103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>85</v>
       </c>
       <c r="O103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>86</v>
       </c>
       <c r="P103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>98</v>
       </c>
       <c r="Q103">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>99</v>
       </c>
       <c r="S103">

--- a/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
+++ b/Nuclear_Fuel_Performance/NE533_Spring2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Nuclear_Fuel_Performance/NE533_Spring2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8B0325-F2B2-A74A-B2BE-E0E319A5B1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A384D3B-697A-0141-A4A3-A1A2EF1CE312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="500" windowWidth="23220" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="400" yWindow="2720" windowWidth="25720" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
